--- a/artfynd/A 41290-2025 artfynd.xlsx
+++ b/artfynd/A 41290-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131067818</v>
+        <v>131067813</v>
       </c>
       <c r="B2" t="n">
-        <v>91829</v>
+        <v>57064</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,50 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465908</v>
+        <v>465954</v>
       </c>
       <c r="R2" t="n">
-        <v>7046627</v>
+        <v>7046648</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,34 +764,23 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Synobservation av 1 födosökande järpe i en björk.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -796,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131067813</v>
+        <v>131067818</v>
       </c>
       <c r="B3" t="n">
-        <v>57064</v>
+        <v>91829</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,50 +809,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465954</v>
+        <v>465908</v>
       </c>
       <c r="R3" t="n">
-        <v>7046648</v>
+        <v>7046627</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,23 +874,34 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Synobservation av 1 födosökande järpe i en björk.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131067020</v>
+        <v>131066991</v>
       </c>
       <c r="B4" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,34 +930,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466180</v>
+        <v>466192</v>
       </c>
       <c r="R4" t="n">
-        <v>7046800</v>
+        <v>7046678</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +1002,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Ringhack, äldre, enstaka på en gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,6 +1013,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1021,10 +1054,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131067470</v>
+        <v>131067779</v>
       </c>
       <c r="B5" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,34 +1065,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465713</v>
+        <v>466288</v>
       </c>
       <c r="R5" t="n">
-        <v>7046828</v>
+        <v>7046865</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,24 +1130,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Död gran</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,23 +1148,43 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131067023</v>
+        <v>131067020</v>
       </c>
       <c r="B6" t="n">
         <v>79244</v>
@@ -1162,19 +1213,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466072</v>
+        <v>466180</v>
       </c>
       <c r="R6" t="n">
-        <v>7046758</v>
+        <v>7046800</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,7 +1259,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,34 +1268,8 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1264,10 +1286,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131066991</v>
+        <v>131067470</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,42 +1297,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466192</v>
+        <v>465713</v>
       </c>
       <c r="R7" t="n">
-        <v>7046678</v>
+        <v>7046828</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,14 +1354,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på en gran.</t>
+          <t>Död gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,51 +1382,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131067779</v>
+        <v>131067023</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1410,31 +1409,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1442,10 +1436,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466288</v>
+        <v>466072</v>
       </c>
       <c r="R8" t="n">
-        <v>7046865</v>
+        <v>7046758</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1482,7 +1476,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,12 +1485,13 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1509,9 +1504,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1631,10 +1631,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131067027</v>
+        <v>131067812</v>
       </c>
       <c r="B10" t="n">
-        <v>79244</v>
+        <v>80350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,34 +1642,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466140</v>
+        <v>466199</v>
       </c>
       <c r="R10" t="n">
-        <v>7046777</v>
+        <v>7046948</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,7 +1709,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Skrovellav på gran!</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1715,8 +1718,34 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1733,10 +1762,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131067812</v>
+        <v>131067027</v>
       </c>
       <c r="B11" t="n">
-        <v>80350</v>
+        <v>79244</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1744,37 +1773,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466199</v>
+        <v>466140</v>
       </c>
       <c r="R11" t="n">
-        <v>7046948</v>
+        <v>7046777</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1811,7 +1837,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Skrovellav på gran!</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,34 +1846,8 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1864,10 +1864,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131067469</v>
+        <v>131066988</v>
       </c>
       <c r="B12" t="n">
-        <v>57064</v>
+        <v>57884</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,16 +1875,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1892,25 +1892,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465770</v>
+        <v>465681</v>
       </c>
       <c r="R12" t="n">
-        <v>7046758</v>
+        <v>7046766</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,24 +1940,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Flög upp.</t>
+          <t>Ringhack, färska, enstaka på stambasen av en gran i granskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1968,23 +1958,48 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131066988</v>
+        <v>131066992</v>
       </c>
       <c r="B13" t="n">
         <v>57884</v>
@@ -2017,7 +2032,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2027,10 +2042,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465681</v>
+        <v>466171</v>
       </c>
       <c r="R13" t="n">
-        <v>7046766</v>
+        <v>7046705</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2067,7 +2082,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka på stambasen av en gran i granskog.</t>
+          <t>Ringhack, äldre, på ca 2 meters höjd på en tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2081,17 +2096,17 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -2101,7 +2116,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2119,7 +2134,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131066992</v>
+        <v>131067808</v>
       </c>
       <c r="B14" t="n">
         <v>57884</v>
@@ -2162,10 +2177,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466171</v>
+        <v>465816</v>
       </c>
       <c r="R14" t="n">
-        <v>7046705</v>
+        <v>7046818</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2202,7 +2217,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på ca 2 meters höjd på en tall.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2216,17 +2231,17 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -2236,7 +2251,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2254,10 +2269,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131067808</v>
+        <v>131067469</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>57064</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,16 +2280,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2282,25 +2297,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465816</v>
+        <v>465770</v>
       </c>
       <c r="R15" t="n">
-        <v>7046818</v>
+        <v>7046758</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2330,14 +2345,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Flög upp.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2348,41 +2373,16 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2496,10 +2496,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131067456</v>
+        <v>131067463</v>
       </c>
       <c r="B17" t="n">
-        <v>79244</v>
+        <v>80350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2507,21 +2507,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466261</v>
+        <v>466198</v>
       </c>
       <c r="R17" t="n">
-        <v>7046745</v>
+        <v>7046954</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2576,7 +2576,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2603,57 +2608,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131067003</v>
+        <v>131067456</v>
       </c>
       <c r="B18" t="n">
-        <v>57073</v>
+        <v>79244</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466180</v>
+        <v>466261</v>
       </c>
       <c r="R18" t="n">
-        <v>7046822</v>
+        <v>7046745</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2683,14 +2676,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket under en tall.</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2701,21 +2699,16 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2857,45 +2850,57 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131067463</v>
+        <v>131067003</v>
       </c>
       <c r="B20" t="n">
-        <v>80350</v>
+        <v>57073</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466198</v>
+        <v>466180</v>
       </c>
       <c r="R20" t="n">
-        <v>7046954</v>
+        <v>7046822</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2925,24 +2930,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Färsk spillning ovanpå snötäcket under en tall.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2953,61 +2948,66 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131067025</v>
+        <v>131067464</v>
       </c>
       <c r="B21" t="n">
-        <v>79244</v>
+        <v>75222</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466160</v>
+        <v>466197</v>
       </c>
       <c r="R21" t="n">
-        <v>7046687</v>
+        <v>7046956</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3037,14 +3037,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Död sälg</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3059,19 +3069,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131067457</v>
+        <v>131067467</v>
       </c>
       <c r="B22" t="n">
         <v>79244</v>
@@ -3106,10 +3116,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466188</v>
+        <v>465982</v>
       </c>
       <c r="R22" t="n">
-        <v>7046783</v>
+        <v>7046926</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3141,7 +3151,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3151,7 +3161,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3178,45 +3188,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131067464</v>
+        <v>131067025</v>
       </c>
       <c r="B23" t="n">
-        <v>75222</v>
+        <v>79244</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466197</v>
+        <v>466160</v>
       </c>
       <c r="R23" t="n">
-        <v>7046956</v>
+        <v>7046687</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3246,24 +3256,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Död sälg</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3278,19 +3278,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131067014</v>
+        <v>131067457</v>
       </c>
       <c r="B24" t="n">
         <v>79244</v>
@@ -3319,19 +3319,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465848</v>
+        <v>466188</v>
       </c>
       <c r="R24" t="n">
-        <v>7046818</v>
+        <v>7046783</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3361,14 +3358,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På gran i granskog.</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3377,51 +3379,25 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131067467</v>
+        <v>131067014</v>
       </c>
       <c r="B25" t="n">
         <v>79244</v>
@@ -3450,16 +3426,19 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465982</v>
+        <v>465848</v>
       </c>
       <c r="R25" t="n">
-        <v>7046926</v>
+        <v>7046818</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3489,19 +3468,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:07</t>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3510,18 +3484,44 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131067820</v>
+        <v>131067815</v>
       </c>
       <c r="B28" t="n">
-        <v>79244</v>
+        <v>91829</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3804,34 +3804,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3839,10 +3831,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466201</v>
+        <v>466248</v>
       </c>
       <c r="R28" t="n">
-        <v>7046958</v>
+        <v>7046866</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3877,11 +3869,6 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav här!</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3907,14 +3894,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3932,10 +3914,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131067815</v>
+        <v>131067820</v>
       </c>
       <c r="B29" t="n">
-        <v>91829</v>
+        <v>79244</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3943,26 +3925,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3970,10 +3960,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466248</v>
+        <v>466201</v>
       </c>
       <c r="R29" t="n">
-        <v>7046866</v>
+        <v>7046958</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4008,6 +3998,11 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav här!</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4033,9 +4028,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4688,7 +4688,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131067455</v>
+        <v>131067823</v>
       </c>
       <c r="B35" t="n">
         <v>79244</v>
@@ -4717,16 +4717,19 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466247</v>
+        <v>466269</v>
       </c>
       <c r="R35" t="n">
-        <v>7046669</v>
+        <v>7046701</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4756,46 +4759,42 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>10:26</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>10:26</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131067823</v>
+        <v>131067462</v>
       </c>
       <c r="B36" t="n">
         <v>79244</v>
@@ -4824,19 +4823,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466269</v>
+        <v>466212</v>
       </c>
       <c r="R36" t="n">
-        <v>7046701</v>
+        <v>7046990</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4866,42 +4862,46 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131067462</v>
+        <v>131067455</v>
       </c>
       <c r="B37" t="n">
         <v>79244</v>
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466212</v>
+        <v>466247</v>
       </c>
       <c r="R37" t="n">
-        <v>7046990</v>
+        <v>7046669</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5867,10 +5867,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131067017</v>
+        <v>131067010</v>
       </c>
       <c r="B45" t="n">
-        <v>79244</v>
+        <v>91829</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5878,34 +5878,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466015</v>
+        <v>465776</v>
       </c>
       <c r="R45" t="n">
-        <v>7046893</v>
+        <v>7046851</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5942,7 +5945,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5951,8 +5954,34 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5969,10 +5998,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131067010</v>
+        <v>131067017</v>
       </c>
       <c r="B46" t="n">
-        <v>91829</v>
+        <v>79244</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5980,37 +6009,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>465776</v>
+        <v>466015</v>
       </c>
       <c r="R46" t="n">
-        <v>7046851</v>
+        <v>7046893</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6047,7 +6073,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6056,34 +6082,8 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6987,7 +6987,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131067821</v>
+        <v>131067013</v>
       </c>
       <c r="B54" t="n">
         <v>79244</v>
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>466212</v>
+        <v>465836</v>
       </c>
       <c r="R54" t="n">
-        <v>7046860</v>
+        <v>7046836</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7063,6 +7063,11 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran i en lucka.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -7076,6 +7081,26 @@
       <c r="AH54" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7224,10 +7249,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131067013</v>
+        <v>131067816</v>
       </c>
       <c r="B56" t="n">
-        <v>79244</v>
+        <v>91829</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7235,26 +7260,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7262,10 +7287,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>465836</v>
+        <v>466283</v>
       </c>
       <c r="R56" t="n">
-        <v>7046836</v>
+        <v>7046884</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7300,11 +7325,6 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran i en lucka.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7330,14 +7350,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7355,10 +7370,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131067816</v>
+        <v>131067821</v>
       </c>
       <c r="B57" t="n">
-        <v>91829</v>
+        <v>79244</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7366,26 +7381,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7393,10 +7408,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>466283</v>
+        <v>466212</v>
       </c>
       <c r="R57" t="n">
-        <v>7046884</v>
+        <v>7046860</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7444,21 +7459,6 @@
       <c r="AH57" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7611,10 +7611,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131067771</v>
+        <v>131067819</v>
       </c>
       <c r="B59" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7622,29 +7622,24 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7654,10 +7649,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>466198</v>
+        <v>466023</v>
       </c>
       <c r="R59" t="n">
-        <v>7046862</v>
+        <v>7046926</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7692,17 +7687,13 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7741,10 +7732,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131067819</v>
+        <v>131067016</v>
       </c>
       <c r="B60" t="n">
-        <v>91829</v>
+        <v>79244</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7752,37 +7743,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>466023</v>
+        <v>466002</v>
       </c>
       <c r="R60" t="n">
-        <v>7046926</v>
+        <v>7046855</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7817,35 +7805,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7862,10 +7834,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131067016</v>
+        <v>131067771</v>
       </c>
       <c r="B61" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7873,34 +7845,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>466002</v>
+        <v>466198</v>
       </c>
       <c r="R61" t="n">
-        <v>7046855</v>
+        <v>7046862</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7937,7 +7917,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7948,6 +7928,26 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -8588,10 +8588,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131067758</v>
+        <v>131067807</v>
       </c>
       <c r="B67" t="n">
-        <v>91809</v>
+        <v>57884</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8599,28 +8599,29 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -8630,10 +8631,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>466220</v>
+        <v>465804</v>
       </c>
       <c r="R67" t="n">
-        <v>7046897</v>
+        <v>7046812</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8668,13 +8669,17 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8695,12 +8700,12 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8718,7 +8723,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131067807</v>
+        <v>131067780</v>
       </c>
       <c r="B68" t="n">
         <v>57884</v>
@@ -8761,10 +8766,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>465804</v>
+        <v>466268</v>
       </c>
       <c r="R68" t="n">
-        <v>7046812</v>
+        <v>7046893</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8828,14 +8833,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8853,10 +8853,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131067780</v>
+        <v>131067026</v>
       </c>
       <c r="B69" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8864,31 +8864,26 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8896,10 +8891,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>466268</v>
+        <v>466116</v>
       </c>
       <c r="R69" t="n">
-        <v>7046893</v>
+        <v>7046744</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8936,7 +8931,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På bark av tall i barrblandskog.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8945,27 +8940,33 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8983,10 +8984,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131067026</v>
+        <v>131067758</v>
       </c>
       <c r="B70" t="n">
-        <v>79244</v>
+        <v>91809</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8994,26 +8995,30 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9021,10 +9026,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>466116</v>
+        <v>466220</v>
       </c>
       <c r="R70" t="n">
-        <v>7046744</v>
+        <v>7046897</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9059,11 +9064,6 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>På bark av tall i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -9076,27 +9076,27 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9114,10 +9114,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131066994</v>
+        <v>131067814</v>
       </c>
       <c r="B71" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9125,29 +9125,24 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -9157,10 +9152,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>466211</v>
+        <v>465657</v>
       </c>
       <c r="R71" t="n">
-        <v>7046715</v>
+        <v>7046731</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9195,17 +9190,13 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran med spår av kådaflöde som står på sluttningen av en mindre kulle.</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -9224,14 +9215,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9356,7 +9342,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131067024</v>
+        <v>131067029</v>
       </c>
       <c r="B73" t="n">
         <v>79244</v>
@@ -9394,10 +9380,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>466097</v>
+        <v>466255</v>
       </c>
       <c r="R73" t="n">
-        <v>7046728</v>
+        <v>7046672</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9434,7 +9420,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9449,7 +9435,7 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -9487,7 +9473,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131067029</v>
+        <v>131067822</v>
       </c>
       <c r="B74" t="n">
         <v>79244</v>
@@ -9525,10 +9511,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>466255</v>
+        <v>466268</v>
       </c>
       <c r="R74" t="n">
-        <v>7046672</v>
+        <v>7046889</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9563,11 +9549,6 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -9581,26 +9562,6 @@
       <c r="AH74" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9618,10 +9579,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131067814</v>
+        <v>131067024</v>
       </c>
       <c r="B75" t="n">
-        <v>91829</v>
+        <v>79244</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9629,26 +9590,26 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9656,10 +9617,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>465657</v>
+        <v>466097</v>
       </c>
       <c r="R75" t="n">
-        <v>7046731</v>
+        <v>7046728</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9694,6 +9655,11 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På gran i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -9706,7 +9672,7 @@
       </c>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
@@ -9719,9 +9685,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9739,7 +9710,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131067822</v>
+        <v>131067018</v>
       </c>
       <c r="B76" t="n">
         <v>79244</v>
@@ -9777,10 +9748,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>466268</v>
+        <v>466067</v>
       </c>
       <c r="R76" t="n">
-        <v>7046889</v>
+        <v>7046910</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9815,6 +9786,11 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>På flera granar i granskog.</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -9828,6 +9804,26 @@
       <c r="AH76" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9845,10 +9841,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131067018</v>
+        <v>131066994</v>
       </c>
       <c r="B77" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9856,26 +9852,31 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9883,10 +9884,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>466067</v>
+        <v>466211</v>
       </c>
       <c r="R77" t="n">
-        <v>7046910</v>
+        <v>7046715</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9923,7 +9924,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På flera granar i granskog.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran med spår av kådaflöde som står på sluttningen av en mindre kulle.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9932,7 +9933,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9953,12 +9953,12 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>

--- a/artfynd/A 41290-2025 artfynd.xlsx
+++ b/artfynd/A 41290-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131067813</v>
+        <v>131067818</v>
       </c>
       <c r="B2" t="n">
-        <v>57064</v>
+        <v>91829</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,50 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465954</v>
+        <v>465908</v>
       </c>
       <c r="R2" t="n">
-        <v>7046648</v>
+        <v>7046627</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,23 +751,34 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Synobservation av 1 födosökande järpe i en björk.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -798,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131067818</v>
+        <v>131067813</v>
       </c>
       <c r="B3" t="n">
-        <v>91829</v>
+        <v>57064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,37 +807,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465908</v>
+        <v>465954</v>
       </c>
       <c r="R3" t="n">
-        <v>7046627</v>
+        <v>7046648</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,34 +885,23 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Synobservation av 1 födosökande järpe i en björk.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1529,10 +1529,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131067028</v>
+        <v>131067812</v>
       </c>
       <c r="B9" t="n">
-        <v>79244</v>
+        <v>80350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,34 +1540,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466204</v>
+        <v>466199</v>
       </c>
       <c r="R9" t="n">
-        <v>7046724</v>
+        <v>7046948</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1604,7 +1607,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Skrovellav på gran!</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,8 +1616,34 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1631,10 +1660,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131067812</v>
+        <v>131067028</v>
       </c>
       <c r="B10" t="n">
-        <v>80350</v>
+        <v>79244</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,37 +1671,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466199</v>
+        <v>466204</v>
       </c>
       <c r="R10" t="n">
-        <v>7046948</v>
+        <v>7046724</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1709,7 +1735,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Skrovellav på gran!</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1718,34 +1744,8 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1864,10 +1864,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131066988</v>
+        <v>131067469</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>57064</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,16 +1875,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1892,25 +1892,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465681</v>
+        <v>465770</v>
       </c>
       <c r="R12" t="n">
-        <v>7046766</v>
+        <v>7046758</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,14 +1940,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka på stambasen av en gran i granskog.</t>
+          <t>Flög upp.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1958,48 +1968,23 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131066992</v>
+        <v>131066988</v>
       </c>
       <c r="B13" t="n">
         <v>57884</v>
@@ -2032,7 +2017,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2042,10 +2027,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466171</v>
+        <v>465681</v>
       </c>
       <c r="R13" t="n">
-        <v>7046705</v>
+        <v>7046766</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2082,7 +2067,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på ca 2 meters höjd på en tall.</t>
+          <t>Ringhack, färska, enstaka på stambasen av en gran i granskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2096,17 +2081,17 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -2116,7 +2101,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2134,7 +2119,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131067808</v>
+        <v>131066992</v>
       </c>
       <c r="B14" t="n">
         <v>57884</v>
@@ -2177,10 +2162,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465816</v>
+        <v>466171</v>
       </c>
       <c r="R14" t="n">
-        <v>7046818</v>
+        <v>7046705</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2217,7 +2202,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, äldre, på ca 2 meters höjd på en tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2231,17 +2216,17 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -2251,7 +2236,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2269,10 +2254,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131067469</v>
+        <v>131067808</v>
       </c>
       <c r="B15" t="n">
-        <v>57064</v>
+        <v>57884</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2280,16 +2265,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2297,25 +2282,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465770</v>
+        <v>465816</v>
       </c>
       <c r="R15" t="n">
-        <v>7046758</v>
+        <v>7046818</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2345,24 +2330,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Flög upp.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2373,61 +2348,98 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131067459</v>
+        <v>131067003</v>
       </c>
       <c r="B16" t="n">
-        <v>79244</v>
+        <v>57073</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466261</v>
+        <v>466180</v>
       </c>
       <c r="R16" t="n">
-        <v>7046954</v>
+        <v>7046822</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2457,19 +2469,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:07</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket under en tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2480,16 +2487,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2608,7 +2620,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131067456</v>
+        <v>131067459</v>
       </c>
       <c r="B18" t="n">
         <v>79244</v>
@@ -2646,7 +2658,7 @@
         <v>466261</v>
       </c>
       <c r="R18" t="n">
-        <v>7046745</v>
+        <v>7046954</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2678,7 +2690,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2688,7 +2700,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2715,10 +2727,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131067766</v>
+        <v>131067456</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2726,42 +2738,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466011</v>
+        <v>466261</v>
       </c>
       <c r="R19" t="n">
-        <v>7046933</v>
+        <v>7046745</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2791,14 +2795,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2809,73 +2818,48 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131067003</v>
+        <v>131067766</v>
       </c>
       <c r="B20" t="n">
-        <v>57073</v>
+        <v>57884</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2883,24 +2867,20 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466180</v>
+        <v>466011</v>
       </c>
       <c r="R20" t="n">
-        <v>7046822</v>
+        <v>7046933</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2937,7 +2917,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket under en tall.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2951,7 +2931,27 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2969,45 +2969,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131067464</v>
+        <v>131067765</v>
       </c>
       <c r="B21" t="n">
-        <v>75222</v>
+        <v>57884</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466197</v>
+        <v>466021</v>
       </c>
       <c r="R21" t="n">
-        <v>7046956</v>
+        <v>7046920</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3037,24 +3045,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Död sälg</t>
+          <t>Gammalt bohål 40 - 45 mm i diameter. Uthackat i stående död grantickerötad gran på 1,8 meters höjd över marken. På/kring fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3065,26 +3063,51 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131067467</v>
+        <v>131067777</v>
       </c>
       <c r="B22" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3092,34 +3115,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465982</v>
+        <v>466291</v>
       </c>
       <c r="R22" t="n">
-        <v>7046926</v>
+        <v>7046932</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3149,19 +3180,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:07</t>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3172,16 +3198,36 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3397,48 +3443,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131067014</v>
+        <v>131067464</v>
       </c>
       <c r="B25" t="n">
-        <v>79244</v>
+        <v>75222</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465848</v>
+        <v>466197</v>
       </c>
       <c r="R25" t="n">
-        <v>7046818</v>
+        <v>7046956</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3468,14 +3511,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Död sälg</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3484,54 +3537,28 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131067765</v>
+        <v>131067014</v>
       </c>
       <c r="B26" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3539,31 +3566,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3571,10 +3593,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466021</v>
+        <v>465848</v>
       </c>
       <c r="R26" t="n">
-        <v>7046920</v>
+        <v>7046818</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3611,7 +3633,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Gammalt bohål 40 - 45 mm i diameter. Uthackat i stående död grantickerötad gran på 1,8 meters höjd över marken. På/kring fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3620,6 +3642,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3640,12 +3663,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3663,10 +3686,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131067777</v>
+        <v>131067467</v>
       </c>
       <c r="B27" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3674,42 +3697,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466291</v>
+        <v>465982</v>
       </c>
       <c r="R27" t="n">
-        <v>7046932</v>
+        <v>7046926</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3739,14 +3754,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3757,36 +3777,16 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -4688,7 +4688,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131067823</v>
+        <v>131067455</v>
       </c>
       <c r="B35" t="n">
         <v>79244</v>
@@ -4717,19 +4717,16 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466269</v>
+        <v>466247</v>
       </c>
       <c r="R35" t="n">
-        <v>7046701</v>
+        <v>7046669</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4759,42 +4756,46 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131067462</v>
+        <v>131067823</v>
       </c>
       <c r="B36" t="n">
         <v>79244</v>
@@ -4823,16 +4824,19 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466212</v>
+        <v>466269</v>
       </c>
       <c r="R36" t="n">
-        <v>7046990</v>
+        <v>7046701</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4862,46 +4866,42 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131067455</v>
+        <v>131067462</v>
       </c>
       <c r="B37" t="n">
         <v>79244</v>
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466247</v>
+        <v>466212</v>
       </c>
       <c r="R37" t="n">
-        <v>7046669</v>
+        <v>7046990</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5653,10 +5653,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131067468</v>
+        <v>131067010</v>
       </c>
       <c r="B43" t="n">
-        <v>79244</v>
+        <v>91829</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5664,34 +5664,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>465833</v>
+        <v>465776</v>
       </c>
       <c r="R43" t="n">
-        <v>7046793</v>
+        <v>7046851</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5721,19 +5724,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>14:48</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5742,25 +5740,51 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131067471</v>
+        <v>131067468</v>
       </c>
       <c r="B44" t="n">
         <v>79244</v>
@@ -5795,10 +5819,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>465684</v>
+        <v>465833</v>
       </c>
       <c r="R44" t="n">
-        <v>7046838</v>
+        <v>7046793</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5830,7 +5854,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5840,7 +5864,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5867,10 +5891,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131067010</v>
+        <v>131067471</v>
       </c>
       <c r="B45" t="n">
-        <v>91829</v>
+        <v>79244</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5878,37 +5902,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>465776</v>
+        <v>465684</v>
       </c>
       <c r="R45" t="n">
-        <v>7046851</v>
+        <v>7046838</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5938,14 +5959,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5954,44 +5980,18 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -6235,10 +6235,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131067458</v>
+        <v>131067824</v>
       </c>
       <c r="B48" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6246,42 +6246,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>466199</v>
+        <v>466223</v>
       </c>
       <c r="R48" t="n">
-        <v>7046831</v>
+        <v>7046669</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6311,54 +6306,45 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack, färska</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131067824</v>
+        <v>131067458</v>
       </c>
       <c r="B49" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6366,37 +6352,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>466223</v>
+        <v>466199</v>
       </c>
       <c r="R49" t="n">
-        <v>7046669</v>
+        <v>7046831</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6426,35 +6417,44 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack, färska</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6987,10 +6987,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131067013</v>
+        <v>131067004</v>
       </c>
       <c r="B54" t="n">
-        <v>79244</v>
+        <v>57881</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6998,26 +6998,31 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7025,10 +7030,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>465836</v>
+        <v>465997</v>
       </c>
       <c r="R54" t="n">
-        <v>7046836</v>
+        <v>7046830</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7065,7 +7070,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i en lucka.</t>
+          <t>Rejäla hackspår i en gran med sockel.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7074,7 +7079,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7095,12 +7099,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7118,7 +7122,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131067019</v>
+        <v>131067821</v>
       </c>
       <c r="B55" t="n">
         <v>79244</v>
@@ -7156,10 +7160,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>466214</v>
+        <v>466212</v>
       </c>
       <c r="R55" t="n">
-        <v>7046881</v>
+        <v>7046860</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7194,11 +7198,6 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -7212,26 +7211,6 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7249,10 +7228,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131067816</v>
+        <v>131067019</v>
       </c>
       <c r="B56" t="n">
-        <v>91829</v>
+        <v>79244</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7260,26 +7239,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7287,10 +7266,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>466283</v>
+        <v>466214</v>
       </c>
       <c r="R56" t="n">
-        <v>7046884</v>
+        <v>7046881</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7325,6 +7304,11 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7350,9 +7334,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7370,7 +7359,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131067821</v>
+        <v>131067013</v>
       </c>
       <c r="B57" t="n">
         <v>79244</v>
@@ -7408,10 +7397,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>466212</v>
+        <v>465836</v>
       </c>
       <c r="R57" t="n">
-        <v>7046860</v>
+        <v>7046836</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7446,6 +7435,11 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran i en lucka.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7459,6 +7453,26 @@
       <c r="AH57" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7476,10 +7490,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131067004</v>
+        <v>131067816</v>
       </c>
       <c r="B58" t="n">
-        <v>57881</v>
+        <v>91829</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7487,29 +7501,24 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -7519,10 +7528,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>465997</v>
+        <v>466283</v>
       </c>
       <c r="R58" t="n">
-        <v>7046830</v>
+        <v>7046884</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7557,17 +7566,13 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i en gran med sockel.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7586,14 +7591,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8588,10 +8588,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131067807</v>
+        <v>131067758</v>
       </c>
       <c r="B67" t="n">
-        <v>57884</v>
+        <v>91809</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8599,29 +8599,28 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -8631,10 +8630,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>465804</v>
+        <v>466220</v>
       </c>
       <c r="R67" t="n">
-        <v>7046812</v>
+        <v>7046897</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8669,17 +8668,13 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8700,12 +8695,12 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8723,10 +8718,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131067780</v>
+        <v>131067026</v>
       </c>
       <c r="B68" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8734,31 +8729,26 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8766,10 +8756,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>466268</v>
+        <v>466116</v>
       </c>
       <c r="R68" t="n">
-        <v>7046893</v>
+        <v>7046744</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8806,7 +8796,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På bark av tall i barrblandskog.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8815,27 +8805,33 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8853,10 +8849,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131067026</v>
+        <v>131067807</v>
       </c>
       <c r="B69" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8864,26 +8860,31 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8891,10 +8892,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>466116</v>
+        <v>465804</v>
       </c>
       <c r="R69" t="n">
-        <v>7046744</v>
+        <v>7046812</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8931,7 +8932,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På bark av tall i barrblandskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8940,33 +8941,32 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8984,10 +8984,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131067758</v>
+        <v>131067780</v>
       </c>
       <c r="B70" t="n">
-        <v>91809</v>
+        <v>57884</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8995,28 +8995,29 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -9026,10 +9027,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>466220</v>
+        <v>466268</v>
       </c>
       <c r="R70" t="n">
-        <v>7046897</v>
+        <v>7046893</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9064,13 +9065,17 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -9089,14 +9094,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9114,10 +9114,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131067814</v>
+        <v>131067472</v>
       </c>
       <c r="B71" t="n">
-        <v>91829</v>
+        <v>79244</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9125,37 +9125,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>465657</v>
+        <v>465661</v>
       </c>
       <c r="R71" t="n">
-        <v>7046731</v>
+        <v>7046738</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9185,57 +9182,46 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131067472</v>
+        <v>131067024</v>
       </c>
       <c r="B72" t="n">
         <v>79244</v>
@@ -9264,16 +9250,19 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>465661</v>
+        <v>466097</v>
       </c>
       <c r="R72" t="n">
-        <v>7046738</v>
+        <v>7046728</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9303,19 +9292,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>15:28</t>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9324,18 +9308,44 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -9579,7 +9589,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131067024</v>
+        <v>131067018</v>
       </c>
       <c r="B75" t="n">
         <v>79244</v>
@@ -9617,10 +9627,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>466097</v>
+        <v>466067</v>
       </c>
       <c r="R75" t="n">
-        <v>7046728</v>
+        <v>7046910</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9657,7 +9667,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>På flera granar i granskog.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9672,7 +9682,7 @@
       </c>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
@@ -9710,10 +9720,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131067018</v>
+        <v>131067814</v>
       </c>
       <c r="B76" t="n">
-        <v>79244</v>
+        <v>91829</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9721,26 +9731,26 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9748,10 +9758,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>466067</v>
+        <v>465657</v>
       </c>
       <c r="R76" t="n">
-        <v>7046910</v>
+        <v>7046731</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9786,11 +9796,6 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>På flera granar i granskog.</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -9816,14 +9821,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10237,10 +10237,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131066995</v>
+        <v>131067811</v>
       </c>
       <c r="B80" t="n">
-        <v>57884</v>
+        <v>58043</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10248,42 +10248,50 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>466224</v>
+        <v>465799</v>
       </c>
       <c r="R80" t="n">
-        <v>7046722</v>
+        <v>7046814</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10320,7 +10328,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran i granskog.</t>
+          <t>Synobservation av 2 st födosökande talltitor i äldre granskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10335,26 +10343,6 @@
       <c r="AH80" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10372,10 +10360,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131067811</v>
+        <v>131066995</v>
       </c>
       <c r="B81" t="n">
-        <v>58043</v>
+        <v>57884</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10383,50 +10371,42 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>465799</v>
+        <v>466224</v>
       </c>
       <c r="R81" t="n">
-        <v>7046814</v>
+        <v>7046722</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10463,7 +10443,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Synobservation av 2 st födosökande talltitor i äldre granskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran i granskog.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10478,6 +10458,26 @@
       <c r="AH81" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>

--- a/artfynd/A 41290-2025 artfynd.xlsx
+++ b/artfynd/A 41290-2025 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131066991</v>
+        <v>131067020</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,42 +930,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466192</v>
+        <v>466180</v>
       </c>
       <c r="R4" t="n">
-        <v>7046678</v>
+        <v>7046800</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,7 +994,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på en gran.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,31 +1005,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1054,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131067779</v>
+        <v>131067470</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1065,42 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466288</v>
+        <v>465713</v>
       </c>
       <c r="R5" t="n">
-        <v>7046865</v>
+        <v>7046828</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,14 +1089,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Död gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,43 +1117,23 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131067020</v>
+        <v>131067023</v>
       </c>
       <c r="B6" t="n">
         <v>79244</v>
@@ -1213,16 +1162,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466180</v>
+        <v>466072</v>
       </c>
       <c r="R6" t="n">
-        <v>7046800</v>
+        <v>7046758</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1259,7 +1211,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,8 +1220,34 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1286,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131067470</v>
+        <v>131066991</v>
       </c>
       <c r="B7" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,34 +1275,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465713</v>
+        <v>466192</v>
       </c>
       <c r="R7" t="n">
-        <v>7046828</v>
+        <v>7046678</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,24 +1340,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Död gran</t>
+          <t>Ringhack, äldre, enstaka på en gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,26 +1358,51 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131067023</v>
+        <v>131067779</v>
       </c>
       <c r="B8" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,26 +1410,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1436,10 +1442,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466072</v>
+        <v>466288</v>
       </c>
       <c r="R8" t="n">
-        <v>7046758</v>
+        <v>7046865</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1482,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1485,13 +1491,12 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1504,14 +1509,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -2389,57 +2389,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131067003</v>
+        <v>131067463</v>
       </c>
       <c r="B16" t="n">
-        <v>57073</v>
+        <v>80350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466180</v>
+        <v>466198</v>
       </c>
       <c r="R16" t="n">
-        <v>7046822</v>
+        <v>7046954</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2469,14 +2457,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket under en tall.</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2487,31 +2485,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131067463</v>
+        <v>131067459</v>
       </c>
       <c r="B17" t="n">
-        <v>80350</v>
+        <v>79244</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2519,21 +2512,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2543,7 +2536,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466198</v>
+        <v>466261</v>
       </c>
       <c r="R17" t="n">
         <v>7046954</v>
@@ -2578,7 +2571,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2588,12 +2581,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Sälg</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2620,7 +2608,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131067459</v>
+        <v>131067456</v>
       </c>
       <c r="B18" t="n">
         <v>79244</v>
@@ -2658,7 +2646,7 @@
         <v>466261</v>
       </c>
       <c r="R18" t="n">
-        <v>7046954</v>
+        <v>7046745</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2690,7 +2678,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2700,7 +2688,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2727,45 +2715,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131067456</v>
+        <v>131067003</v>
       </c>
       <c r="B19" t="n">
-        <v>79244</v>
+        <v>57073</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466261</v>
+        <v>466180</v>
       </c>
       <c r="R19" t="n">
-        <v>7046745</v>
+        <v>7046822</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2795,19 +2795,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10:34</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>10:34</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket under en tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2818,16 +2813,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2969,10 +2969,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131067765</v>
+        <v>131067457</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2980,42 +2980,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466021</v>
+        <v>466188</v>
       </c>
       <c r="R21" t="n">
-        <v>7046920</v>
+        <v>7046783</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3045,14 +3037,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gammalt bohål 40 - 45 mm i diameter. Uthackat i stående död grantickerötad gran på 1,8 meters höjd över marken. På/kring fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3063,94 +3060,61 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131067777</v>
+        <v>131067464</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>75222</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466291</v>
+        <v>466197</v>
       </c>
       <c r="R22" t="n">
-        <v>7046932</v>
+        <v>7046956</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3180,14 +3144,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Död sälg</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3198,43 +3172,23 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131067025</v>
+        <v>131067014</v>
       </c>
       <c r="B23" t="n">
         <v>79244</v>
@@ -3263,16 +3217,19 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466160</v>
+        <v>465848</v>
       </c>
       <c r="R23" t="n">
-        <v>7046687</v>
+        <v>7046818</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3309,7 +3266,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3318,8 +3275,34 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3336,7 +3319,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131067457</v>
+        <v>131067467</v>
       </c>
       <c r="B24" t="n">
         <v>79244</v>
@@ -3371,10 +3354,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466188</v>
+        <v>465982</v>
       </c>
       <c r="R24" t="n">
-        <v>7046783</v>
+        <v>7046926</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3406,7 +3389,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3416,7 +3399,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3443,45 +3426,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131067464</v>
+        <v>131067765</v>
       </c>
       <c r="B25" t="n">
-        <v>75222</v>
+        <v>57884</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466197</v>
+        <v>466021</v>
       </c>
       <c r="R25" t="n">
-        <v>7046956</v>
+        <v>7046920</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3511,24 +3502,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Död sälg</t>
+          <t>Gammalt bohål 40 - 45 mm i diameter. Uthackat i stående död grantickerötad gran på 1,8 meters höjd över marken. På/kring fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3539,26 +3520,51 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131067014</v>
+        <v>131067777</v>
       </c>
       <c r="B26" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3566,26 +3572,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3593,10 +3604,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465848</v>
+        <v>466291</v>
       </c>
       <c r="R26" t="n">
-        <v>7046818</v>
+        <v>7046932</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3633,7 +3644,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3642,7 +3653,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3661,14 +3671,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3686,7 +3691,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131067467</v>
+        <v>131067025</v>
       </c>
       <c r="B27" t="n">
         <v>79244</v>
@@ -3717,14 +3722,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>465982</v>
+        <v>466160</v>
       </c>
       <c r="R27" t="n">
-        <v>7046926</v>
+        <v>7046687</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3754,19 +3759,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:07</t>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3781,22 +3781,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131067815</v>
+        <v>131067820</v>
       </c>
       <c r="B28" t="n">
-        <v>91829</v>
+        <v>79244</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3804,26 +3804,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3831,10 +3839,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466248</v>
+        <v>466201</v>
       </c>
       <c r="R28" t="n">
-        <v>7046866</v>
+        <v>7046958</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3869,6 +3877,11 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav här!</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3894,9 +3907,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3914,10 +3932,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131067820</v>
+        <v>131067815</v>
       </c>
       <c r="B29" t="n">
-        <v>79244</v>
+        <v>91829</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3925,34 +3943,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3960,10 +3970,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466201</v>
+        <v>466248</v>
       </c>
       <c r="R29" t="n">
-        <v>7046958</v>
+        <v>7046866</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3998,11 +4008,6 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav här!</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4028,14 +4033,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4688,10 +4688,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131067455</v>
+        <v>131067778</v>
       </c>
       <c r="B35" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4699,34 +4699,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466247</v>
+        <v>466299</v>
       </c>
       <c r="R35" t="n">
-        <v>7046669</v>
+        <v>7046954</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4756,19 +4764,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>10:26</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>10:26</t>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4779,26 +4782,46 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131067823</v>
+        <v>131067769</v>
       </c>
       <c r="B36" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4806,26 +4829,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4833,10 +4861,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466269</v>
+        <v>466118</v>
       </c>
       <c r="R36" t="n">
-        <v>7046701</v>
+        <v>7046899</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4871,19 +4899,38 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4901,10 +4948,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131067462</v>
+        <v>131067466</v>
       </c>
       <c r="B37" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4912,34 +4959,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466212</v>
+        <v>465976</v>
       </c>
       <c r="R37" t="n">
-        <v>7046990</v>
+        <v>7046933</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4971,7 +5026,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4981,7 +5036,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5008,7 +5068,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131067778</v>
+        <v>131067776</v>
       </c>
       <c r="B38" t="n">
         <v>57884</v>
@@ -5051,10 +5111,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466299</v>
+        <v>466296</v>
       </c>
       <c r="R38" t="n">
-        <v>7046954</v>
+        <v>7046956</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5138,10 +5198,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131067769</v>
+        <v>131067455</v>
       </c>
       <c r="B39" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5149,42 +5209,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466118</v>
+        <v>466247</v>
       </c>
       <c r="R39" t="n">
-        <v>7046899</v>
+        <v>7046669</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5214,14 +5266,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5232,46 +5289,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131067466</v>
+        <v>131067823</v>
       </c>
       <c r="B40" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5279,42 +5316,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465976</v>
+        <v>466269</v>
       </c>
       <c r="R40" t="n">
-        <v>7046933</v>
+        <v>7046701</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5344,54 +5376,45 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131067776</v>
+        <v>131067462</v>
       </c>
       <c r="B41" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5399,42 +5422,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466296</v>
+        <v>466212</v>
       </c>
       <c r="R41" t="n">
-        <v>7046956</v>
+        <v>7046990</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5464,14 +5479,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5482,36 +5502,16 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5653,10 +5653,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131067010</v>
+        <v>131067468</v>
       </c>
       <c r="B43" t="n">
-        <v>91829</v>
+        <v>79244</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5664,37 +5664,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>465776</v>
+        <v>465833</v>
       </c>
       <c r="R43" t="n">
-        <v>7046851</v>
+        <v>7046793</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5724,14 +5721,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5740,51 +5742,25 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131067468</v>
+        <v>131067471</v>
       </c>
       <c r="B44" t="n">
         <v>79244</v>
@@ -5819,10 +5795,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>465833</v>
+        <v>465684</v>
       </c>
       <c r="R44" t="n">
-        <v>7046793</v>
+        <v>7046838</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5854,7 +5830,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5864,7 +5840,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5891,7 +5867,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131067471</v>
+        <v>131067017</v>
       </c>
       <c r="B45" t="n">
         <v>79244</v>
@@ -5922,14 +5898,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>465684</v>
+        <v>466015</v>
       </c>
       <c r="R45" t="n">
-        <v>7046838</v>
+        <v>7046893</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5959,19 +5935,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>15:18</t>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5986,22 +5957,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131067017</v>
+        <v>131067010</v>
       </c>
       <c r="B46" t="n">
-        <v>79244</v>
+        <v>91829</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6009,34 +5980,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466015</v>
+        <v>465776</v>
       </c>
       <c r="R46" t="n">
-        <v>7046893</v>
+        <v>7046851</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6073,7 +6047,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6082,8 +6056,34 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6461,10 +6461,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131067022</v>
+        <v>131067770</v>
       </c>
       <c r="B50" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6472,26 +6472,31 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6499,10 +6504,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>466123</v>
+        <v>466195</v>
       </c>
       <c r="R50" t="n">
-        <v>7046774</v>
+        <v>7046876</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6539,7 +6544,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i  barrblandskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6548,13 +6553,12 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -6567,14 +6571,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6592,10 +6591,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131067770</v>
+        <v>131067022</v>
       </c>
       <c r="B51" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6603,31 +6602,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6635,10 +6629,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>466195</v>
+        <v>466123</v>
       </c>
       <c r="R51" t="n">
-        <v>7046876</v>
+        <v>7046774</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6675,7 +6669,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Långväxta bålar på gran i  barrblandskog.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6684,12 +6678,13 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -6702,9 +6697,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -8588,10 +8588,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131067758</v>
+        <v>131067807</v>
       </c>
       <c r="B67" t="n">
-        <v>91809</v>
+        <v>57884</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8599,28 +8599,29 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -8630,10 +8631,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>466220</v>
+        <v>465804</v>
       </c>
       <c r="R67" t="n">
-        <v>7046897</v>
+        <v>7046812</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8668,13 +8669,17 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8695,12 +8700,12 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8718,10 +8723,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131067026</v>
+        <v>131067780</v>
       </c>
       <c r="B68" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8729,26 +8734,31 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8756,10 +8766,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>466116</v>
+        <v>466268</v>
       </c>
       <c r="R68" t="n">
-        <v>7046744</v>
+        <v>7046893</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8796,7 +8806,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På bark av tall i barrblandskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8805,33 +8815,27 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8849,10 +8853,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131067807</v>
+        <v>131067758</v>
       </c>
       <c r="B69" t="n">
-        <v>57884</v>
+        <v>91809</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8860,29 +8864,28 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -8892,10 +8895,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>465804</v>
+        <v>466220</v>
       </c>
       <c r="R69" t="n">
-        <v>7046812</v>
+        <v>7046897</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8930,17 +8933,13 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8961,12 +8960,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8984,10 +8983,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131067780</v>
+        <v>131067026</v>
       </c>
       <c r="B70" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8995,31 +8994,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9027,10 +9021,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>466268</v>
+        <v>466116</v>
       </c>
       <c r="R70" t="n">
-        <v>7046893</v>
+        <v>7046744</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9067,7 +9061,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På bark av tall i barrblandskog.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9076,27 +9070,33 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9114,10 +9114,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131067472</v>
+        <v>131066994</v>
       </c>
       <c r="B71" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9125,34 +9125,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>465661</v>
+        <v>466211</v>
       </c>
       <c r="R71" t="n">
-        <v>7046738</v>
+        <v>7046715</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9182,19 +9190,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>15:28</t>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på stambasen av en gran med spår av kådaflöde som står på sluttningen av en mindre kulle.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9205,26 +9208,51 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131067024</v>
+        <v>131067773</v>
       </c>
       <c r="B72" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9232,26 +9260,31 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9259,10 +9292,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>466097</v>
+        <v>466253</v>
       </c>
       <c r="R72" t="n">
-        <v>7046728</v>
+        <v>7046994</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9299,7 +9332,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9308,13 +9341,12 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
@@ -9327,14 +9359,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9352,7 +9379,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131067029</v>
+        <v>131067472</v>
       </c>
       <c r="B73" t="n">
         <v>79244</v>
@@ -9381,19 +9408,16 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>466255</v>
+        <v>465661</v>
       </c>
       <c r="R73" t="n">
-        <v>7046672</v>
+        <v>7046738</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9423,14 +9447,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9439,51 +9468,25 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131067822</v>
+        <v>131067024</v>
       </c>
       <c r="B74" t="n">
         <v>79244</v>
@@ -9521,10 +9524,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>466268</v>
+        <v>466097</v>
       </c>
       <c r="R74" t="n">
-        <v>7046889</v>
+        <v>7046728</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9559,6 +9562,11 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På gran i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -9571,7 +9579,27 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9589,7 +9617,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131067018</v>
+        <v>131067029</v>
       </c>
       <c r="B75" t="n">
         <v>79244</v>
@@ -9627,10 +9655,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>466067</v>
+        <v>466255</v>
       </c>
       <c r="R75" t="n">
-        <v>7046910</v>
+        <v>7046672</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9667,7 +9695,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>På flera granar i granskog.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9841,10 +9869,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131066994</v>
+        <v>131067822</v>
       </c>
       <c r="B77" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9852,31 +9880,26 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9884,10 +9907,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>466211</v>
+        <v>466268</v>
       </c>
       <c r="R77" t="n">
-        <v>7046715</v>
+        <v>7046889</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9922,43 +9945,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran med spår av kådaflöde som står på sluttningen av en mindre kulle.</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9976,10 +9975,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131067773</v>
+        <v>131067018</v>
       </c>
       <c r="B78" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9987,31 +9986,26 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -10019,10 +10013,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>466253</v>
+        <v>466067</v>
       </c>
       <c r="R78" t="n">
-        <v>7046994</v>
+        <v>7046910</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10059,7 +10053,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På flera granar i granskog.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10068,6 +10062,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -10086,9 +10081,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10237,10 +10237,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131067811</v>
+        <v>131066995</v>
       </c>
       <c r="B80" t="n">
-        <v>58043</v>
+        <v>57884</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10248,50 +10248,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>465799</v>
+        <v>466224</v>
       </c>
       <c r="R80" t="n">
-        <v>7046814</v>
+        <v>7046722</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10328,7 +10320,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Synobservation av 2 st födosökande talltitor i äldre granskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran i granskog.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10343,6 +10335,26 @@
       <c r="AH80" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10360,10 +10372,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131066995</v>
+        <v>131067811</v>
       </c>
       <c r="B81" t="n">
-        <v>57884</v>
+        <v>58043</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10371,42 +10383,50 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>466224</v>
+        <v>465799</v>
       </c>
       <c r="R81" t="n">
-        <v>7046722</v>
+        <v>7046814</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10443,7 +10463,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran i granskog.</t>
+          <t>Synobservation av 2 st födosökande talltitor i äldre granskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10458,26 +10478,6 @@
       <c r="AH81" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>

--- a/artfynd/A 41290-2025 artfynd.xlsx
+++ b/artfynd/A 41290-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131067818</v>
       </c>
       <c r="B2" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>131067020</v>
       </c>
       <c r="B4" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>131067470</v>
       </c>
       <c r="B5" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>131067023</v>
       </c>
       <c r="B6" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1529,10 +1529,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131067812</v>
+        <v>131067028</v>
       </c>
       <c r="B9" t="n">
-        <v>80350</v>
+        <v>79245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,37 +1540,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466199</v>
+        <v>466204</v>
       </c>
       <c r="R9" t="n">
-        <v>7046948</v>
+        <v>7046724</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1607,7 +1604,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Skrovellav på gran!</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1616,34 +1613,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1660,10 +1631,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131067028</v>
+        <v>131067027</v>
       </c>
       <c r="B10" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,10 +1666,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466204</v>
+        <v>466140</v>
       </c>
       <c r="R10" t="n">
-        <v>7046724</v>
+        <v>7046777</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1762,10 +1733,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131067027</v>
+        <v>131067812</v>
       </c>
       <c r="B11" t="n">
-        <v>79244</v>
+        <v>80351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,34 +1744,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466140</v>
+        <v>466199</v>
       </c>
       <c r="R11" t="n">
-        <v>7046777</v>
+        <v>7046948</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1837,7 +1811,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Skrovellav på gran!</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1846,8 +1820,34 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1864,10 +1864,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131067469</v>
+        <v>131066988</v>
       </c>
       <c r="B12" t="n">
-        <v>57064</v>
+        <v>57884</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,16 +1875,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1892,25 +1892,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465770</v>
+        <v>465681</v>
       </c>
       <c r="R12" t="n">
-        <v>7046758</v>
+        <v>7046766</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,24 +1940,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Flög upp.</t>
+          <t>Ringhack, färska, enstaka på stambasen av en gran i granskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1968,23 +1958,48 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131066988</v>
+        <v>131066992</v>
       </c>
       <c r="B13" t="n">
         <v>57884</v>
@@ -2017,7 +2032,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2027,10 +2042,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465681</v>
+        <v>466171</v>
       </c>
       <c r="R13" t="n">
-        <v>7046766</v>
+        <v>7046705</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2067,7 +2082,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka på stambasen av en gran i granskog.</t>
+          <t>Ringhack, äldre, på ca 2 meters höjd på en tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2081,17 +2096,17 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -2101,7 +2116,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2119,7 +2134,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131066992</v>
+        <v>131067808</v>
       </c>
       <c r="B14" t="n">
         <v>57884</v>
@@ -2162,10 +2177,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466171</v>
+        <v>465816</v>
       </c>
       <c r="R14" t="n">
-        <v>7046705</v>
+        <v>7046818</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2202,7 +2217,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på ca 2 meters höjd på en tall.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2216,17 +2231,17 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -2236,7 +2251,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2254,10 +2269,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131067808</v>
+        <v>131067469</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>57064</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,16 +2280,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2282,25 +2297,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465816</v>
+        <v>465770</v>
       </c>
       <c r="R15" t="n">
-        <v>7046818</v>
+        <v>7046758</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2330,14 +2345,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Flög upp.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2348,51 +2373,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131067463</v>
+        <v>131067459</v>
       </c>
       <c r="B16" t="n">
-        <v>80350</v>
+        <v>79245</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2400,21 +2400,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2424,7 +2424,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466198</v>
+        <v>466261</v>
       </c>
       <c r="R16" t="n">
         <v>7046954</v>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2469,12 +2469,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Sälg</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2501,10 +2496,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131067459</v>
+        <v>131067456</v>
       </c>
       <c r="B17" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2539,7 +2534,7 @@
         <v>466261</v>
       </c>
       <c r="R17" t="n">
-        <v>7046954</v>
+        <v>7046745</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2571,7 +2566,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2581,7 +2576,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2608,10 +2603,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131067456</v>
+        <v>131067463</v>
       </c>
       <c r="B18" t="n">
-        <v>79244</v>
+        <v>80351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2619,21 +2614,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2643,10 +2638,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466261</v>
+        <v>466198</v>
       </c>
       <c r="R18" t="n">
-        <v>7046745</v>
+        <v>7046954</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2678,7 +2673,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2688,7 +2683,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2969,10 +2969,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131067457</v>
+        <v>131067025</v>
       </c>
       <c r="B21" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3000,14 +3000,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466188</v>
+        <v>466160</v>
       </c>
       <c r="R21" t="n">
-        <v>7046783</v>
+        <v>7046687</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3037,19 +3037,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>10:44</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3064,44 +3059,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131067464</v>
+        <v>131067457</v>
       </c>
       <c r="B22" t="n">
-        <v>75222</v>
+        <v>79245</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3111,10 +3106,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466197</v>
+        <v>466188</v>
       </c>
       <c r="R22" t="n">
-        <v>7046956</v>
+        <v>7046783</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3146,7 +3141,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3156,12 +3151,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Död sälg</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3188,48 +3178,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131067014</v>
+        <v>131067464</v>
       </c>
       <c r="B23" t="n">
-        <v>79244</v>
+        <v>75223</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465848</v>
+        <v>466197</v>
       </c>
       <c r="R23" t="n">
-        <v>7046818</v>
+        <v>7046956</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3259,14 +3246,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Död sälg</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3275,54 +3272,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131067467</v>
+        <v>131067014</v>
       </c>
       <c r="B24" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,16 +3319,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465982</v>
+        <v>465848</v>
       </c>
       <c r="R24" t="n">
-        <v>7046926</v>
+        <v>7046818</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3387,19 +3361,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:07</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3408,28 +3377,54 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131067765</v>
+        <v>131067467</v>
       </c>
       <c r="B25" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3437,42 +3432,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466021</v>
+        <v>465982</v>
       </c>
       <c r="R25" t="n">
-        <v>7046920</v>
+        <v>7046926</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3502,14 +3489,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Gammalt bohål 40 - 45 mm i diameter. Uthackat i stående död grantickerötad gran på 1,8 meters höjd över marken. På/kring fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3520,48 +3512,23 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131067777</v>
+        <v>131067765</v>
       </c>
       <c r="B26" t="n">
         <v>57884</v>
@@ -3594,7 +3561,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3604,10 +3571,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466291</v>
+        <v>466021</v>
       </c>
       <c r="R26" t="n">
-        <v>7046932</v>
+        <v>7046920</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3644,7 +3611,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Gammalt bohål 40 - 45 mm i diameter. Uthackat i stående död grantickerötad gran på 1,8 meters höjd över marken. På/kring fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3671,9 +3638,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3691,10 +3663,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131067025</v>
+        <v>131067777</v>
       </c>
       <c r="B27" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3702,34 +3674,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466160</v>
+        <v>466291</v>
       </c>
       <c r="R27" t="n">
-        <v>7046687</v>
+        <v>7046932</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3766,7 +3746,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3777,6 +3757,26 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3796,7 +3796,7 @@
         <v>131067820</v>
       </c>
       <c r="B28" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>131067815</v>
       </c>
       <c r="B29" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4688,10 +4688,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131067778</v>
+        <v>131067455</v>
       </c>
       <c r="B35" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4699,42 +4699,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466299</v>
+        <v>466247</v>
       </c>
       <c r="R35" t="n">
-        <v>7046954</v>
+        <v>7046669</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4764,14 +4756,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4782,46 +4779,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131067769</v>
+        <v>131067823</v>
       </c>
       <c r="B36" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4829,31 +4806,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4861,10 +4833,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466118</v>
+        <v>466269</v>
       </c>
       <c r="R36" t="n">
-        <v>7046899</v>
+        <v>7046701</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4899,38 +4871,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4948,10 +4901,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131067466</v>
+        <v>131067462</v>
       </c>
       <c r="B37" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4959,42 +4912,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465976</v>
+        <v>466212</v>
       </c>
       <c r="R37" t="n">
-        <v>7046933</v>
+        <v>7046990</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5026,7 +4971,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5036,12 +4981,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5068,7 +5008,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131067776</v>
+        <v>131067778</v>
       </c>
       <c r="B38" t="n">
         <v>57884</v>
@@ -5111,10 +5051,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466296</v>
+        <v>466299</v>
       </c>
       <c r="R38" t="n">
-        <v>7046956</v>
+        <v>7046954</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5198,10 +5138,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131067455</v>
+        <v>131067769</v>
       </c>
       <c r="B39" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5209,34 +5149,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466247</v>
+        <v>466118</v>
       </c>
       <c r="R39" t="n">
-        <v>7046669</v>
+        <v>7046899</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5266,19 +5214,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>10:26</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>10:26</t>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5289,26 +5232,46 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131067823</v>
+        <v>131067466</v>
       </c>
       <c r="B40" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5316,37 +5279,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466269</v>
+        <v>465976</v>
       </c>
       <c r="R40" t="n">
-        <v>7046701</v>
+        <v>7046933</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5376,45 +5344,54 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131067462</v>
+        <v>131067776</v>
       </c>
       <c r="B41" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5422,34 +5399,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466212</v>
+        <v>466296</v>
       </c>
       <c r="R41" t="n">
-        <v>7046990</v>
+        <v>7046956</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5479,19 +5464,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>11:39</t>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5502,16 +5482,36 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5653,10 +5653,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131067468</v>
+        <v>131067471</v>
       </c>
       <c r="B43" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>465833</v>
+        <v>465684</v>
       </c>
       <c r="R43" t="n">
-        <v>7046793</v>
+        <v>7046838</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5760,10 +5760,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131067471</v>
+        <v>131067017</v>
       </c>
       <c r="B44" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5791,14 +5791,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>465684</v>
+        <v>466015</v>
       </c>
       <c r="R44" t="n">
-        <v>7046838</v>
+        <v>7046893</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5828,19 +5828,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>15:18</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5855,22 +5850,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131067017</v>
+        <v>131067010</v>
       </c>
       <c r="B45" t="n">
-        <v>79244</v>
+        <v>91830</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5878,34 +5873,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466015</v>
+        <v>465776</v>
       </c>
       <c r="R45" t="n">
-        <v>7046893</v>
+        <v>7046851</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5942,7 +5940,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5951,8 +5949,34 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5969,10 +5993,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131067010</v>
+        <v>131067809</v>
       </c>
       <c r="B46" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5980,24 +6004,29 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -6007,10 +6036,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>465776</v>
+        <v>466011</v>
       </c>
       <c r="R46" t="n">
-        <v>7046851</v>
+        <v>7046932</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6047,7 +6076,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6056,7 +6085,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6100,10 +6128,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131067809</v>
+        <v>131067468</v>
       </c>
       <c r="B47" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6111,42 +6139,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>466011</v>
+        <v>465833</v>
       </c>
       <c r="R47" t="n">
-        <v>7046932</v>
+        <v>7046793</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6176,14 +6196,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6194,41 +6219,16 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6238,7 +6238,7 @@
         <v>131067824</v>
       </c>
       <c r="B48" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6461,10 +6461,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131067770</v>
+        <v>131067022</v>
       </c>
       <c r="B50" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6472,31 +6472,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6504,10 +6499,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>466195</v>
+        <v>466123</v>
       </c>
       <c r="R50" t="n">
-        <v>7046876</v>
+        <v>7046774</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6544,7 +6539,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Långväxta bålar på gran i  barrblandskog.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6553,12 +6548,13 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -6571,9 +6567,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6591,10 +6592,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131067022</v>
+        <v>131067770</v>
       </c>
       <c r="B51" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6602,26 +6603,31 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6629,10 +6635,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>466123</v>
+        <v>466195</v>
       </c>
       <c r="R51" t="n">
-        <v>7046774</v>
+        <v>7046876</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6669,7 +6675,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i  barrblandskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6678,13 +6684,12 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -6697,14 +6702,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7125,7 +7125,7 @@
         <v>131067821</v>
       </c>
       <c r="B55" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>131067019</v>
       </c>
       <c r="B56" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
         <v>131067013</v>
       </c>
       <c r="B57" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>131067816</v>
       </c>
       <c r="B58" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7611,10 +7611,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131067819</v>
+        <v>131067771</v>
       </c>
       <c r="B59" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7622,24 +7622,29 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7649,10 +7654,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>466023</v>
+        <v>466198</v>
       </c>
       <c r="R59" t="n">
-        <v>7046926</v>
+        <v>7046862</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7687,13 +7692,17 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7732,10 +7741,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131067016</v>
+        <v>131067819</v>
       </c>
       <c r="B60" t="n">
-        <v>79244</v>
+        <v>91830</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7743,34 +7752,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>466002</v>
+        <v>466023</v>
       </c>
       <c r="R60" t="n">
-        <v>7046855</v>
+        <v>7046926</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7805,19 +7817,35 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7834,10 +7862,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131067771</v>
+        <v>131067016</v>
       </c>
       <c r="B61" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7845,42 +7873,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>466198</v>
+        <v>466002</v>
       </c>
       <c r="R61" t="n">
-        <v>7046862</v>
+        <v>7046855</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7917,7 +7937,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7928,26 +7948,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7967,7 +7967,7 @@
         <v>131067021</v>
       </c>
       <c r="B62" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>131067015</v>
       </c>
       <c r="B63" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>131067817</v>
       </c>
       <c r="B66" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8588,10 +8588,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131067807</v>
+        <v>131067026</v>
       </c>
       <c r="B67" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8599,31 +8599,26 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8631,10 +8626,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>465804</v>
+        <v>466116</v>
       </c>
       <c r="R67" t="n">
-        <v>7046812</v>
+        <v>7046744</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8671,7 +8666,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På bark av tall i barrblandskog.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8680,32 +8675,33 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8723,10 +8719,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131067780</v>
+        <v>131067758</v>
       </c>
       <c r="B68" t="n">
-        <v>57884</v>
+        <v>91810</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8734,29 +8730,28 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -8766,10 +8761,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>466268</v>
+        <v>466220</v>
       </c>
       <c r="R68" t="n">
-        <v>7046893</v>
+        <v>7046897</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8804,17 +8799,13 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8833,9 +8824,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8853,10 +8849,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131067758</v>
+        <v>131067807</v>
       </c>
       <c r="B69" t="n">
-        <v>91809</v>
+        <v>57884</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8864,28 +8860,29 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -8895,10 +8892,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>466220</v>
+        <v>465804</v>
       </c>
       <c r="R69" t="n">
-        <v>7046897</v>
+        <v>7046812</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8933,13 +8930,17 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8960,12 +8961,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8983,10 +8984,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131067026</v>
+        <v>131067780</v>
       </c>
       <c r="B70" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8994,26 +8995,31 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9021,10 +9027,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>466116</v>
+        <v>466268</v>
       </c>
       <c r="R70" t="n">
-        <v>7046744</v>
+        <v>7046893</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9061,7 +9067,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På bark av tall i barrblandskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9070,33 +9076,27 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9114,10 +9114,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131066994</v>
+        <v>131067472</v>
       </c>
       <c r="B71" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9125,42 +9125,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>466211</v>
+        <v>465661</v>
       </c>
       <c r="R71" t="n">
-        <v>7046715</v>
+        <v>7046738</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9190,14 +9182,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran med spår av kådaflöde som står på sluttningen av en mindre kulle.</t>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9208,51 +9205,26 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131067773</v>
+        <v>131067024</v>
       </c>
       <c r="B72" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9260,31 +9232,26 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9292,10 +9259,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>466253</v>
+        <v>466097</v>
       </c>
       <c r="R72" t="n">
-        <v>7046994</v>
+        <v>7046728</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9332,7 +9299,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9341,12 +9308,13 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
@@ -9359,9 +9327,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9379,10 +9352,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131067472</v>
+        <v>131067029</v>
       </c>
       <c r="B73" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9408,16 +9381,19 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>465661</v>
+        <v>466255</v>
       </c>
       <c r="R73" t="n">
-        <v>7046738</v>
+        <v>7046672</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9447,19 +9423,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>15:28</t>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9468,28 +9439,54 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131067024</v>
+        <v>131067814</v>
       </c>
       <c r="B74" t="n">
-        <v>79244</v>
+        <v>91830</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9497,26 +9494,26 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9524,10 +9521,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>466097</v>
+        <v>465657</v>
       </c>
       <c r="R74" t="n">
-        <v>7046728</v>
+        <v>7046731</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9562,11 +9559,6 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På gran i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -9579,7 +9571,7 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
@@ -9592,14 +9584,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9617,10 +9604,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131067029</v>
+        <v>131067822</v>
       </c>
       <c r="B75" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9655,10 +9642,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>466255</v>
+        <v>466268</v>
       </c>
       <c r="R75" t="n">
-        <v>7046672</v>
+        <v>7046889</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9693,11 +9680,6 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -9711,26 +9693,6 @@
       <c r="AH75" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9748,10 +9710,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131067814</v>
+        <v>131067018</v>
       </c>
       <c r="B76" t="n">
-        <v>91829</v>
+        <v>79245</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9759,26 +9721,26 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9786,10 +9748,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>465657</v>
+        <v>466067</v>
       </c>
       <c r="R76" t="n">
-        <v>7046731</v>
+        <v>7046910</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9824,6 +9786,11 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>På flera granar i granskog.</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -9849,9 +9816,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9869,10 +9841,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131067822</v>
+        <v>131066994</v>
       </c>
       <c r="B77" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9880,26 +9852,31 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9907,10 +9884,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>466268</v>
+        <v>466211</v>
       </c>
       <c r="R77" t="n">
-        <v>7046889</v>
+        <v>7046715</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9945,19 +9922,43 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på stambasen av en gran med spår av kådaflöde som står på sluttningen av en mindre kulle.</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9975,10 +9976,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131067018</v>
+        <v>131067773</v>
       </c>
       <c r="B78" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9986,26 +9987,31 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -10013,10 +10019,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>466067</v>
+        <v>466253</v>
       </c>
       <c r="R78" t="n">
-        <v>7046910</v>
+        <v>7046994</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10053,7 +10059,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På flera granar i granskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10062,7 +10068,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -10081,14 +10086,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10106,10 +10106,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131067011</v>
+        <v>131067811</v>
       </c>
       <c r="B79" t="n">
-        <v>79244</v>
+        <v>58043</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10117,37 +10117,50 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>465794</v>
+        <v>465799</v>
       </c>
       <c r="R79" t="n">
-        <v>7046853</v>
+        <v>7046814</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10184,7 +10197,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På flera granar i granskog.</t>
+          <t>Synobservation av 2 st födosökande talltitor i äldre granskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10193,33 +10206,12 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10237,10 +10229,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131066995</v>
+        <v>131067011</v>
       </c>
       <c r="B80" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10248,31 +10240,26 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -10280,10 +10267,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>466224</v>
+        <v>465794</v>
       </c>
       <c r="R80" t="n">
-        <v>7046722</v>
+        <v>7046853</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10320,7 +10307,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran i granskog.</t>
+          <t>På flera granar i granskog.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10329,6 +10316,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -10349,12 +10337,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10372,10 +10360,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131067811</v>
+        <v>131066995</v>
       </c>
       <c r="B81" t="n">
-        <v>58043</v>
+        <v>57884</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10383,50 +10371,42 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>465799</v>
+        <v>466224</v>
       </c>
       <c r="R81" t="n">
-        <v>7046814</v>
+        <v>7046722</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10463,7 +10443,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Synobservation av 2 st födosökande talltitor i äldre granskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran i granskog.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10478,6 +10458,26 @@
       <c r="AH81" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>

--- a/artfynd/A 41290-2025 artfynd.xlsx
+++ b/artfynd/A 41290-2025 artfynd.xlsx
@@ -1529,10 +1529,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131067028</v>
+        <v>131067812</v>
       </c>
       <c r="B9" t="n">
-        <v>79245</v>
+        <v>80351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,34 +1540,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466204</v>
+        <v>466199</v>
       </c>
       <c r="R9" t="n">
-        <v>7046724</v>
+        <v>7046948</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1604,7 +1607,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Skrovellav på gran!</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,8 +1616,34 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1631,7 +1660,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131067027</v>
+        <v>131067028</v>
       </c>
       <c r="B10" t="n">
         <v>79245</v>
@@ -1666,10 +1695,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466140</v>
+        <v>466204</v>
       </c>
       <c r="R10" t="n">
-        <v>7046777</v>
+        <v>7046724</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1733,10 +1762,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131067812</v>
+        <v>131067027</v>
       </c>
       <c r="B11" t="n">
-        <v>80351</v>
+        <v>79245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1744,37 +1773,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466199</v>
+        <v>466140</v>
       </c>
       <c r="R11" t="n">
-        <v>7046948</v>
+        <v>7046777</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1811,7 +1837,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Skrovellav på gran!</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,34 +1846,8 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -2969,10 +2969,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131067025</v>
+        <v>131067765</v>
       </c>
       <c r="B21" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2980,34 +2980,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466160</v>
+        <v>466021</v>
       </c>
       <c r="R21" t="n">
-        <v>7046687</v>
+        <v>7046920</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3044,7 +3052,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Gammalt bohål 40 - 45 mm i diameter. Uthackat i stående död grantickerötad gran på 1,8 meters höjd över marken. På/kring fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3055,6 +3063,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3071,10 +3104,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131067457</v>
+        <v>131067777</v>
       </c>
       <c r="B22" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3082,34 +3115,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466188</v>
+        <v>466291</v>
       </c>
       <c r="R22" t="n">
-        <v>7046783</v>
+        <v>7046932</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3139,19 +3180,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>10:44</t>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3162,61 +3198,81 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131067464</v>
+        <v>131067025</v>
       </c>
       <c r="B23" t="n">
-        <v>75223</v>
+        <v>79245</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466197</v>
+        <v>466160</v>
       </c>
       <c r="R23" t="n">
-        <v>7046956</v>
+        <v>7046687</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3246,24 +3302,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Död sälg</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3278,19 +3324,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131067014</v>
+        <v>131067457</v>
       </c>
       <c r="B24" t="n">
         <v>79245</v>
@@ -3319,19 +3365,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465848</v>
+        <v>466188</v>
       </c>
       <c r="R24" t="n">
-        <v>7046818</v>
+        <v>7046783</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3361,14 +3404,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På gran i granskog.</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3377,76 +3425,50 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131067467</v>
+        <v>131067464</v>
       </c>
       <c r="B25" t="n">
-        <v>79245</v>
+        <v>75223</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3456,10 +3478,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465982</v>
+        <v>466197</v>
       </c>
       <c r="R25" t="n">
-        <v>7046926</v>
+        <v>7046956</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3491,7 +3513,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3501,7 +3523,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Död sälg</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3528,10 +3555,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131067765</v>
+        <v>131067014</v>
       </c>
       <c r="B26" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3539,31 +3566,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3571,10 +3593,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466021</v>
+        <v>465848</v>
       </c>
       <c r="R26" t="n">
-        <v>7046920</v>
+        <v>7046818</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3611,7 +3633,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Gammalt bohål 40 - 45 mm i diameter. Uthackat i stående död grantickerötad gran på 1,8 meters höjd över marken. På/kring fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3620,6 +3642,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3640,12 +3663,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3663,10 +3686,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131067777</v>
+        <v>131067467</v>
       </c>
       <c r="B27" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3674,42 +3697,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466291</v>
+        <v>465982</v>
       </c>
       <c r="R27" t="n">
-        <v>7046932</v>
+        <v>7046926</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3739,14 +3754,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3757,36 +3777,16 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -4688,10 +4688,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131067455</v>
+        <v>131067778</v>
       </c>
       <c r="B35" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4699,34 +4699,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466247</v>
+        <v>466299</v>
       </c>
       <c r="R35" t="n">
-        <v>7046669</v>
+        <v>7046954</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4756,19 +4764,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>10:26</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>10:26</t>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4779,26 +4782,46 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131067823</v>
+        <v>131067769</v>
       </c>
       <c r="B36" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4806,26 +4829,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4833,10 +4861,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466269</v>
+        <v>466118</v>
       </c>
       <c r="R36" t="n">
-        <v>7046701</v>
+        <v>7046899</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4871,19 +4899,38 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4901,10 +4948,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131067462</v>
+        <v>131067466</v>
       </c>
       <c r="B37" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4912,34 +4959,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466212</v>
+        <v>465976</v>
       </c>
       <c r="R37" t="n">
-        <v>7046990</v>
+        <v>7046933</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4971,7 +5026,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4981,7 +5036,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5008,7 +5068,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131067778</v>
+        <v>131067776</v>
       </c>
       <c r="B38" t="n">
         <v>57884</v>
@@ -5051,10 +5111,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466299</v>
+        <v>466296</v>
       </c>
       <c r="R38" t="n">
-        <v>7046954</v>
+        <v>7046956</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5138,10 +5198,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131067769</v>
+        <v>131067455</v>
       </c>
       <c r="B39" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5149,42 +5209,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466118</v>
+        <v>466247</v>
       </c>
       <c r="R39" t="n">
-        <v>7046899</v>
+        <v>7046669</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5214,14 +5266,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5232,46 +5289,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131067466</v>
+        <v>131067823</v>
       </c>
       <c r="B40" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5279,42 +5316,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465976</v>
+        <v>466269</v>
       </c>
       <c r="R40" t="n">
-        <v>7046933</v>
+        <v>7046701</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5344,54 +5376,45 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131067776</v>
+        <v>131067462</v>
       </c>
       <c r="B41" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5399,42 +5422,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466296</v>
+        <v>466212</v>
       </c>
       <c r="R41" t="n">
-        <v>7046956</v>
+        <v>7046990</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5464,14 +5479,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5482,36 +5502,16 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5653,7 +5653,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131067471</v>
+        <v>131067468</v>
       </c>
       <c r="B43" t="n">
         <v>79245</v>
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>465684</v>
+        <v>465833</v>
       </c>
       <c r="R43" t="n">
-        <v>7046838</v>
+        <v>7046793</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5760,7 +5760,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131067017</v>
+        <v>131067471</v>
       </c>
       <c r="B44" t="n">
         <v>79245</v>
@@ -5791,14 +5791,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466015</v>
+        <v>465684</v>
       </c>
       <c r="R44" t="n">
-        <v>7046893</v>
+        <v>7046838</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5828,14 +5828,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5850,22 +5855,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131067010</v>
+        <v>131067017</v>
       </c>
       <c r="B45" t="n">
-        <v>91830</v>
+        <v>79245</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5873,37 +5878,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>465776</v>
+        <v>466015</v>
       </c>
       <c r="R45" t="n">
-        <v>7046851</v>
+        <v>7046893</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5940,7 +5942,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5949,34 +5951,8 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5993,10 +5969,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131067809</v>
+        <v>131067010</v>
       </c>
       <c r="B46" t="n">
-        <v>57884</v>
+        <v>91830</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6004,29 +5980,24 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -6036,10 +6007,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466011</v>
+        <v>465776</v>
       </c>
       <c r="R46" t="n">
-        <v>7046932</v>
+        <v>7046851</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6076,7 +6047,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6085,6 +6056,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6128,10 +6100,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131067468</v>
+        <v>131067809</v>
       </c>
       <c r="B47" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6139,34 +6111,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>465833</v>
+        <v>466011</v>
       </c>
       <c r="R47" t="n">
-        <v>7046793</v>
+        <v>7046932</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6196,19 +6176,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:48</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6219,16 +6194,41 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -7964,10 +7964,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131067021</v>
+        <v>131067774</v>
       </c>
       <c r="B62" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7975,26 +7975,31 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8002,10 +8007,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>466160</v>
+        <v>466303</v>
       </c>
       <c r="R62" t="n">
-        <v>7046831</v>
+        <v>7047009</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8042,7 +8047,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8051,7 +8056,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -8072,12 +8076,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8095,10 +8099,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131067015</v>
+        <v>131067772</v>
       </c>
       <c r="B63" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8106,34 +8110,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>465958</v>
+        <v>466208</v>
       </c>
       <c r="R63" t="n">
-        <v>7046711</v>
+        <v>7046922</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8170,7 +8182,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8181,6 +8193,31 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -8197,10 +8234,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131067774</v>
+        <v>131067021</v>
       </c>
       <c r="B64" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8208,31 +8245,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8240,10 +8272,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>466303</v>
+        <v>466160</v>
       </c>
       <c r="R64" t="n">
-        <v>7047009</v>
+        <v>7046831</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8280,7 +8312,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8289,6 +8321,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -8309,12 +8342,12 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8332,10 +8365,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131067772</v>
+        <v>131067015</v>
       </c>
       <c r="B65" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8343,42 +8376,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>466208</v>
+        <v>465958</v>
       </c>
       <c r="R65" t="n">
-        <v>7046922</v>
+        <v>7046711</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8415,7 +8440,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8426,31 +8451,6 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -10106,10 +10106,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131067811</v>
+        <v>131067011</v>
       </c>
       <c r="B79" t="n">
-        <v>58043</v>
+        <v>79245</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10117,50 +10117,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>465799</v>
+        <v>465794</v>
       </c>
       <c r="R79" t="n">
-        <v>7046814</v>
+        <v>7046853</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10197,7 +10184,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Synobservation av 2 st födosökande talltitor i äldre granskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
+          <t>På flera granar i granskog.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10206,12 +10193,33 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10229,10 +10237,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131067011</v>
+        <v>131066995</v>
       </c>
       <c r="B80" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10240,26 +10248,31 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -10267,10 +10280,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>465794</v>
+        <v>466224</v>
       </c>
       <c r="R80" t="n">
-        <v>7046853</v>
+        <v>7046722</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10307,7 +10320,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På flera granar i granskog.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran i granskog.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10316,7 +10329,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -10337,12 +10349,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10360,10 +10372,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131066995</v>
+        <v>131067811</v>
       </c>
       <c r="B81" t="n">
-        <v>57884</v>
+        <v>58043</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10371,42 +10383,50 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>466224</v>
+        <v>465799</v>
       </c>
       <c r="R81" t="n">
-        <v>7046722</v>
+        <v>7046814</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10443,7 +10463,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran i granskog.</t>
+          <t>Synobservation av 2 st födosökande talltitor i äldre granskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10458,26 +10478,6 @@
       <c r="AH81" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>

--- a/artfynd/A 41290-2025 artfynd.xlsx
+++ b/artfynd/A 41290-2025 artfynd.xlsx
@@ -1529,10 +1529,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131067812</v>
+        <v>131067028</v>
       </c>
       <c r="B9" t="n">
-        <v>80351</v>
+        <v>79245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,37 +1540,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466199</v>
+        <v>466204</v>
       </c>
       <c r="R9" t="n">
-        <v>7046948</v>
+        <v>7046724</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1607,7 +1604,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Skrovellav på gran!</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1616,34 +1613,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1660,7 +1631,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131067028</v>
+        <v>131067027</v>
       </c>
       <c r="B10" t="n">
         <v>79245</v>
@@ -1695,10 +1666,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466204</v>
+        <v>466140</v>
       </c>
       <c r="R10" t="n">
-        <v>7046724</v>
+        <v>7046777</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1762,10 +1733,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131067027</v>
+        <v>131067812</v>
       </c>
       <c r="B11" t="n">
-        <v>79245</v>
+        <v>80351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,34 +1744,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466140</v>
+        <v>466199</v>
       </c>
       <c r="R11" t="n">
-        <v>7046777</v>
+        <v>7046948</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1837,7 +1811,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Skrovellav på gran!</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1846,8 +1820,34 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -2389,10 +2389,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131067459</v>
+        <v>131067463</v>
       </c>
       <c r="B16" t="n">
-        <v>79245</v>
+        <v>80351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2400,21 +2400,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2424,7 +2424,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466261</v>
+        <v>466198</v>
       </c>
       <c r="R16" t="n">
         <v>7046954</v>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2469,7 +2469,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2496,7 +2501,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131067456</v>
+        <v>131067459</v>
       </c>
       <c r="B17" t="n">
         <v>79245</v>
@@ -2534,7 +2539,7 @@
         <v>466261</v>
       </c>
       <c r="R17" t="n">
-        <v>7046745</v>
+        <v>7046954</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2566,7 +2571,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2576,7 +2581,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2603,10 +2608,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131067463</v>
+        <v>131067456</v>
       </c>
       <c r="B18" t="n">
-        <v>80351</v>
+        <v>79245</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2614,21 +2619,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2638,10 +2643,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466198</v>
+        <v>466261</v>
       </c>
       <c r="R18" t="n">
-        <v>7046954</v>
+        <v>7046745</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2673,7 +2678,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2683,12 +2688,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Sälg</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -7964,10 +7964,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131067774</v>
+        <v>131067021</v>
       </c>
       <c r="B62" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7975,31 +7975,26 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8007,10 +8002,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>466303</v>
+        <v>466160</v>
       </c>
       <c r="R62" t="n">
-        <v>7047009</v>
+        <v>7046831</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8047,7 +8042,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8056,6 +8051,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -8076,12 +8072,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8099,10 +8095,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131067772</v>
+        <v>131067015</v>
       </c>
       <c r="B63" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8110,42 +8106,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>466208</v>
+        <v>465958</v>
       </c>
       <c r="R63" t="n">
-        <v>7046922</v>
+        <v>7046711</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8182,7 +8170,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8193,31 +8181,6 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -8234,10 +8197,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131067021</v>
+        <v>131067774</v>
       </c>
       <c r="B64" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8245,26 +8208,31 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8272,10 +8240,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>466160</v>
+        <v>466303</v>
       </c>
       <c r="R64" t="n">
-        <v>7046831</v>
+        <v>7047009</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8312,7 +8280,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8321,7 +8289,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -8342,12 +8309,12 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8365,10 +8332,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131067015</v>
+        <v>131067772</v>
       </c>
       <c r="B65" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8376,34 +8343,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>465958</v>
+        <v>466208</v>
       </c>
       <c r="R65" t="n">
-        <v>7046711</v>
+        <v>7046922</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8440,7 +8415,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8451,6 +8426,31 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8588,10 +8588,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131067026</v>
+        <v>131067758</v>
       </c>
       <c r="B67" t="n">
-        <v>79245</v>
+        <v>91810</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8599,26 +8599,30 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8626,10 +8630,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>466116</v>
+        <v>466220</v>
       </c>
       <c r="R67" t="n">
-        <v>7046744</v>
+        <v>7046897</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8664,11 +8668,6 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På bark av tall i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8681,27 +8680,27 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8719,10 +8718,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131067758</v>
+        <v>131067026</v>
       </c>
       <c r="B68" t="n">
-        <v>91810</v>
+        <v>79245</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8730,30 +8729,26 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8761,10 +8756,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>466220</v>
+        <v>466116</v>
       </c>
       <c r="R68" t="n">
-        <v>7046897</v>
+        <v>7046744</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8799,6 +8794,11 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På bark av tall i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8811,27 +8811,27 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>

--- a/artfynd/A 41290-2025 artfynd.xlsx
+++ b/artfynd/A 41290-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131067818</v>
       </c>
       <c r="B2" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131067020</v>
+        <v>131067023</v>
       </c>
       <c r="B4" t="n">
         <v>79245</v>
@@ -948,16 +948,19 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466180</v>
+        <v>466072</v>
       </c>
       <c r="R4" t="n">
-        <v>7046800</v>
+        <v>7046758</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +997,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,8 +1006,34 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1021,7 +1050,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131067470</v>
+        <v>131067020</v>
       </c>
       <c r="B5" t="n">
         <v>79245</v>
@@ -1052,14 +1081,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465713</v>
+        <v>466180</v>
       </c>
       <c r="R5" t="n">
-        <v>7046828</v>
+        <v>7046800</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,24 +1118,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Död gran</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,19 +1140,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131067023</v>
+        <v>131067470</v>
       </c>
       <c r="B6" t="n">
         <v>79245</v>
@@ -1162,19 +1181,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466072</v>
+        <v>465713</v>
       </c>
       <c r="R6" t="n">
-        <v>7046758</v>
+        <v>7046828</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,14 +1220,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Död gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,44 +1246,18 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -2389,10 +2389,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131067463</v>
+        <v>131067459</v>
       </c>
       <c r="B16" t="n">
-        <v>80351</v>
+        <v>79245</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2400,21 +2400,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2424,7 +2424,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466198</v>
+        <v>466261</v>
       </c>
       <c r="R16" t="n">
         <v>7046954</v>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2469,12 +2469,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Sälg</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2501,7 +2496,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131067459</v>
+        <v>131067456</v>
       </c>
       <c r="B17" t="n">
         <v>79245</v>
@@ -2539,7 +2534,7 @@
         <v>466261</v>
       </c>
       <c r="R17" t="n">
-        <v>7046954</v>
+        <v>7046745</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2571,7 +2566,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2581,7 +2576,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2608,10 +2603,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131067456</v>
+        <v>131067463</v>
       </c>
       <c r="B18" t="n">
-        <v>79245</v>
+        <v>80351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2619,21 +2614,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2643,10 +2638,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466261</v>
+        <v>466198</v>
       </c>
       <c r="R18" t="n">
-        <v>7046745</v>
+        <v>7046954</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2678,7 +2673,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2688,7 +2683,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2969,10 +2969,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131067765</v>
+        <v>131067025</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2980,42 +2980,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466021</v>
+        <v>466160</v>
       </c>
       <c r="R21" t="n">
-        <v>7046920</v>
+        <v>7046687</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3052,7 +3044,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Gammalt bohål 40 - 45 mm i diameter. Uthackat i stående död grantickerötad gran på 1,8 meters höjd över marken. På/kring fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3063,31 +3055,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3104,10 +3071,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131067777</v>
+        <v>131067457</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3115,42 +3082,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466291</v>
+        <v>466188</v>
       </c>
       <c r="R22" t="n">
-        <v>7046932</v>
+        <v>7046783</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3180,14 +3139,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3198,81 +3162,61 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131067025</v>
+        <v>131067464</v>
       </c>
       <c r="B23" t="n">
-        <v>79245</v>
+        <v>75223</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466160</v>
+        <v>466197</v>
       </c>
       <c r="R23" t="n">
-        <v>7046687</v>
+        <v>7046956</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3302,14 +3246,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Död sälg</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3324,19 +3278,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131067457</v>
+        <v>131067014</v>
       </c>
       <c r="B24" t="n">
         <v>79245</v>
@@ -3365,16 +3319,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466188</v>
+        <v>465848</v>
       </c>
       <c r="R24" t="n">
-        <v>7046783</v>
+        <v>7046818</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3404,19 +3361,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:44</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3425,50 +3377,76 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131067464</v>
+        <v>131067467</v>
       </c>
       <c r="B25" t="n">
-        <v>75223</v>
+        <v>79245</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3478,10 +3456,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466197</v>
+        <v>465982</v>
       </c>
       <c r="R25" t="n">
-        <v>7046956</v>
+        <v>7046926</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3513,7 +3491,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3523,12 +3501,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Död sälg</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3555,10 +3528,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131067014</v>
+        <v>131067765</v>
       </c>
       <c r="B26" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3566,26 +3539,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3593,10 +3571,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465848</v>
+        <v>466021</v>
       </c>
       <c r="R26" t="n">
-        <v>7046818</v>
+        <v>7046920</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3633,7 +3611,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Gammalt bohål 40 - 45 mm i diameter. Uthackat i stående död grantickerötad gran på 1,8 meters höjd över marken. På/kring fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3642,7 +3620,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3663,12 +3640,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3686,10 +3663,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131067467</v>
+        <v>131067777</v>
       </c>
       <c r="B27" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3697,34 +3674,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>465982</v>
+        <v>466291</v>
       </c>
       <c r="R27" t="n">
-        <v>7046926</v>
+        <v>7046932</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3754,19 +3739,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:07</t>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3777,26 +3757,46 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131067820</v>
+        <v>131067775</v>
       </c>
       <c r="B28" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3804,34 +3804,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3839,10 +3836,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466201</v>
+        <v>466299</v>
       </c>
       <c r="R28" t="n">
-        <v>7046958</v>
+        <v>7047010</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3879,7 +3876,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav här!</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3888,7 +3885,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3907,14 +3903,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3932,10 +3923,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131067815</v>
+        <v>131066990</v>
       </c>
       <c r="B29" t="n">
-        <v>91830</v>
+        <v>57884</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3943,24 +3934,29 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3970,10 +3966,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466248</v>
+        <v>466169</v>
       </c>
       <c r="R29" t="n">
-        <v>7046866</v>
+        <v>7046684</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4008,13 +4004,17 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4033,9 +4033,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4053,7 +4058,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131067775</v>
+        <v>131067460</v>
       </c>
       <c r="B30" t="n">
         <v>57884</v>
@@ -4092,14 +4097,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466299</v>
+        <v>466264</v>
       </c>
       <c r="R30" t="n">
-        <v>7047010</v>
+        <v>7046965</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4129,14 +4134,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4147,43 +4162,23 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131066990</v>
+        <v>131067767</v>
       </c>
       <c r="B31" t="n">
         <v>57884</v>
@@ -4226,10 +4221,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466169</v>
+        <v>466140</v>
       </c>
       <c r="R31" t="n">
-        <v>7046684</v>
+        <v>7046909</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4266,7 +4261,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack, äldre, på tall.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4280,27 +4275,22 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4318,7 +4308,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131067460</v>
+        <v>131067465</v>
       </c>
       <c r="B32" t="n">
         <v>57884</v>
@@ -4351,7 +4341,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4361,10 +4351,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466264</v>
+        <v>466152</v>
       </c>
       <c r="R32" t="n">
-        <v>7046965</v>
+        <v>7046928</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4396,7 +4386,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4406,12 +4396,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4438,10 +4428,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131067767</v>
+        <v>131067820</v>
       </c>
       <c r="B33" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4449,31 +4439,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4481,10 +4474,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466140</v>
+        <v>466201</v>
       </c>
       <c r="R33" t="n">
-        <v>7046909</v>
+        <v>7046958</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4521,7 +4514,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på tall.</t>
+          <t>Rikligt med garnlav här!</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4530,27 +4523,33 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4568,10 +4567,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131067465</v>
+        <v>131067815</v>
       </c>
       <c r="B34" t="n">
-        <v>57884</v>
+        <v>91833</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4579,42 +4578,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466152</v>
+        <v>466248</v>
       </c>
       <c r="R34" t="n">
-        <v>7046928</v>
+        <v>7046866</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4644,44 +4638,50 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre och färska ringhack</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -5972,7 +5972,7 @@
         <v>131067010</v>
       </c>
       <c r="B46" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6987,10 +6987,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131067004</v>
+        <v>131067821</v>
       </c>
       <c r="B54" t="n">
-        <v>57881</v>
+        <v>79245</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6998,31 +6998,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7030,10 +7025,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>465997</v>
+        <v>466212</v>
       </c>
       <c r="R54" t="n">
-        <v>7046830</v>
+        <v>7046860</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7068,43 +7063,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i en gran med sockel.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7122,7 +7093,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131067821</v>
+        <v>131067019</v>
       </c>
       <c r="B55" t="n">
         <v>79245</v>
@@ -7160,10 +7131,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>466212</v>
+        <v>466214</v>
       </c>
       <c r="R55" t="n">
-        <v>7046860</v>
+        <v>7046881</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7198,6 +7169,11 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -7211,6 +7187,26 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7228,7 +7224,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131067019</v>
+        <v>131067013</v>
       </c>
       <c r="B56" t="n">
         <v>79245</v>
@@ -7266,10 +7262,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>466214</v>
+        <v>465836</v>
       </c>
       <c r="R56" t="n">
-        <v>7046881</v>
+        <v>7046836</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7306,7 +7302,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Långväxta bålar på gran i en lucka.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7359,10 +7355,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131067013</v>
+        <v>131067816</v>
       </c>
       <c r="B57" t="n">
-        <v>79245</v>
+        <v>91833</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7370,26 +7366,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7397,10 +7393,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>465836</v>
+        <v>466283</v>
       </c>
       <c r="R57" t="n">
-        <v>7046836</v>
+        <v>7046884</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7435,11 +7431,6 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran i en lucka.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7465,14 +7456,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7490,10 +7476,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131067816</v>
+        <v>131067004</v>
       </c>
       <c r="B58" t="n">
-        <v>91830</v>
+        <v>57881</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7501,24 +7487,29 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -7528,10 +7519,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>466283</v>
+        <v>465997</v>
       </c>
       <c r="R58" t="n">
-        <v>7046884</v>
+        <v>7046830</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7566,13 +7557,17 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i en gran med sockel.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7591,9 +7586,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7611,10 +7611,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131067771</v>
+        <v>131067819</v>
       </c>
       <c r="B59" t="n">
-        <v>57884</v>
+        <v>91833</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7622,29 +7622,24 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7654,10 +7649,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>466198</v>
+        <v>466023</v>
       </c>
       <c r="R59" t="n">
-        <v>7046862</v>
+        <v>7046926</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7692,17 +7687,13 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7741,10 +7732,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131067819</v>
+        <v>131067016</v>
       </c>
       <c r="B60" t="n">
-        <v>91830</v>
+        <v>79245</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7752,37 +7743,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>466023</v>
+        <v>466002</v>
       </c>
       <c r="R60" t="n">
-        <v>7046926</v>
+        <v>7046855</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7817,35 +7805,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7862,10 +7834,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131067016</v>
+        <v>131067771</v>
       </c>
       <c r="B61" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7873,34 +7845,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>466002</v>
+        <v>466198</v>
       </c>
       <c r="R61" t="n">
-        <v>7046855</v>
+        <v>7046862</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7937,7 +7917,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7948,6 +7928,26 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -8470,7 +8470,7 @@
         <v>131067817</v>
       </c>
       <c r="B66" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8588,10 +8588,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131067758</v>
+        <v>131067807</v>
       </c>
       <c r="B67" t="n">
-        <v>91810</v>
+        <v>57884</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8599,28 +8599,29 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -8630,10 +8631,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>466220</v>
+        <v>465804</v>
       </c>
       <c r="R67" t="n">
-        <v>7046897</v>
+        <v>7046812</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8668,13 +8669,17 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8695,12 +8700,12 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8718,10 +8723,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131067026</v>
+        <v>131067780</v>
       </c>
       <c r="B68" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8729,26 +8734,31 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8756,10 +8766,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>466116</v>
+        <v>466268</v>
       </c>
       <c r="R68" t="n">
-        <v>7046744</v>
+        <v>7046893</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8796,7 +8806,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På bark av tall i barrblandskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8805,33 +8815,27 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8849,10 +8853,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131067807</v>
+        <v>131067758</v>
       </c>
       <c r="B69" t="n">
-        <v>57884</v>
+        <v>91813</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8860,29 +8864,28 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -8892,10 +8895,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>465804</v>
+        <v>466220</v>
       </c>
       <c r="R69" t="n">
-        <v>7046812</v>
+        <v>7046897</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8930,17 +8933,13 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8961,12 +8960,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8984,10 +8983,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131067780</v>
+        <v>131067026</v>
       </c>
       <c r="B70" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8995,31 +8994,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9027,10 +9021,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>466268</v>
+        <v>466116</v>
       </c>
       <c r="R70" t="n">
-        <v>7046893</v>
+        <v>7046744</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9067,7 +9061,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På bark av tall i barrblandskog.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9076,27 +9070,33 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9486,7 +9486,7 @@
         <v>131067814</v>
       </c>
       <c r="B74" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 41290-2025 artfynd.xlsx
+++ b/artfynd/A 41290-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131067818</v>
       </c>
       <c r="B2" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131067023</v>
+        <v>131066991</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,26 +930,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -957,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466072</v>
+        <v>466192</v>
       </c>
       <c r="R4" t="n">
-        <v>7046758</v>
+        <v>7046678</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,7 +1002,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, enstaka på en gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,13 +1011,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1027,12 +1031,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1050,10 +1054,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131067020</v>
+        <v>131067779</v>
       </c>
       <c r="B5" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1061,34 +1065,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466180</v>
+        <v>466288</v>
       </c>
       <c r="R5" t="n">
-        <v>7046800</v>
+        <v>7046865</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,7 +1137,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,6 +1148,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1152,10 +1184,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131067470</v>
+        <v>131067020</v>
       </c>
       <c r="B6" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,14 +1215,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465713</v>
+        <v>466180</v>
       </c>
       <c r="R6" t="n">
-        <v>7046828</v>
+        <v>7046800</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,24 +1252,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Död gran</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,22 +1274,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131066991</v>
+        <v>131067470</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,42 +1297,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466192</v>
+        <v>465713</v>
       </c>
       <c r="R7" t="n">
-        <v>7046678</v>
+        <v>7046828</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,14 +1354,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på en gran.</t>
+          <t>Död gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,51 +1382,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131067779</v>
+        <v>131067023</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1410,31 +1409,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1442,10 +1436,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466288</v>
+        <v>466072</v>
       </c>
       <c r="R8" t="n">
-        <v>7046865</v>
+        <v>7046758</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1482,7 +1476,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,12 +1485,13 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1509,9 +1504,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1532,7 +1532,7 @@
         <v>131067028</v>
       </c>
       <c r="B9" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>131067027</v>
       </c>
       <c r="B10" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>131067812</v>
       </c>
       <c r="B11" t="n">
-        <v>80351</v>
+        <v>80352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131066988</v>
+        <v>131067469</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>57064</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,16 +1875,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1892,25 +1892,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465681</v>
+        <v>465770</v>
       </c>
       <c r="R12" t="n">
-        <v>7046766</v>
+        <v>7046758</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,14 +1940,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka på stambasen av en gran i granskog.</t>
+          <t>Flög upp.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1958,48 +1968,23 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131066992</v>
+        <v>131066988</v>
       </c>
       <c r="B13" t="n">
         <v>57884</v>
@@ -2032,7 +2017,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2042,10 +2027,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466171</v>
+        <v>465681</v>
       </c>
       <c r="R13" t="n">
-        <v>7046705</v>
+        <v>7046766</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2082,7 +2067,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på ca 2 meters höjd på en tall.</t>
+          <t>Ringhack, färska, enstaka på stambasen av en gran i granskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2096,17 +2081,17 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -2116,7 +2101,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2134,7 +2119,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131067808</v>
+        <v>131066992</v>
       </c>
       <c r="B14" t="n">
         <v>57884</v>
@@ -2177,10 +2162,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465816</v>
+        <v>466171</v>
       </c>
       <c r="R14" t="n">
-        <v>7046818</v>
+        <v>7046705</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2217,7 +2202,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, äldre, på ca 2 meters höjd på en tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2231,17 +2216,17 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -2251,7 +2236,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2269,10 +2254,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131067469</v>
+        <v>131067808</v>
       </c>
       <c r="B15" t="n">
-        <v>57064</v>
+        <v>57884</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2280,16 +2265,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2297,25 +2282,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465770</v>
+        <v>465816</v>
       </c>
       <c r="R15" t="n">
-        <v>7046758</v>
+        <v>7046818</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2345,24 +2330,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Flög upp.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2373,61 +2348,98 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131067459</v>
+        <v>131067003</v>
       </c>
       <c r="B16" t="n">
-        <v>79245</v>
+        <v>57073</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466261</v>
+        <v>466180</v>
       </c>
       <c r="R16" t="n">
-        <v>7046954</v>
+        <v>7046822</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2457,19 +2469,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:07</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket under en tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2480,26 +2487,31 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131067456</v>
+        <v>131067459</v>
       </c>
       <c r="B17" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2534,7 +2546,7 @@
         <v>466261</v>
       </c>
       <c r="R17" t="n">
-        <v>7046745</v>
+        <v>7046954</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2566,7 +2578,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2576,7 +2588,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2603,10 +2615,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131067463</v>
+        <v>131067456</v>
       </c>
       <c r="B18" t="n">
-        <v>80351</v>
+        <v>79246</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2614,21 +2626,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2638,10 +2650,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466198</v>
+        <v>466261</v>
       </c>
       <c r="R18" t="n">
-        <v>7046954</v>
+        <v>7046745</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2673,7 +2685,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2683,12 +2695,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Sälg</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2715,57 +2722,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131067003</v>
+        <v>131067463</v>
       </c>
       <c r="B19" t="n">
-        <v>57073</v>
+        <v>80352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466180</v>
+        <v>466198</v>
       </c>
       <c r="R19" t="n">
-        <v>7046822</v>
+        <v>7046954</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2795,14 +2790,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket under en tall.</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2813,21 +2818,16 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2972,7 +2972,7 @@
         <v>131067025</v>
       </c>
       <c r="B21" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>131067457</v>
       </c>
       <c r="B22" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>131067464</v>
       </c>
       <c r="B23" t="n">
-        <v>75223</v>
+        <v>75224</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>131067014</v>
       </c>
       <c r="B24" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>131067467</v>
       </c>
       <c r="B25" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131067775</v>
+        <v>131067820</v>
       </c>
       <c r="B28" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3804,31 +3804,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3836,10 +3839,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466299</v>
+        <v>466201</v>
       </c>
       <c r="R28" t="n">
-        <v>7047010</v>
+        <v>7046958</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3876,7 +3879,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Rikligt med garnlav här!</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3885,6 +3888,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3903,9 +3907,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3923,10 +3932,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131066990</v>
+        <v>131067815</v>
       </c>
       <c r="B29" t="n">
-        <v>57884</v>
+        <v>91834</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3934,29 +3943,24 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3966,10 +3970,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466169</v>
+        <v>466248</v>
       </c>
       <c r="R29" t="n">
-        <v>7046684</v>
+        <v>7046866</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4004,17 +4008,13 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4033,14 +4033,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4058,7 +4053,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131067460</v>
+        <v>131067775</v>
       </c>
       <c r="B30" t="n">
         <v>57884</v>
@@ -4097,14 +4092,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466264</v>
+        <v>466299</v>
       </c>
       <c r="R30" t="n">
-        <v>7046965</v>
+        <v>7047010</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4134,24 +4129,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4162,23 +4147,43 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131067767</v>
+        <v>131066990</v>
       </c>
       <c r="B31" t="n">
         <v>57884</v>
@@ -4221,10 +4226,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466140</v>
+        <v>466169</v>
       </c>
       <c r="R31" t="n">
-        <v>7046909</v>
+        <v>7046684</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4261,7 +4266,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på tall.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4275,22 +4280,27 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4308,7 +4318,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131067465</v>
+        <v>131067460</v>
       </c>
       <c r="B32" t="n">
         <v>57884</v>
@@ -4341,7 +4351,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4351,10 +4361,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466152</v>
+        <v>466264</v>
       </c>
       <c r="R32" t="n">
-        <v>7046928</v>
+        <v>7046965</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4386,7 +4396,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4396,12 +4406,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Äldre och färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4428,10 +4438,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131067820</v>
+        <v>131067767</v>
       </c>
       <c r="B33" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4439,34 +4449,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4474,10 +4481,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466201</v>
+        <v>466140</v>
       </c>
       <c r="R33" t="n">
-        <v>7046958</v>
+        <v>7046909</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4514,7 +4521,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav här!</t>
+          <t>Ringhack, äldre, på tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4523,33 +4530,27 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4567,10 +4568,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131067815</v>
+        <v>131067465</v>
       </c>
       <c r="B34" t="n">
-        <v>91833</v>
+        <v>57884</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4578,37 +4579,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466248</v>
+        <v>466152</v>
       </c>
       <c r="R34" t="n">
-        <v>7046866</v>
+        <v>7046928</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4638,60 +4644,54 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre och färska ringhack</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131067778</v>
+        <v>131067455</v>
       </c>
       <c r="B35" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4699,42 +4699,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466299</v>
+        <v>466247</v>
       </c>
       <c r="R35" t="n">
-        <v>7046954</v>
+        <v>7046669</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4764,14 +4756,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4782,46 +4779,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131067769</v>
+        <v>131067823</v>
       </c>
       <c r="B36" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4829,31 +4806,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4861,10 +4833,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466118</v>
+        <v>466269</v>
       </c>
       <c r="R36" t="n">
-        <v>7046899</v>
+        <v>7046701</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4899,38 +4871,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4948,10 +4901,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131067466</v>
+        <v>131067462</v>
       </c>
       <c r="B37" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4959,42 +4912,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465976</v>
+        <v>466212</v>
       </c>
       <c r="R37" t="n">
-        <v>7046933</v>
+        <v>7046990</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5026,7 +4971,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5036,12 +4981,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5068,7 +5008,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131067776</v>
+        <v>131067778</v>
       </c>
       <c r="B38" t="n">
         <v>57884</v>
@@ -5111,10 +5051,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466296</v>
+        <v>466299</v>
       </c>
       <c r="R38" t="n">
-        <v>7046956</v>
+        <v>7046954</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5198,10 +5138,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131067455</v>
+        <v>131067769</v>
       </c>
       <c r="B39" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5209,34 +5149,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466247</v>
+        <v>466118</v>
       </c>
       <c r="R39" t="n">
-        <v>7046669</v>
+        <v>7046899</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5266,19 +5214,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>10:26</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>10:26</t>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5289,26 +5232,46 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131067823</v>
+        <v>131067466</v>
       </c>
       <c r="B40" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5316,37 +5279,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466269</v>
+        <v>465976</v>
       </c>
       <c r="R40" t="n">
-        <v>7046701</v>
+        <v>7046933</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5376,45 +5344,54 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131067462</v>
+        <v>131067776</v>
       </c>
       <c r="B41" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5422,34 +5399,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466212</v>
+        <v>466296</v>
       </c>
       <c r="R41" t="n">
-        <v>7046990</v>
+        <v>7046956</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5479,19 +5464,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>11:39</t>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5502,16 +5482,36 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5656,7 +5656,7 @@
         <v>131067468</v>
       </c>
       <c r="B43" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>131067471</v>
       </c>
       <c r="B44" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>131067017</v>
       </c>
       <c r="B45" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>131067010</v>
       </c>
       <c r="B46" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>131067824</v>
       </c>
       <c r="B48" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>131067022</v>
       </c>
       <c r="B50" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>131067821</v>
       </c>
       <c r="B54" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         <v>131067019</v>
       </c>
       <c r="B55" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>131067013</v>
       </c>
       <c r="B56" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>131067816</v>
       </c>
       <c r="B57" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7611,10 +7611,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131067819</v>
+        <v>131067771</v>
       </c>
       <c r="B59" t="n">
-        <v>91833</v>
+        <v>57884</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7622,24 +7622,29 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7649,10 +7654,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>466023</v>
+        <v>466198</v>
       </c>
       <c r="R59" t="n">
-        <v>7046926</v>
+        <v>7046862</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7687,13 +7692,17 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7732,10 +7741,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131067016</v>
+        <v>131067819</v>
       </c>
       <c r="B60" t="n">
-        <v>79245</v>
+        <v>91834</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7743,34 +7752,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>466002</v>
+        <v>466023</v>
       </c>
       <c r="R60" t="n">
-        <v>7046855</v>
+        <v>7046926</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7805,19 +7817,35 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7834,10 +7862,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131067771</v>
+        <v>131067016</v>
       </c>
       <c r="B61" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7845,42 +7873,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>466198</v>
+        <v>466002</v>
       </c>
       <c r="R61" t="n">
-        <v>7046862</v>
+        <v>7046855</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7917,7 +7937,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7928,26 +7948,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7964,10 +7964,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131067021</v>
+        <v>131067774</v>
       </c>
       <c r="B62" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7975,26 +7975,31 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8002,10 +8007,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>466160</v>
+        <v>466303</v>
       </c>
       <c r="R62" t="n">
-        <v>7046831</v>
+        <v>7047009</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8042,7 +8047,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8051,7 +8056,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -8072,12 +8076,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8095,10 +8099,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131067015</v>
+        <v>131067772</v>
       </c>
       <c r="B63" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8106,34 +8110,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>465958</v>
+        <v>466208</v>
       </c>
       <c r="R63" t="n">
-        <v>7046711</v>
+        <v>7046922</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8170,7 +8182,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8181,6 +8193,31 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -8197,10 +8234,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131067774</v>
+        <v>131067021</v>
       </c>
       <c r="B64" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8208,31 +8245,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8240,10 +8272,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>466303</v>
+        <v>466160</v>
       </c>
       <c r="R64" t="n">
-        <v>7047009</v>
+        <v>7046831</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8280,7 +8312,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8289,6 +8321,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -8309,12 +8342,12 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8332,10 +8365,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131067772</v>
+        <v>131067015</v>
       </c>
       <c r="B65" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8343,42 +8376,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>466208</v>
+        <v>465958</v>
       </c>
       <c r="R65" t="n">
-        <v>7046922</v>
+        <v>7046711</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8415,7 +8440,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8426,31 +8451,6 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8470,7 +8470,7 @@
         <v>131067817</v>
       </c>
       <c r="B66" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8588,10 +8588,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131067807</v>
+        <v>131067758</v>
       </c>
       <c r="B67" t="n">
-        <v>57884</v>
+        <v>91814</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8599,29 +8599,28 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -8631,10 +8630,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>465804</v>
+        <v>466220</v>
       </c>
       <c r="R67" t="n">
-        <v>7046812</v>
+        <v>7046897</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8669,17 +8668,13 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8700,12 +8695,12 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8723,7 +8718,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131067780</v>
+        <v>131067807</v>
       </c>
       <c r="B68" t="n">
         <v>57884</v>
@@ -8766,10 +8761,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>466268</v>
+        <v>465804</v>
       </c>
       <c r="R68" t="n">
-        <v>7046893</v>
+        <v>7046812</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8833,9 +8828,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8853,10 +8853,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131067758</v>
+        <v>131067780</v>
       </c>
       <c r="B69" t="n">
-        <v>91813</v>
+        <v>57884</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8864,28 +8864,29 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -8895,10 +8896,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>466220</v>
+        <v>466268</v>
       </c>
       <c r="R69" t="n">
-        <v>7046897</v>
+        <v>7046893</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8933,13 +8934,17 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8958,14 +8963,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8986,7 +8986,7 @@
         <v>131067026</v>
       </c>
       <c r="B70" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>131067472</v>
       </c>
       <c r="B71" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>131067024</v>
       </c>
       <c r="B72" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>131067029</v>
       </c>
       <c r="B73" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>131067814</v>
       </c>
       <c r="B74" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>131067822</v>
       </c>
       <c r="B75" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>131067018</v>
       </c>
       <c r="B76" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10106,10 +10106,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131067011</v>
+        <v>131066995</v>
       </c>
       <c r="B79" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10117,26 +10117,31 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -10144,10 +10149,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>465794</v>
+        <v>466224</v>
       </c>
       <c r="R79" t="n">
-        <v>7046853</v>
+        <v>7046722</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10184,7 +10189,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På flera granar i granskog.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran i granskog.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10193,7 +10198,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -10214,12 +10218,12 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10237,10 +10241,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131066995</v>
+        <v>131067011</v>
       </c>
       <c r="B80" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10248,31 +10252,26 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -10280,10 +10279,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>466224</v>
+        <v>465794</v>
       </c>
       <c r="R80" t="n">
-        <v>7046722</v>
+        <v>7046853</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10320,7 +10319,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran i granskog.</t>
+          <t>På flera granar i granskog.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10329,6 +10328,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -10349,12 +10349,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>

--- a/artfynd/A 41290-2025 artfynd.xlsx
+++ b/artfynd/A 41290-2025 artfynd.xlsx
@@ -3793,10 +3793,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131067820</v>
+        <v>131067775</v>
       </c>
       <c r="B28" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3804,34 +3804,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3839,10 +3836,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466201</v>
+        <v>466299</v>
       </c>
       <c r="R28" t="n">
-        <v>7046958</v>
+        <v>7047010</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3879,7 +3876,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav här!</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3888,7 +3885,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3907,14 +3903,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3932,10 +3923,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131067815</v>
+        <v>131066990</v>
       </c>
       <c r="B29" t="n">
-        <v>91834</v>
+        <v>57884</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3943,24 +3934,29 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3970,10 +3966,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466248</v>
+        <v>466169</v>
       </c>
       <c r="R29" t="n">
-        <v>7046866</v>
+        <v>7046684</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4008,13 +4004,17 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4033,9 +4033,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4053,7 +4058,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131067775</v>
+        <v>131067460</v>
       </c>
       <c r="B30" t="n">
         <v>57884</v>
@@ -4092,14 +4097,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466299</v>
+        <v>466264</v>
       </c>
       <c r="R30" t="n">
-        <v>7047010</v>
+        <v>7046965</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4129,14 +4134,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4147,43 +4162,23 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131066990</v>
+        <v>131067767</v>
       </c>
       <c r="B31" t="n">
         <v>57884</v>
@@ -4226,10 +4221,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466169</v>
+        <v>466140</v>
       </c>
       <c r="R31" t="n">
-        <v>7046684</v>
+        <v>7046909</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4266,7 +4261,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack, äldre, på tall.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4280,27 +4275,22 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4318,7 +4308,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131067460</v>
+        <v>131067465</v>
       </c>
       <c r="B32" t="n">
         <v>57884</v>
@@ -4351,7 +4341,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4361,10 +4351,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466264</v>
+        <v>466152</v>
       </c>
       <c r="R32" t="n">
-        <v>7046965</v>
+        <v>7046928</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4396,7 +4386,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4406,12 +4396,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4438,10 +4428,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131067767</v>
+        <v>131067820</v>
       </c>
       <c r="B33" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4449,31 +4439,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4481,10 +4474,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466140</v>
+        <v>466201</v>
       </c>
       <c r="R33" t="n">
-        <v>7046909</v>
+        <v>7046958</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4521,7 +4514,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på tall.</t>
+          <t>Rikligt med garnlav här!</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4530,27 +4523,33 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4568,10 +4567,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131067465</v>
+        <v>131067815</v>
       </c>
       <c r="B34" t="n">
-        <v>57884</v>
+        <v>91834</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4579,42 +4578,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466152</v>
+        <v>466248</v>
       </c>
       <c r="R34" t="n">
-        <v>7046928</v>
+        <v>7046866</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4644,44 +4638,50 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre och färska ringhack</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -7611,10 +7611,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131067771</v>
+        <v>131067819</v>
       </c>
       <c r="B59" t="n">
-        <v>57884</v>
+        <v>91834</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7622,29 +7622,24 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7654,10 +7649,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>466198</v>
+        <v>466023</v>
       </c>
       <c r="R59" t="n">
-        <v>7046862</v>
+        <v>7046926</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7692,17 +7687,13 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7741,10 +7732,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131067819</v>
+        <v>131067016</v>
       </c>
       <c r="B60" t="n">
-        <v>91834</v>
+        <v>79246</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7752,37 +7743,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>466023</v>
+        <v>466002</v>
       </c>
       <c r="R60" t="n">
-        <v>7046926</v>
+        <v>7046855</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7817,35 +7805,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7862,10 +7834,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131067016</v>
+        <v>131067771</v>
       </c>
       <c r="B61" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7873,34 +7845,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>466002</v>
+        <v>466198</v>
       </c>
       <c r="R61" t="n">
-        <v>7046855</v>
+        <v>7046862</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7937,7 +7917,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7948,6 +7928,26 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7964,10 +7964,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131067774</v>
+        <v>131067021</v>
       </c>
       <c r="B62" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7975,31 +7975,26 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8007,10 +8002,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>466303</v>
+        <v>466160</v>
       </c>
       <c r="R62" t="n">
-        <v>7047009</v>
+        <v>7046831</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8047,7 +8042,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8056,6 +8051,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -8076,12 +8072,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8099,10 +8095,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131067772</v>
+        <v>131067015</v>
       </c>
       <c r="B63" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8110,42 +8106,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>466208</v>
+        <v>465958</v>
       </c>
       <c r="R63" t="n">
-        <v>7046922</v>
+        <v>7046711</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8182,7 +8170,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8193,31 +8181,6 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -8234,10 +8197,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131067021</v>
+        <v>131067774</v>
       </c>
       <c r="B64" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8245,26 +8208,31 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8272,10 +8240,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>466160</v>
+        <v>466303</v>
       </c>
       <c r="R64" t="n">
-        <v>7046831</v>
+        <v>7047009</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8312,7 +8280,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8321,7 +8289,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -8342,12 +8309,12 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8365,10 +8332,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131067015</v>
+        <v>131067772</v>
       </c>
       <c r="B65" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8376,34 +8343,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>465958</v>
+        <v>466208</v>
       </c>
       <c r="R65" t="n">
-        <v>7046711</v>
+        <v>7046922</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8440,7 +8415,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8451,6 +8426,31 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -10106,10 +10106,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131066995</v>
+        <v>131067811</v>
       </c>
       <c r="B79" t="n">
-        <v>57884</v>
+        <v>58043</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10117,42 +10117,50 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>466224</v>
+        <v>465799</v>
       </c>
       <c r="R79" t="n">
-        <v>7046722</v>
+        <v>7046814</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10189,7 +10197,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran i granskog.</t>
+          <t>Synobservation av 2 st födosökande talltitor i äldre granskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10204,26 +10212,6 @@
       <c r="AH79" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10241,10 +10229,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131067011</v>
+        <v>131066995</v>
       </c>
       <c r="B80" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10252,26 +10240,31 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -10279,10 +10272,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>465794</v>
+        <v>466224</v>
       </c>
       <c r="R80" t="n">
-        <v>7046853</v>
+        <v>7046722</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10319,7 +10312,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På flera granar i granskog.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran i granskog.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10328,7 +10321,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -10349,12 +10341,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10372,10 +10364,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131067811</v>
+        <v>131067011</v>
       </c>
       <c r="B81" t="n">
-        <v>58043</v>
+        <v>79246</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10383,50 +10375,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>465799</v>
+        <v>465794</v>
       </c>
       <c r="R81" t="n">
-        <v>7046814</v>
+        <v>7046853</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10463,7 +10442,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Synobservation av 2 st födosökande talltitor i äldre granskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
+          <t>På flera granar i granskog.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10472,12 +10451,33 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>

--- a/artfynd/A 41290-2025 artfynd.xlsx
+++ b/artfynd/A 41290-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131067818</v>
+        <v>131067813</v>
       </c>
       <c r="B2" t="n">
-        <v>91834</v>
+        <v>57066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,50 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465908</v>
+        <v>465954</v>
       </c>
       <c r="R2" t="n">
-        <v>7046627</v>
+        <v>7046648</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,34 +764,23 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Synobservation av 1 födosökande järpe i en björk.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -796,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131067813</v>
+        <v>131067818</v>
       </c>
       <c r="B3" t="n">
-        <v>57064</v>
+        <v>91836</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,50 +809,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465954</v>
+        <v>465908</v>
       </c>
       <c r="R3" t="n">
-        <v>7046648</v>
+        <v>7046627</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,23 +874,34 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Synobservation av 1 födosökande järpe i en björk.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131066991</v>
+        <v>131067020</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,42 +930,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466192</v>
+        <v>466180</v>
       </c>
       <c r="R4" t="n">
-        <v>7046678</v>
+        <v>7046800</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,7 +994,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på en gran.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,31 +1005,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1054,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131067779</v>
+        <v>131067470</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1065,42 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466288</v>
+        <v>465713</v>
       </c>
       <c r="R5" t="n">
-        <v>7046865</v>
+        <v>7046828</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,14 +1089,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Död gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,46 +1117,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131067020</v>
+        <v>131067023</v>
       </c>
       <c r="B6" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,16 +1162,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466180</v>
+        <v>466072</v>
       </c>
       <c r="R6" t="n">
-        <v>7046800</v>
+        <v>7046758</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1259,7 +1211,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,8 +1220,34 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1286,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131067470</v>
+        <v>131066991</v>
       </c>
       <c r="B7" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,34 +1275,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465713</v>
+        <v>466192</v>
       </c>
       <c r="R7" t="n">
-        <v>7046828</v>
+        <v>7046678</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,24 +1340,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Död gran</t>
+          <t>Ringhack, äldre, enstaka på en gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,26 +1358,51 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131067023</v>
+        <v>131067779</v>
       </c>
       <c r="B8" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,26 +1410,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1436,10 +1442,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466072</v>
+        <v>466288</v>
       </c>
       <c r="R8" t="n">
-        <v>7046758</v>
+        <v>7046865</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1482,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1485,13 +1491,12 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1504,14 +1509,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1529,10 +1529,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131067028</v>
+        <v>131067812</v>
       </c>
       <c r="B9" t="n">
-        <v>79246</v>
+        <v>80354</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,34 +1540,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466204</v>
+        <v>466199</v>
       </c>
       <c r="R9" t="n">
-        <v>7046724</v>
+        <v>7046948</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1604,7 +1607,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Skrovellav på gran!</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,8 +1616,34 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1631,10 +1660,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131067027</v>
+        <v>131067028</v>
       </c>
       <c r="B10" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,10 +1695,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466140</v>
+        <v>466204</v>
       </c>
       <c r="R10" t="n">
-        <v>7046777</v>
+        <v>7046724</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1733,10 +1762,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131067812</v>
+        <v>131067027</v>
       </c>
       <c r="B11" t="n">
-        <v>80352</v>
+        <v>79248</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1744,37 +1773,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466199</v>
+        <v>466140</v>
       </c>
       <c r="R11" t="n">
-        <v>7046948</v>
+        <v>7046777</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1811,7 +1837,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Skrovellav på gran!</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,34 +1846,8 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1864,10 +1864,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131067469</v>
+        <v>131066988</v>
       </c>
       <c r="B12" t="n">
-        <v>57064</v>
+        <v>57886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,16 +1875,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1892,25 +1892,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465770</v>
+        <v>465681</v>
       </c>
       <c r="R12" t="n">
-        <v>7046758</v>
+        <v>7046766</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,24 +1940,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Flög upp.</t>
+          <t>Ringhack, färska, enstaka på stambasen av en gran i granskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1968,26 +1958,51 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131066988</v>
+        <v>131066992</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2017,7 +2032,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2027,10 +2042,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465681</v>
+        <v>466171</v>
       </c>
       <c r="R13" t="n">
-        <v>7046766</v>
+        <v>7046705</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2067,7 +2082,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka på stambasen av en gran i granskog.</t>
+          <t>Ringhack, äldre, på ca 2 meters höjd på en tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2081,17 +2096,17 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -2101,7 +2116,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2119,10 +2134,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131066992</v>
+        <v>131067808</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2162,10 +2177,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466171</v>
+        <v>465816</v>
       </c>
       <c r="R14" t="n">
-        <v>7046705</v>
+        <v>7046818</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2202,7 +2217,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på ca 2 meters höjd på en tall.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2216,17 +2231,17 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -2236,7 +2251,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2254,10 +2269,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131067808</v>
+        <v>131067469</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>57066</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,16 +2280,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2282,25 +2297,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465816</v>
+        <v>465770</v>
       </c>
       <c r="R15" t="n">
-        <v>7046818</v>
+        <v>7046758</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2330,14 +2345,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Flög upp.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2348,98 +2373,61 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131067003</v>
+        <v>131067459</v>
       </c>
       <c r="B16" t="n">
-        <v>57073</v>
+        <v>79248</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466180</v>
+        <v>466261</v>
       </c>
       <c r="R16" t="n">
-        <v>7046822</v>
+        <v>7046954</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2469,14 +2457,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket under en tall.</t>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2487,31 +2480,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131067459</v>
+        <v>131067456</v>
       </c>
       <c r="B17" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2546,7 +2534,7 @@
         <v>466261</v>
       </c>
       <c r="R17" t="n">
-        <v>7046954</v>
+        <v>7046745</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2578,7 +2566,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2588,7 +2576,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2615,10 +2603,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131067456</v>
+        <v>131067463</v>
       </c>
       <c r="B18" t="n">
-        <v>79246</v>
+        <v>80354</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2626,21 +2614,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2650,10 +2638,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466261</v>
+        <v>466198</v>
       </c>
       <c r="R18" t="n">
-        <v>7046745</v>
+        <v>7046954</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2685,7 +2673,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2695,7 +2683,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2722,10 +2715,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131067463</v>
+        <v>131067766</v>
       </c>
       <c r="B19" t="n">
-        <v>80352</v>
+        <v>57886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2733,34 +2726,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466198</v>
+        <v>466011</v>
       </c>
       <c r="R19" t="n">
-        <v>7046954</v>
+        <v>7046933</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2790,24 +2791,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2818,48 +2809,73 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131067766</v>
+        <v>131067003</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>57075</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2867,20 +2883,24 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466011</v>
+        <v>466180</v>
       </c>
       <c r="R20" t="n">
-        <v>7046933</v>
+        <v>7046822</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2917,7 +2937,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Färsk spillning ovanpå snötäcket under en tall.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2931,27 +2951,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2969,10 +2969,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131067025</v>
+        <v>131067014</v>
       </c>
       <c r="B21" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2998,16 +2998,19 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466160</v>
+        <v>465848</v>
       </c>
       <c r="R21" t="n">
-        <v>7046687</v>
+        <v>7046818</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3044,7 +3047,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3053,8 +3056,34 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3071,10 +3100,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131067457</v>
+        <v>131067467</v>
       </c>
       <c r="B22" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3106,10 +3135,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466188</v>
+        <v>465982</v>
       </c>
       <c r="R22" t="n">
-        <v>7046783</v>
+        <v>7046926</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3141,7 +3170,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3151,7 +3180,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3178,45 +3207,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131067464</v>
+        <v>131067765</v>
       </c>
       <c r="B23" t="n">
-        <v>75224</v>
+        <v>57886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466197</v>
+        <v>466021</v>
       </c>
       <c r="R23" t="n">
-        <v>7046956</v>
+        <v>7046920</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3246,24 +3283,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Död sälg</t>
+          <t>Gammalt bohål 40 - 45 mm i diameter. Uthackat i stående död grantickerötad gran på 1,8 meters höjd över marken. På/kring fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3274,26 +3301,51 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131067014</v>
+        <v>131067777</v>
       </c>
       <c r="B24" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3301,26 +3353,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3328,10 +3385,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465848</v>
+        <v>466291</v>
       </c>
       <c r="R24" t="n">
-        <v>7046818</v>
+        <v>7046932</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3368,7 +3425,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3377,7 +3434,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3396,14 +3452,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3421,10 +3472,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131067467</v>
+        <v>131067025</v>
       </c>
       <c r="B25" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3452,14 +3503,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465982</v>
+        <v>466160</v>
       </c>
       <c r="R25" t="n">
-        <v>7046926</v>
+        <v>7046687</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3489,19 +3540,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:07</t>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3516,22 +3562,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131067765</v>
+        <v>131067457</v>
       </c>
       <c r="B26" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3539,42 +3585,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466021</v>
+        <v>466188</v>
       </c>
       <c r="R26" t="n">
-        <v>7046920</v>
+        <v>7046783</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3604,14 +3642,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Gammalt bohål 40 - 45 mm i diameter. Uthackat i stående död grantickerötad gran på 1,8 meters höjd över marken. På/kring fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3622,94 +3665,61 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131067777</v>
+        <v>131067464</v>
       </c>
       <c r="B27" t="n">
-        <v>57884</v>
+        <v>75226</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466291</v>
+        <v>466197</v>
       </c>
       <c r="R27" t="n">
-        <v>7046932</v>
+        <v>7046956</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3739,14 +3749,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Död sälg</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3757,46 +3777,26 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131067775</v>
+        <v>131067820</v>
       </c>
       <c r="B28" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3804,31 +3804,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3836,10 +3839,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466299</v>
+        <v>466201</v>
       </c>
       <c r="R28" t="n">
-        <v>7047010</v>
+        <v>7046958</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3876,7 +3879,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Rikligt med garnlav här!</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3885,6 +3888,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3903,9 +3907,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3923,10 +3932,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131066990</v>
+        <v>131067815</v>
       </c>
       <c r="B29" t="n">
-        <v>57884</v>
+        <v>91836</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3934,29 +3943,24 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3966,10 +3970,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466169</v>
+        <v>466248</v>
       </c>
       <c r="R29" t="n">
-        <v>7046684</v>
+        <v>7046866</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4004,17 +4008,13 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4033,14 +4033,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4058,10 +4053,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131067460</v>
+        <v>131067775</v>
       </c>
       <c r="B30" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4097,14 +4092,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466264</v>
+        <v>466299</v>
       </c>
       <c r="R30" t="n">
-        <v>7046965</v>
+        <v>7047010</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4134,24 +4129,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4162,26 +4147,46 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131067767</v>
+        <v>131066990</v>
       </c>
       <c r="B31" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4221,10 +4226,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466140</v>
+        <v>466169</v>
       </c>
       <c r="R31" t="n">
-        <v>7046909</v>
+        <v>7046684</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4261,7 +4266,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på tall.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4275,22 +4280,27 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4308,10 +4318,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131067465</v>
+        <v>131067460</v>
       </c>
       <c r="B32" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4341,7 +4351,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4351,10 +4361,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466152</v>
+        <v>466264</v>
       </c>
       <c r="R32" t="n">
-        <v>7046928</v>
+        <v>7046965</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4386,7 +4396,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4396,12 +4406,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Äldre och färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4428,10 +4438,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131067820</v>
+        <v>131067767</v>
       </c>
       <c r="B33" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4439,34 +4449,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4474,10 +4481,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466201</v>
+        <v>466140</v>
       </c>
       <c r="R33" t="n">
-        <v>7046958</v>
+        <v>7046909</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4514,7 +4521,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav här!</t>
+          <t>Ringhack, äldre, på tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4523,33 +4530,27 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4567,10 +4568,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131067815</v>
+        <v>131067465</v>
       </c>
       <c r="B34" t="n">
-        <v>91834</v>
+        <v>57886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4578,37 +4579,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466248</v>
+        <v>466152</v>
       </c>
       <c r="R34" t="n">
-        <v>7046866</v>
+        <v>7046928</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4638,60 +4644,54 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre och färska ringhack</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131067455</v>
+        <v>131067778</v>
       </c>
       <c r="B35" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4699,34 +4699,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466247</v>
+        <v>466299</v>
       </c>
       <c r="R35" t="n">
-        <v>7046669</v>
+        <v>7046954</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4756,19 +4764,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>10:26</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>10:26</t>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4779,26 +4782,46 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131067823</v>
+        <v>131067769</v>
       </c>
       <c r="B36" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4806,26 +4829,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4833,10 +4861,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466269</v>
+        <v>466118</v>
       </c>
       <c r="R36" t="n">
-        <v>7046701</v>
+        <v>7046899</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4871,19 +4899,38 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4901,10 +4948,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131067462</v>
+        <v>131067466</v>
       </c>
       <c r="B37" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4912,34 +4959,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466212</v>
+        <v>465976</v>
       </c>
       <c r="R37" t="n">
-        <v>7046990</v>
+        <v>7046933</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4971,7 +5026,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4981,7 +5036,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5008,10 +5068,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131067778</v>
+        <v>131067776</v>
       </c>
       <c r="B38" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5051,10 +5111,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466299</v>
+        <v>466296</v>
       </c>
       <c r="R38" t="n">
-        <v>7046954</v>
+        <v>7046956</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5138,10 +5198,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131067769</v>
+        <v>131067455</v>
       </c>
       <c r="B39" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5149,42 +5209,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466118</v>
+        <v>466247</v>
       </c>
       <c r="R39" t="n">
-        <v>7046899</v>
+        <v>7046669</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5214,14 +5266,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5232,46 +5289,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131067466</v>
+        <v>131067823</v>
       </c>
       <c r="B40" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5279,42 +5316,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465976</v>
+        <v>466269</v>
       </c>
       <c r="R40" t="n">
-        <v>7046933</v>
+        <v>7046701</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5344,54 +5376,45 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131067776</v>
+        <v>131067462</v>
       </c>
       <c r="B41" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5399,42 +5422,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466296</v>
+        <v>466212</v>
       </c>
       <c r="R41" t="n">
-        <v>7046956</v>
+        <v>7046990</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5464,14 +5479,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5482,36 +5502,16 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5521,7 +5521,7 @@
         <v>131066993</v>
       </c>
       <c r="B42" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5653,10 +5653,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131067468</v>
+        <v>131067809</v>
       </c>
       <c r="B43" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5664,34 +5664,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>465833</v>
+        <v>466011</v>
       </c>
       <c r="R43" t="n">
-        <v>7046793</v>
+        <v>7046932</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5721,19 +5729,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>14:48</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5744,26 +5747,51 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131067471</v>
+        <v>131067468</v>
       </c>
       <c r="B44" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5795,10 +5823,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>465684</v>
+        <v>465833</v>
       </c>
       <c r="R44" t="n">
-        <v>7046838</v>
+        <v>7046793</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5830,7 +5858,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5840,7 +5868,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5867,10 +5895,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131067017</v>
+        <v>131067471</v>
       </c>
       <c r="B45" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5898,14 +5926,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466015</v>
+        <v>465684</v>
       </c>
       <c r="R45" t="n">
-        <v>7046893</v>
+        <v>7046838</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5935,14 +5963,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5957,22 +5990,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131067010</v>
+        <v>131067017</v>
       </c>
       <c r="B46" t="n">
-        <v>91834</v>
+        <v>79248</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5980,37 +6013,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>465776</v>
+        <v>466015</v>
       </c>
       <c r="R46" t="n">
-        <v>7046851</v>
+        <v>7046893</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6047,7 +6077,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6056,34 +6086,8 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6100,10 +6104,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131067809</v>
+        <v>131067010</v>
       </c>
       <c r="B47" t="n">
-        <v>57884</v>
+        <v>91836</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6111,29 +6115,24 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -6143,10 +6142,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>466011</v>
+        <v>465776</v>
       </c>
       <c r="R47" t="n">
-        <v>7046932</v>
+        <v>7046851</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6183,7 +6182,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6192,6 +6191,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6238,7 +6238,7 @@
         <v>131067824</v>
       </c>
       <c r="B48" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>131067458</v>
       </c>
       <c r="B49" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6461,10 +6461,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131067022</v>
+        <v>131067770</v>
       </c>
       <c r="B50" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6472,26 +6472,31 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6499,10 +6504,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>466123</v>
+        <v>466195</v>
       </c>
       <c r="R50" t="n">
-        <v>7046774</v>
+        <v>7046876</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6539,7 +6544,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i  barrblandskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6548,13 +6553,12 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -6567,14 +6571,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6592,10 +6591,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131067770</v>
+        <v>131067022</v>
       </c>
       <c r="B51" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6603,31 +6602,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6635,10 +6629,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>466195</v>
+        <v>466123</v>
       </c>
       <c r="R51" t="n">
-        <v>7046876</v>
+        <v>7046774</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6675,7 +6669,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Långväxta bålar på gran i  barrblandskog.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6684,12 +6678,13 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -6702,9 +6697,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6725,7 +6725,7 @@
         <v>131066989</v>
       </c>
       <c r="B52" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>131067768</v>
       </c>
       <c r="B53" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6987,10 +6987,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131067821</v>
+        <v>131067004</v>
       </c>
       <c r="B54" t="n">
-        <v>79246</v>
+        <v>57883</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6998,26 +6998,31 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7025,10 +7030,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>466212</v>
+        <v>465997</v>
       </c>
       <c r="R54" t="n">
-        <v>7046860</v>
+        <v>7046830</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7063,19 +7068,43 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i en gran med sockel.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7093,10 +7122,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131067019</v>
+        <v>131067821</v>
       </c>
       <c r="B55" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7131,10 +7160,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>466214</v>
+        <v>466212</v>
       </c>
       <c r="R55" t="n">
-        <v>7046881</v>
+        <v>7046860</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7169,11 +7198,6 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -7187,26 +7211,6 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7224,10 +7228,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131067013</v>
+        <v>131067019</v>
       </c>
       <c r="B56" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7262,10 +7266,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>465836</v>
+        <v>466214</v>
       </c>
       <c r="R56" t="n">
-        <v>7046836</v>
+        <v>7046881</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7302,7 +7306,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i en lucka.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7355,10 +7359,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131067816</v>
+        <v>131067013</v>
       </c>
       <c r="B57" t="n">
-        <v>91834</v>
+        <v>79248</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7366,26 +7370,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7393,10 +7397,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>466283</v>
+        <v>465836</v>
       </c>
       <c r="R57" t="n">
-        <v>7046884</v>
+        <v>7046836</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7431,6 +7435,11 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran i en lucka.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7456,9 +7465,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7476,10 +7490,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131067004</v>
+        <v>131067816</v>
       </c>
       <c r="B58" t="n">
-        <v>57881</v>
+        <v>91836</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7487,29 +7501,24 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -7519,10 +7528,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>465997</v>
+        <v>466283</v>
       </c>
       <c r="R58" t="n">
-        <v>7046830</v>
+        <v>7046884</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7557,17 +7566,13 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i en gran med sockel.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7586,14 +7591,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7611,10 +7611,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131067819</v>
+        <v>131067771</v>
       </c>
       <c r="B59" t="n">
-        <v>91834</v>
+        <v>57886</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7622,24 +7622,29 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7649,10 +7654,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>466023</v>
+        <v>466198</v>
       </c>
       <c r="R59" t="n">
-        <v>7046926</v>
+        <v>7046862</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7687,13 +7692,17 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7732,10 +7741,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131067016</v>
+        <v>131067819</v>
       </c>
       <c r="B60" t="n">
-        <v>79246</v>
+        <v>91836</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7743,34 +7752,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>466002</v>
+        <v>466023</v>
       </c>
       <c r="R60" t="n">
-        <v>7046855</v>
+        <v>7046926</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7805,19 +7817,35 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7834,10 +7862,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131067771</v>
+        <v>131067016</v>
       </c>
       <c r="B61" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7845,42 +7873,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>466198</v>
+        <v>466002</v>
       </c>
       <c r="R61" t="n">
-        <v>7046862</v>
+        <v>7046855</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7917,7 +7937,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7928,26 +7948,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7964,10 +7964,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131067021</v>
+        <v>131067774</v>
       </c>
       <c r="B62" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7975,26 +7975,31 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8002,10 +8007,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>466160</v>
+        <v>466303</v>
       </c>
       <c r="R62" t="n">
-        <v>7046831</v>
+        <v>7047009</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8042,7 +8047,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8051,7 +8056,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -8072,12 +8076,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8095,10 +8099,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131067015</v>
+        <v>131067021</v>
       </c>
       <c r="B63" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8124,16 +8128,19 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>465958</v>
+        <v>466160</v>
       </c>
       <c r="R63" t="n">
-        <v>7046711</v>
+        <v>7046831</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8170,7 +8177,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8179,8 +8186,34 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -8197,10 +8230,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131067774</v>
+        <v>131067015</v>
       </c>
       <c r="B64" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8208,42 +8241,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>466303</v>
+        <v>465958</v>
       </c>
       <c r="R64" t="n">
-        <v>7047009</v>
+        <v>7046711</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8280,7 +8305,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8291,31 +8316,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8335,7 +8335,7 @@
         <v>131067772</v>
       </c>
       <c r="B65" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>131067817</v>
       </c>
       <c r="B66" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8588,10 +8588,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131067758</v>
+        <v>131067026</v>
       </c>
       <c r="B67" t="n">
-        <v>91814</v>
+        <v>79248</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8599,30 +8599,26 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8630,10 +8626,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>466220</v>
+        <v>466116</v>
       </c>
       <c r="R67" t="n">
-        <v>7046897</v>
+        <v>7046744</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8668,6 +8664,11 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På bark av tall i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8680,27 +8681,27 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8718,10 +8719,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131067807</v>
+        <v>131067758</v>
       </c>
       <c r="B68" t="n">
-        <v>57884</v>
+        <v>91816</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8729,29 +8730,28 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -8761,10 +8761,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>465804</v>
+        <v>466220</v>
       </c>
       <c r="R68" t="n">
-        <v>7046812</v>
+        <v>7046897</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8799,17 +8799,13 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8830,12 +8826,12 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8853,10 +8849,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131067780</v>
+        <v>131067807</v>
       </c>
       <c r="B69" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8896,10 +8892,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>466268</v>
+        <v>465804</v>
       </c>
       <c r="R69" t="n">
-        <v>7046893</v>
+        <v>7046812</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8963,9 +8959,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8983,10 +8984,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131067026</v>
+        <v>131067780</v>
       </c>
       <c r="B70" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8994,26 +8995,31 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9021,10 +9027,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>466116</v>
+        <v>466268</v>
       </c>
       <c r="R70" t="n">
-        <v>7046744</v>
+        <v>7046893</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9061,7 +9067,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På bark av tall i barrblandskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9070,33 +9076,27 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9114,10 +9114,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131067472</v>
+        <v>131067024</v>
       </c>
       <c r="B71" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9143,16 +9143,19 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>465661</v>
+        <v>466097</v>
       </c>
       <c r="R71" t="n">
-        <v>7046738</v>
+        <v>7046728</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9182,19 +9185,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>15:28</t>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9203,28 +9201,54 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131067024</v>
+        <v>131067822</v>
       </c>
       <c r="B72" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9259,10 +9283,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>466097</v>
+        <v>466268</v>
       </c>
       <c r="R72" t="n">
-        <v>7046728</v>
+        <v>7046889</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9297,11 +9321,6 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På gran i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -9314,27 +9333,7 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9352,10 +9351,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131067029</v>
+        <v>131067018</v>
       </c>
       <c r="B73" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9390,10 +9389,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>466255</v>
+        <v>466067</v>
       </c>
       <c r="R73" t="n">
-        <v>7046672</v>
+        <v>7046910</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9430,7 +9429,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På flera granar i granskog.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9483,10 +9482,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131067814</v>
+        <v>131067472</v>
       </c>
       <c r="B74" t="n">
-        <v>91834</v>
+        <v>79248</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9494,37 +9493,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>465657</v>
+        <v>465661</v>
       </c>
       <c r="R74" t="n">
-        <v>7046731</v>
+        <v>7046738</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9554,60 +9550,49 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131067822</v>
+        <v>131067029</v>
       </c>
       <c r="B75" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9642,10 +9627,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>466268</v>
+        <v>466255</v>
       </c>
       <c r="R75" t="n">
-        <v>7046889</v>
+        <v>7046672</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9680,6 +9665,11 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -9693,6 +9683,26 @@
       <c r="AH75" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9710,10 +9720,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131067018</v>
+        <v>131067814</v>
       </c>
       <c r="B76" t="n">
-        <v>79246</v>
+        <v>91836</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9721,26 +9731,26 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9748,10 +9758,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>466067</v>
+        <v>465657</v>
       </c>
       <c r="R76" t="n">
-        <v>7046910</v>
+        <v>7046731</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9786,11 +9796,6 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>På flera granar i granskog.</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -9816,14 +9821,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9844,7 +9844,7 @@
         <v>131066994</v>
       </c>
       <c r="B77" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>131067773</v>
       </c>
       <c r="B78" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10106,10 +10106,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131067811</v>
+        <v>131067011</v>
       </c>
       <c r="B79" t="n">
-        <v>58043</v>
+        <v>79248</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10117,50 +10117,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>465799</v>
+        <v>465794</v>
       </c>
       <c r="R79" t="n">
-        <v>7046814</v>
+        <v>7046853</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10197,7 +10184,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Synobservation av 2 st födosökande talltitor i äldre granskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
+          <t>På flera granar i granskog.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10206,12 +10193,33 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10232,7 +10240,7 @@
         <v>131066995</v>
       </c>
       <c r="B80" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10364,10 +10372,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131067011</v>
+        <v>131067811</v>
       </c>
       <c r="B81" t="n">
-        <v>79246</v>
+        <v>58045</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10375,37 +10383,50 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>465794</v>
+        <v>465799</v>
       </c>
       <c r="R81" t="n">
-        <v>7046853</v>
+        <v>7046814</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10442,7 +10463,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På flera granar i granskog.</t>
+          <t>Synobservation av 2 st födosökande talltitor i äldre granskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10451,33 +10472,12 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10498,7 +10498,7 @@
         <v>131067764</v>
       </c>
       <c r="B82" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 41290-2025 artfynd.xlsx
+++ b/artfynd/A 41290-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131067813</v>
       </c>
       <c r="B2" t="n">
-        <v>57066</v>
+        <v>57067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>131067818</v>
       </c>
       <c r="B3" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131067020</v>
+        <v>131067470</v>
       </c>
       <c r="B4" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -950,14 +950,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466180</v>
+        <v>465713</v>
       </c>
       <c r="R4" t="n">
-        <v>7046800</v>
+        <v>7046828</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,14 +987,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Död gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,22 +1019,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131067470</v>
+        <v>131067023</v>
       </c>
       <c r="B5" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1050,16 +1060,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465713</v>
+        <v>466072</v>
       </c>
       <c r="R5" t="n">
-        <v>7046828</v>
+        <v>7046758</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,24 +1102,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Död gran</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,28 +1118,54 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131067023</v>
+        <v>131066991</v>
       </c>
       <c r="B6" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,26 +1173,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1171,10 +1205,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466072</v>
+        <v>466192</v>
       </c>
       <c r="R6" t="n">
-        <v>7046758</v>
+        <v>7046678</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,7 +1245,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, enstaka på en gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,13 +1254,12 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1241,12 +1274,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1264,10 +1297,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131066991</v>
+        <v>131067779</v>
       </c>
       <c r="B7" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,10 +1340,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466192</v>
+        <v>466288</v>
       </c>
       <c r="R7" t="n">
-        <v>7046678</v>
+        <v>7046865</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,7 +1380,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på en gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,14 +1407,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1399,10 +1427,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131067779</v>
+        <v>131067020</v>
       </c>
       <c r="B8" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1410,42 +1438,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466288</v>
+        <v>466180</v>
       </c>
       <c r="R8" t="n">
-        <v>7046865</v>
+        <v>7046800</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1482,7 +1502,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,26 +1513,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1532,7 +1532,7 @@
         <v>131067812</v>
       </c>
       <c r="B9" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>131067028</v>
       </c>
       <c r="B10" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>131067027</v>
       </c>
       <c r="B11" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>131066988</v>
       </c>
       <c r="B12" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>131066992</v>
       </c>
       <c r="B13" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>131067808</v>
       </c>
       <c r="B14" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>131067469</v>
       </c>
       <c r="B15" t="n">
-        <v>57066</v>
+        <v>57067</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2389,10 +2389,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131067459</v>
+        <v>131067463</v>
       </c>
       <c r="B16" t="n">
-        <v>79248</v>
+        <v>80355</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2400,21 +2400,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2424,7 +2424,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466261</v>
+        <v>466198</v>
       </c>
       <c r="R16" t="n">
         <v>7046954</v>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2469,7 +2469,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2496,10 +2501,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131067456</v>
+        <v>131067459</v>
       </c>
       <c r="B17" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2534,7 +2539,7 @@
         <v>466261</v>
       </c>
       <c r="R17" t="n">
-        <v>7046745</v>
+        <v>7046954</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2566,7 +2571,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2576,7 +2581,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2603,10 +2608,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131067463</v>
+        <v>131067456</v>
       </c>
       <c r="B18" t="n">
-        <v>80354</v>
+        <v>79249</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2614,21 +2619,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2638,10 +2643,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466198</v>
+        <v>466261</v>
       </c>
       <c r="R18" t="n">
-        <v>7046954</v>
+        <v>7046745</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2673,7 +2678,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2683,12 +2688,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Sälg</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2715,32 +2715,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131067766</v>
+        <v>131067003</v>
       </c>
       <c r="B19" t="n">
-        <v>57886</v>
+        <v>57076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2748,20 +2748,24 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466011</v>
+        <v>466180</v>
       </c>
       <c r="R19" t="n">
-        <v>7046933</v>
+        <v>7046822</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2798,7 +2802,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Färsk spillning ovanpå snötäcket under en tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2812,27 +2816,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2850,32 +2834,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131067003</v>
+        <v>131067766</v>
       </c>
       <c r="B20" t="n">
-        <v>57075</v>
+        <v>57887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2883,24 +2867,20 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466180</v>
+        <v>466011</v>
       </c>
       <c r="R20" t="n">
-        <v>7046822</v>
+        <v>7046933</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2937,7 +2917,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket under en tall.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2951,7 +2931,27 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2969,10 +2969,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131067014</v>
+        <v>131067025</v>
       </c>
       <c r="B21" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2998,19 +2998,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465848</v>
+        <v>466160</v>
       </c>
       <c r="R21" t="n">
-        <v>7046818</v>
+        <v>7046687</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3047,7 +3044,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3056,34 +3053,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3100,10 +3071,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131067467</v>
+        <v>131067457</v>
       </c>
       <c r="B22" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3135,10 +3106,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465982</v>
+        <v>466188</v>
       </c>
       <c r="R22" t="n">
-        <v>7046926</v>
+        <v>7046783</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3170,7 +3141,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3180,7 +3151,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3207,53 +3178,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131067765</v>
+        <v>131067464</v>
       </c>
       <c r="B23" t="n">
-        <v>57886</v>
+        <v>75227</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466021</v>
+        <v>466197</v>
       </c>
       <c r="R23" t="n">
-        <v>7046920</v>
+        <v>7046956</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3283,14 +3246,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Gammalt bohål 40 - 45 mm i diameter. Uthackat i stående död grantickerötad gran på 1,8 meters höjd över marken. På/kring fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Död sälg</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3301,51 +3274,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131067777</v>
+        <v>131067014</v>
       </c>
       <c r="B24" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3353,31 +3301,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3385,10 +3328,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466291</v>
+        <v>465848</v>
       </c>
       <c r="R24" t="n">
-        <v>7046932</v>
+        <v>7046818</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3425,7 +3368,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3434,6 +3377,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3452,9 +3396,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3472,10 +3421,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131067025</v>
+        <v>131067467</v>
       </c>
       <c r="B25" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3503,14 +3452,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466160</v>
+        <v>465982</v>
       </c>
       <c r="R25" t="n">
-        <v>7046687</v>
+        <v>7046926</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3540,14 +3489,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Enstaka på gran.</t>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3562,22 +3516,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131067457</v>
+        <v>131067765</v>
       </c>
       <c r="B26" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3585,34 +3539,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466188</v>
+        <v>466021</v>
       </c>
       <c r="R26" t="n">
-        <v>7046783</v>
+        <v>7046920</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3642,19 +3604,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>10:44</t>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Gammalt bohål 40 - 45 mm i diameter. Uthackat i stående död grantickerötad gran på 1,8 meters höjd över marken. På/kring fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3665,61 +3622,94 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131067464</v>
+        <v>131067777</v>
       </c>
       <c r="B27" t="n">
-        <v>75226</v>
+        <v>57887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466197</v>
+        <v>466291</v>
       </c>
       <c r="R27" t="n">
-        <v>7046956</v>
+        <v>7046932</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3749,24 +3739,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Död sälg</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3777,26 +3757,46 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131067820</v>
+        <v>131067815</v>
       </c>
       <c r="B28" t="n">
-        <v>79248</v>
+        <v>91837</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3804,34 +3804,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3839,10 +3831,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466201</v>
+        <v>466248</v>
       </c>
       <c r="R28" t="n">
-        <v>7046958</v>
+        <v>7046866</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3877,11 +3869,6 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav här!</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3907,14 +3894,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3932,10 +3914,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131067815</v>
+        <v>131067820</v>
       </c>
       <c r="B29" t="n">
-        <v>91836</v>
+        <v>79249</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3943,26 +3925,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3970,10 +3960,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466248</v>
+        <v>466201</v>
       </c>
       <c r="R29" t="n">
-        <v>7046866</v>
+        <v>7046958</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4008,6 +3998,11 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav här!</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4033,9 +4028,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4056,7 +4056,7 @@
         <v>131067775</v>
       </c>
       <c r="B30" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>131066990</v>
       </c>
       <c r="B31" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>131067460</v>
       </c>
       <c r="B32" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>131067767</v>
       </c>
       <c r="B33" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>131067465</v>
       </c>
       <c r="B34" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4688,10 +4688,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131067778</v>
+        <v>131067455</v>
       </c>
       <c r="B35" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4699,42 +4699,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466299</v>
+        <v>466247</v>
       </c>
       <c r="R35" t="n">
-        <v>7046954</v>
+        <v>7046669</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4764,14 +4756,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4782,46 +4779,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131067769</v>
+        <v>131067823</v>
       </c>
       <c r="B36" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4829,31 +4806,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4861,10 +4833,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466118</v>
+        <v>466269</v>
       </c>
       <c r="R36" t="n">
-        <v>7046899</v>
+        <v>7046701</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4899,38 +4871,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4948,10 +4901,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131067466</v>
+        <v>131067462</v>
       </c>
       <c r="B37" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4959,42 +4912,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465976</v>
+        <v>466212</v>
       </c>
       <c r="R37" t="n">
-        <v>7046933</v>
+        <v>7046990</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5026,7 +4971,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5036,12 +4981,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5068,10 +5008,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131067776</v>
+        <v>131067778</v>
       </c>
       <c r="B38" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5111,10 +5051,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466296</v>
+        <v>466299</v>
       </c>
       <c r="R38" t="n">
-        <v>7046956</v>
+        <v>7046954</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5198,10 +5138,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131067455</v>
+        <v>131067769</v>
       </c>
       <c r="B39" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5209,34 +5149,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466247</v>
+        <v>466118</v>
       </c>
       <c r="R39" t="n">
-        <v>7046669</v>
+        <v>7046899</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5266,19 +5214,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>10:26</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>10:26</t>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5289,26 +5232,46 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131067823</v>
+        <v>131067466</v>
       </c>
       <c r="B40" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5316,37 +5279,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466269</v>
+        <v>465976</v>
       </c>
       <c r="R40" t="n">
-        <v>7046701</v>
+        <v>7046933</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5376,45 +5344,54 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131067462</v>
+        <v>131067776</v>
       </c>
       <c r="B41" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5422,34 +5399,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466212</v>
+        <v>466296</v>
       </c>
       <c r="R41" t="n">
-        <v>7046990</v>
+        <v>7046956</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5479,19 +5464,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>11:39</t>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5502,16 +5482,36 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5521,7 +5521,7 @@
         <v>131066993</v>
       </c>
       <c r="B42" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         <v>131067809</v>
       </c>
       <c r="B43" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>131067468</v>
       </c>
       <c r="B44" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>131067471</v>
       </c>
       <c r="B45" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>131067017</v>
       </c>
       <c r="B46" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>131067010</v>
       </c>
       <c r="B47" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6235,10 +6235,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131067824</v>
+        <v>131067458</v>
       </c>
       <c r="B48" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6246,37 +6246,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>466223</v>
+        <v>466199</v>
       </c>
       <c r="R48" t="n">
-        <v>7046669</v>
+        <v>7046831</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6306,45 +6311,54 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack, färska</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131067458</v>
+        <v>131067824</v>
       </c>
       <c r="B49" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6352,42 +6366,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>466199</v>
+        <v>466223</v>
       </c>
       <c r="R49" t="n">
-        <v>7046831</v>
+        <v>7046669</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6417,54 +6426,45 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack, färska</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131067770</v>
+        <v>131067022</v>
       </c>
       <c r="B50" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6472,31 +6472,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6504,10 +6499,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>466195</v>
+        <v>466123</v>
       </c>
       <c r="R50" t="n">
-        <v>7046876</v>
+        <v>7046774</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6544,7 +6539,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Långväxta bålar på gran i  barrblandskog.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6553,12 +6548,13 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -6571,9 +6567,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6591,10 +6592,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131067022</v>
+        <v>131067770</v>
       </c>
       <c r="B51" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6602,26 +6603,31 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6629,10 +6635,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>466123</v>
+        <v>466195</v>
       </c>
       <c r="R51" t="n">
-        <v>7046774</v>
+        <v>7046876</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6669,7 +6675,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i  barrblandskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6678,13 +6684,12 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -6697,14 +6702,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6725,7 +6725,7 @@
         <v>131066989</v>
       </c>
       <c r="B52" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>131067768</v>
       </c>
       <c r="B53" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6987,10 +6987,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131067004</v>
+        <v>131067816</v>
       </c>
       <c r="B54" t="n">
-        <v>57883</v>
+        <v>91837</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6998,29 +6998,24 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -7030,10 +7025,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>465997</v>
+        <v>466283</v>
       </c>
       <c r="R54" t="n">
-        <v>7046830</v>
+        <v>7046884</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7068,17 +7063,13 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i en gran med sockel.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7097,14 +7088,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7125,7 +7111,7 @@
         <v>131067821</v>
       </c>
       <c r="B55" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7231,7 +7217,7 @@
         <v>131067019</v>
       </c>
       <c r="B56" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7362,7 +7348,7 @@
         <v>131067013</v>
       </c>
       <c r="B57" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7490,10 +7476,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131067816</v>
+        <v>131067004</v>
       </c>
       <c r="B58" t="n">
-        <v>91836</v>
+        <v>57884</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7501,24 +7487,29 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -7528,10 +7519,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>466283</v>
+        <v>465997</v>
       </c>
       <c r="R58" t="n">
-        <v>7046884</v>
+        <v>7046830</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7566,13 +7557,17 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i en gran med sockel.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7591,9 +7586,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7611,10 +7611,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131067771</v>
+        <v>131067819</v>
       </c>
       <c r="B59" t="n">
-        <v>57886</v>
+        <v>91837</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7622,29 +7622,24 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7654,10 +7649,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>466198</v>
+        <v>466023</v>
       </c>
       <c r="R59" t="n">
-        <v>7046862</v>
+        <v>7046926</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7692,17 +7687,13 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7741,10 +7732,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131067819</v>
+        <v>131067016</v>
       </c>
       <c r="B60" t="n">
-        <v>91836</v>
+        <v>79249</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7752,37 +7743,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>466023</v>
+        <v>466002</v>
       </c>
       <c r="R60" t="n">
-        <v>7046926</v>
+        <v>7046855</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7817,35 +7805,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7862,10 +7834,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131067016</v>
+        <v>131067771</v>
       </c>
       <c r="B61" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7873,34 +7845,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>466002</v>
+        <v>466198</v>
       </c>
       <c r="R61" t="n">
-        <v>7046855</v>
+        <v>7046862</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7937,7 +7917,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7948,6 +7928,26 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7964,10 +7964,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131067774</v>
+        <v>131067021</v>
       </c>
       <c r="B62" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7975,31 +7975,26 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8007,10 +8002,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>466303</v>
+        <v>466160</v>
       </c>
       <c r="R62" t="n">
-        <v>7047009</v>
+        <v>7046831</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8047,7 +8042,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8056,6 +8051,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -8076,12 +8072,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8099,10 +8095,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131067021</v>
+        <v>131067015</v>
       </c>
       <c r="B63" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8128,19 +8124,16 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>466160</v>
+        <v>465958</v>
       </c>
       <c r="R63" t="n">
-        <v>7046831</v>
+        <v>7046711</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8177,7 +8170,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8186,34 +8179,8 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -8230,10 +8197,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131067015</v>
+        <v>131067774</v>
       </c>
       <c r="B64" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8241,34 +8208,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>465958</v>
+        <v>466303</v>
       </c>
       <c r="R64" t="n">
-        <v>7046711</v>
+        <v>7047009</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8305,7 +8280,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8316,6 +8291,31 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8335,7 +8335,7 @@
         <v>131067772</v>
       </c>
       <c r="B65" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>131067817</v>
       </c>
       <c r="B66" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         <v>131067026</v>
       </c>
       <c r="B67" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8722,7 +8722,7 @@
         <v>131067758</v>
       </c>
       <c r="B68" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         <v>131067807</v>
       </c>
       <c r="B69" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>131067780</v>
       </c>
       <c r="B70" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9114,10 +9114,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131067024</v>
+        <v>131067814</v>
       </c>
       <c r="B71" t="n">
-        <v>79248</v>
+        <v>91837</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9125,26 +9125,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9152,10 +9152,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>466097</v>
+        <v>465657</v>
       </c>
       <c r="R71" t="n">
-        <v>7046728</v>
+        <v>7046731</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9190,11 +9190,6 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På gran i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -9207,7 +9202,7 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
@@ -9220,14 +9215,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9245,10 +9235,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131067822</v>
+        <v>131067472</v>
       </c>
       <c r="B72" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9274,19 +9264,16 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>466268</v>
+        <v>465661</v>
       </c>
       <c r="R72" t="n">
-        <v>7046889</v>
+        <v>7046738</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9316,45 +9303,49 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131067018</v>
+        <v>131067024</v>
       </c>
       <c r="B73" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9389,10 +9380,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>466067</v>
+        <v>466097</v>
       </c>
       <c r="R73" t="n">
-        <v>7046910</v>
+        <v>7046728</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9429,7 +9420,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På flera granar i granskog.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9444,7 +9435,7 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -9482,10 +9473,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131067472</v>
+        <v>131067029</v>
       </c>
       <c r="B74" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9511,16 +9502,19 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>465661</v>
+        <v>466255</v>
       </c>
       <c r="R74" t="n">
-        <v>7046738</v>
+        <v>7046672</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9550,19 +9544,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>15:28</t>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9571,28 +9560,54 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131067029</v>
+        <v>131067822</v>
       </c>
       <c r="B75" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9627,10 +9642,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>466255</v>
+        <v>466268</v>
       </c>
       <c r="R75" t="n">
-        <v>7046672</v>
+        <v>7046889</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9665,11 +9680,6 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -9683,26 +9693,6 @@
       <c r="AH75" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9720,10 +9710,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131067814</v>
+        <v>131067018</v>
       </c>
       <c r="B76" t="n">
-        <v>91836</v>
+        <v>79249</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9731,26 +9721,26 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9758,10 +9748,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>465657</v>
+        <v>466067</v>
       </c>
       <c r="R76" t="n">
-        <v>7046731</v>
+        <v>7046910</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9796,6 +9786,11 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>På flera granar i granskog.</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -9821,9 +9816,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9844,7 +9844,7 @@
         <v>131066994</v>
       </c>
       <c r="B77" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>131067773</v>
       </c>
       <c r="B78" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
         <v>131067011</v>
       </c>
       <c r="B79" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>131066995</v>
       </c>
       <c r="B80" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>131067811</v>
       </c>
       <c r="B81" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>131067764</v>
       </c>
       <c r="B82" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 41290-2025 artfynd.xlsx
+++ b/artfynd/A 41290-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131067813</v>
+        <v>131067818</v>
       </c>
       <c r="B2" t="n">
-        <v>57067</v>
+        <v>91837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,50 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465954</v>
+        <v>465908</v>
       </c>
       <c r="R2" t="n">
-        <v>7046648</v>
+        <v>7046627</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,23 +751,34 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Synobservation av 1 födosökande järpe i en björk.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -798,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131067818</v>
+        <v>131067813</v>
       </c>
       <c r="B3" t="n">
-        <v>91837</v>
+        <v>57067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,37 +807,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465908</v>
+        <v>465954</v>
       </c>
       <c r="R3" t="n">
-        <v>7046627</v>
+        <v>7046648</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,34 +885,23 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Synobservation av 1 födosökande järpe i en björk.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,7 +919,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131067470</v>
+        <v>131067020</v>
       </c>
       <c r="B4" t="n">
         <v>79249</v>
@@ -950,14 +950,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465713</v>
+        <v>466180</v>
       </c>
       <c r="R4" t="n">
-        <v>7046828</v>
+        <v>7046800</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,24 +987,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Död gran</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,19 +1009,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131067023</v>
+        <v>131067470</v>
       </c>
       <c r="B5" t="n">
         <v>79249</v>
@@ -1060,19 +1050,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466072</v>
+        <v>465713</v>
       </c>
       <c r="R5" t="n">
-        <v>7046758</v>
+        <v>7046828</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,14 +1089,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Död gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,54 +1115,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131066991</v>
+        <v>131067023</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,31 +1144,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1205,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466192</v>
+        <v>466072</v>
       </c>
       <c r="R6" t="n">
-        <v>7046678</v>
+        <v>7046758</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,7 +1211,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på en gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,12 +1220,13 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1274,12 +1241,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1297,7 +1264,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131067779</v>
+        <v>131066991</v>
       </c>
       <c r="B7" t="n">
         <v>57887</v>
@@ -1340,10 +1307,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466288</v>
+        <v>466192</v>
       </c>
       <c r="R7" t="n">
-        <v>7046865</v>
+        <v>7046678</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1380,7 +1347,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, äldre, enstaka på en gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1407,9 +1374,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1427,10 +1399,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131067020</v>
+        <v>131067779</v>
       </c>
       <c r="B8" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,34 +1410,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466180</v>
+        <v>466288</v>
       </c>
       <c r="R8" t="n">
-        <v>7046800</v>
+        <v>7046865</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1502,7 +1482,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1513,6 +1493,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1864,10 +1864,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131066988</v>
+        <v>131067469</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>57067</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,16 +1875,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1892,25 +1892,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465681</v>
+        <v>465770</v>
       </c>
       <c r="R12" t="n">
-        <v>7046766</v>
+        <v>7046758</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,14 +1940,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka på stambasen av en gran i granskog.</t>
+          <t>Flög upp.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1958,41 +1968,16 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2134,7 +2119,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131067808</v>
+        <v>131066988</v>
       </c>
       <c r="B14" t="n">
         <v>57887</v>
@@ -2167,7 +2152,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2177,10 +2162,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465816</v>
+        <v>465681</v>
       </c>
       <c r="R14" t="n">
-        <v>7046818</v>
+        <v>7046766</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2217,7 +2202,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, enstaka på stambasen av en gran i granskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2269,10 +2254,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131067469</v>
+        <v>131067808</v>
       </c>
       <c r="B15" t="n">
-        <v>57067</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2280,16 +2265,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2297,25 +2282,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465770</v>
+        <v>465816</v>
       </c>
       <c r="R15" t="n">
-        <v>7046758</v>
+        <v>7046818</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2345,24 +2330,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Flög upp.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2373,16 +2348,41 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2501,10 +2501,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131067459</v>
+        <v>131067766</v>
       </c>
       <c r="B17" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2512,34 +2512,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466261</v>
+        <v>466011</v>
       </c>
       <c r="R17" t="n">
-        <v>7046954</v>
+        <v>7046933</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2569,19 +2577,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:07</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2592,23 +2595,48 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131067456</v>
+        <v>131067459</v>
       </c>
       <c r="B18" t="n">
         <v>79249</v>
@@ -2646,7 +2674,7 @@
         <v>466261</v>
       </c>
       <c r="R18" t="n">
-        <v>7046745</v>
+        <v>7046954</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2678,7 +2706,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2688,7 +2716,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2715,57 +2743,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131067003</v>
+        <v>131067456</v>
       </c>
       <c r="B19" t="n">
-        <v>57076</v>
+        <v>79249</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466180</v>
+        <v>466261</v>
       </c>
       <c r="R19" t="n">
-        <v>7046822</v>
+        <v>7046745</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2795,14 +2811,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket under en tall.</t>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2813,53 +2834,48 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131067766</v>
+        <v>131067003</v>
       </c>
       <c r="B20" t="n">
-        <v>57887</v>
+        <v>57076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2867,20 +2883,24 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466011</v>
+        <v>466180</v>
       </c>
       <c r="R20" t="n">
-        <v>7046933</v>
+        <v>7046822</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2917,7 +2937,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Färsk spillning ovanpå snötäcket under en tall.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2931,27 +2951,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131067815</v>
+        <v>131067820</v>
       </c>
       <c r="B28" t="n">
-        <v>91837</v>
+        <v>79249</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3804,26 +3804,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3831,10 +3839,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466248</v>
+        <v>466201</v>
       </c>
       <c r="R28" t="n">
-        <v>7046866</v>
+        <v>7046958</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3869,6 +3877,11 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav här!</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3894,9 +3907,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3914,10 +3932,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131067820</v>
+        <v>131067815</v>
       </c>
       <c r="B29" t="n">
-        <v>79249</v>
+        <v>91837</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3925,34 +3943,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3960,10 +3970,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466201</v>
+        <v>466248</v>
       </c>
       <c r="R29" t="n">
-        <v>7046958</v>
+        <v>7046866</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3998,11 +4008,6 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav här!</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4028,14 +4033,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4688,10 +4688,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131067455</v>
+        <v>131067778</v>
       </c>
       <c r="B35" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4699,34 +4699,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466247</v>
+        <v>466299</v>
       </c>
       <c r="R35" t="n">
-        <v>7046669</v>
+        <v>7046954</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4756,19 +4764,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>10:26</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>10:26</t>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4779,23 +4782,43 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131067823</v>
+        <v>131067455</v>
       </c>
       <c r="B36" t="n">
         <v>79249</v>
@@ -4824,19 +4847,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466269</v>
+        <v>466247</v>
       </c>
       <c r="R36" t="n">
-        <v>7046701</v>
+        <v>7046669</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4866,42 +4886,46 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131067462</v>
+        <v>131067823</v>
       </c>
       <c r="B37" t="n">
         <v>79249</v>
@@ -4930,16 +4954,19 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466212</v>
+        <v>466269</v>
       </c>
       <c r="R37" t="n">
-        <v>7046990</v>
+        <v>7046701</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4969,49 +4996,45 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131067778</v>
+        <v>131067462</v>
       </c>
       <c r="B38" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5019,42 +5042,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466299</v>
+        <v>466212</v>
       </c>
       <c r="R38" t="n">
-        <v>7046954</v>
+        <v>7046990</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5084,14 +5099,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5102,36 +5122,16 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5653,10 +5653,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131067809</v>
+        <v>131067017</v>
       </c>
       <c r="B43" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5664,42 +5664,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466011</v>
+        <v>466015</v>
       </c>
       <c r="R43" t="n">
-        <v>7046932</v>
+        <v>7046893</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5736,7 +5728,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5747,31 +5739,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5788,10 +5755,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131067468</v>
+        <v>131067010</v>
       </c>
       <c r="B44" t="n">
-        <v>79249</v>
+        <v>91837</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5799,34 +5766,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>465833</v>
+        <v>465776</v>
       </c>
       <c r="R44" t="n">
-        <v>7046793</v>
+        <v>7046851</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5856,19 +5826,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:48</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5877,28 +5842,54 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131067471</v>
+        <v>131067809</v>
       </c>
       <c r="B45" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5906,34 +5897,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>465684</v>
+        <v>466011</v>
       </c>
       <c r="R45" t="n">
-        <v>7046838</v>
+        <v>7046932</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5963,19 +5962,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>15:18</t>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5986,23 +5980,48 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131067017</v>
+        <v>131067468</v>
       </c>
       <c r="B46" t="n">
         <v>79249</v>
@@ -6033,14 +6052,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466015</v>
+        <v>465833</v>
       </c>
       <c r="R46" t="n">
-        <v>7046893</v>
+        <v>7046793</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6070,14 +6089,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6092,22 +6116,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131067010</v>
+        <v>131067471</v>
       </c>
       <c r="B47" t="n">
-        <v>91837</v>
+        <v>79249</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6115,37 +6139,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>465776</v>
+        <v>465684</v>
       </c>
       <c r="R47" t="n">
-        <v>7046851</v>
+        <v>7046838</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6175,14 +6196,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6191,54 +6217,28 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131067458</v>
+        <v>131067824</v>
       </c>
       <c r="B48" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6246,42 +6246,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>466199</v>
+        <v>466223</v>
       </c>
       <c r="R48" t="n">
-        <v>7046831</v>
+        <v>7046669</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6311,54 +6306,45 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack, färska</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131067824</v>
+        <v>131067458</v>
       </c>
       <c r="B49" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6366,37 +6352,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>466223</v>
+        <v>466199</v>
       </c>
       <c r="R49" t="n">
-        <v>7046669</v>
+        <v>7046831</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6426,35 +6417,44 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack, färska</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6987,10 +6987,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131067816</v>
+        <v>131067821</v>
       </c>
       <c r="B54" t="n">
-        <v>91837</v>
+        <v>79249</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6998,26 +6998,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>466283</v>
+        <v>466212</v>
       </c>
       <c r="R54" t="n">
-        <v>7046884</v>
+        <v>7046860</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7076,21 +7076,6 @@
       <c r="AH54" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7108,7 +7093,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131067821</v>
+        <v>131067019</v>
       </c>
       <c r="B55" t="n">
         <v>79249</v>
@@ -7146,10 +7131,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>466212</v>
+        <v>466214</v>
       </c>
       <c r="R55" t="n">
-        <v>7046860</v>
+        <v>7046881</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7184,6 +7169,11 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -7197,6 +7187,26 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7214,7 +7224,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131067019</v>
+        <v>131067013</v>
       </c>
       <c r="B56" t="n">
         <v>79249</v>
@@ -7252,10 +7262,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>466214</v>
+        <v>465836</v>
       </c>
       <c r="R56" t="n">
-        <v>7046881</v>
+        <v>7046836</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7292,7 +7302,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Långväxta bålar på gran i en lucka.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7345,10 +7355,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131067013</v>
+        <v>131067816</v>
       </c>
       <c r="B57" t="n">
-        <v>79249</v>
+        <v>91837</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7356,26 +7366,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7383,10 +7393,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>465836</v>
+        <v>466283</v>
       </c>
       <c r="R57" t="n">
-        <v>7046836</v>
+        <v>7046884</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7421,11 +7431,6 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran i en lucka.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7451,14 +7456,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7611,10 +7611,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131067819</v>
+        <v>131067771</v>
       </c>
       <c r="B59" t="n">
-        <v>91837</v>
+        <v>57887</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7622,24 +7622,29 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7649,10 +7654,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>466023</v>
+        <v>466198</v>
       </c>
       <c r="R59" t="n">
-        <v>7046926</v>
+        <v>7046862</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7687,13 +7692,17 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7732,10 +7741,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131067016</v>
+        <v>131067819</v>
       </c>
       <c r="B60" t="n">
-        <v>79249</v>
+        <v>91837</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7743,34 +7752,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>466002</v>
+        <v>466023</v>
       </c>
       <c r="R60" t="n">
-        <v>7046855</v>
+        <v>7046926</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7805,19 +7817,35 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7834,10 +7862,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131067771</v>
+        <v>131067016</v>
       </c>
       <c r="B61" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7845,42 +7873,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>466198</v>
+        <v>466002</v>
       </c>
       <c r="R61" t="n">
-        <v>7046862</v>
+        <v>7046855</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7917,7 +7937,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7928,26 +7948,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -8588,10 +8588,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131067026</v>
+        <v>131067807</v>
       </c>
       <c r="B67" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8599,26 +8599,31 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8626,10 +8631,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>466116</v>
+        <v>465804</v>
       </c>
       <c r="R67" t="n">
-        <v>7046744</v>
+        <v>7046812</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8666,7 +8671,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På bark av tall i barrblandskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8675,33 +8680,32 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8719,10 +8723,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131067758</v>
+        <v>131067780</v>
       </c>
       <c r="B68" t="n">
-        <v>91817</v>
+        <v>57887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8730,28 +8734,29 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -8761,10 +8766,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>466220</v>
+        <v>466268</v>
       </c>
       <c r="R68" t="n">
-        <v>7046897</v>
+        <v>7046893</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8799,13 +8804,17 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8824,14 +8833,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8849,10 +8853,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131067807</v>
+        <v>131067758</v>
       </c>
       <c r="B69" t="n">
-        <v>57887</v>
+        <v>91817</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8860,29 +8864,28 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -8892,10 +8895,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>465804</v>
+        <v>466220</v>
       </c>
       <c r="R69" t="n">
-        <v>7046812</v>
+        <v>7046897</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8930,17 +8933,13 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8961,12 +8960,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8984,10 +8983,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131067780</v>
+        <v>131067026</v>
       </c>
       <c r="B70" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8995,31 +8994,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9027,10 +9021,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>466268</v>
+        <v>466116</v>
       </c>
       <c r="R70" t="n">
-        <v>7046893</v>
+        <v>7046744</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9067,7 +9061,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På bark av tall i barrblandskog.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9076,27 +9070,33 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9114,10 +9114,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131067814</v>
+        <v>131067472</v>
       </c>
       <c r="B71" t="n">
-        <v>91837</v>
+        <v>79249</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9125,37 +9125,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>465657</v>
+        <v>465661</v>
       </c>
       <c r="R71" t="n">
-        <v>7046731</v>
+        <v>7046738</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9185,57 +9182,46 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131067472</v>
+        <v>131067024</v>
       </c>
       <c r="B72" t="n">
         <v>79249</v>
@@ -9264,16 +9250,19 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>465661</v>
+        <v>466097</v>
       </c>
       <c r="R72" t="n">
-        <v>7046738</v>
+        <v>7046728</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9303,19 +9292,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>15:28</t>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9324,25 +9308,51 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131067024</v>
+        <v>131067029</v>
       </c>
       <c r="B73" t="n">
         <v>79249</v>
@@ -9380,10 +9390,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>466097</v>
+        <v>466255</v>
       </c>
       <c r="R73" t="n">
-        <v>7046728</v>
+        <v>7046672</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9420,7 +9430,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9435,7 +9445,7 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -9473,7 +9483,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131067029</v>
+        <v>131067822</v>
       </c>
       <c r="B74" t="n">
         <v>79249</v>
@@ -9511,10 +9521,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>466255</v>
+        <v>466268</v>
       </c>
       <c r="R74" t="n">
-        <v>7046672</v>
+        <v>7046889</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9549,11 +9559,6 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -9567,26 +9572,6 @@
       <c r="AH74" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9604,7 +9589,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131067822</v>
+        <v>131067018</v>
       </c>
       <c r="B75" t="n">
         <v>79249</v>
@@ -9642,10 +9627,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>466268</v>
+        <v>466067</v>
       </c>
       <c r="R75" t="n">
-        <v>7046889</v>
+        <v>7046910</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9680,6 +9665,11 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På flera granar i granskog.</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -9693,6 +9683,26 @@
       <c r="AH75" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9710,10 +9720,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131067018</v>
+        <v>131067773</v>
       </c>
       <c r="B76" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9721,26 +9731,31 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9748,10 +9763,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>466067</v>
+        <v>466253</v>
       </c>
       <c r="R76" t="n">
-        <v>7046910</v>
+        <v>7046994</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9788,7 +9803,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På flera granar i granskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9797,7 +9812,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -9816,14 +9830,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9841,10 +9850,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131066994</v>
+        <v>131067814</v>
       </c>
       <c r="B77" t="n">
-        <v>57887</v>
+        <v>91837</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9852,29 +9861,24 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -9884,10 +9888,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>466211</v>
+        <v>465657</v>
       </c>
       <c r="R77" t="n">
-        <v>7046715</v>
+        <v>7046731</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9922,17 +9926,13 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran med spår av kådaflöde som står på sluttningen av en mindre kulle.</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9951,14 +9951,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9976,7 +9971,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131067773</v>
+        <v>131066994</v>
       </c>
       <c r="B78" t="n">
         <v>57887</v>
@@ -10009,7 +10004,7 @@
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -10019,10 +10014,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>466253</v>
+        <v>466211</v>
       </c>
       <c r="R78" t="n">
-        <v>7046994</v>
+        <v>7046715</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10059,7 +10054,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran med spår av kådaflöde som står på sluttningen av en mindre kulle.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10086,9 +10081,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>

--- a/artfynd/A 41290-2025 artfynd.xlsx
+++ b/artfynd/A 41290-2025 artfynd.xlsx
@@ -1529,10 +1529,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131067812</v>
+        <v>131067028</v>
       </c>
       <c r="B9" t="n">
-        <v>80355</v>
+        <v>79249</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,37 +1540,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466199</v>
+        <v>466204</v>
       </c>
       <c r="R9" t="n">
-        <v>7046948</v>
+        <v>7046724</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1607,7 +1604,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Skrovellav på gran!</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1616,34 +1613,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1660,7 +1631,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131067028</v>
+        <v>131067027</v>
       </c>
       <c r="B10" t="n">
         <v>79249</v>
@@ -1695,10 +1666,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466204</v>
+        <v>466140</v>
       </c>
       <c r="R10" t="n">
-        <v>7046724</v>
+        <v>7046777</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1762,10 +1733,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131067027</v>
+        <v>131067812</v>
       </c>
       <c r="B11" t="n">
-        <v>79249</v>
+        <v>80355</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,34 +1744,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466140</v>
+        <v>466199</v>
       </c>
       <c r="R11" t="n">
-        <v>7046777</v>
+        <v>7046948</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1837,7 +1811,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Skrovellav på gran!</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1846,8 +1820,34 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1864,10 +1864,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131067469</v>
+        <v>131066988</v>
       </c>
       <c r="B12" t="n">
-        <v>57067</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,16 +1875,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1892,25 +1892,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465770</v>
+        <v>465681</v>
       </c>
       <c r="R12" t="n">
-        <v>7046758</v>
+        <v>7046766</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,24 +1940,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Flög upp.</t>
+          <t>Ringhack, färska, enstaka på stambasen av en gran i granskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1968,16 +1958,41 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2119,7 +2134,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131066988</v>
+        <v>131067808</v>
       </c>
       <c r="B14" t="n">
         <v>57887</v>
@@ -2152,7 +2167,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2162,10 +2177,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465681</v>
+        <v>465816</v>
       </c>
       <c r="R14" t="n">
-        <v>7046766</v>
+        <v>7046818</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2202,7 +2217,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka på stambasen av en gran i granskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2254,10 +2269,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131067808</v>
+        <v>131067469</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>57067</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,16 +2280,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2282,25 +2297,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465816</v>
+        <v>465770</v>
       </c>
       <c r="R15" t="n">
-        <v>7046818</v>
+        <v>7046758</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2330,14 +2345,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Flög upp.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2348,51 +2373,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131067463</v>
+        <v>131067766</v>
       </c>
       <c r="B16" t="n">
-        <v>80355</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2400,34 +2400,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466198</v>
+        <v>466011</v>
       </c>
       <c r="R16" t="n">
-        <v>7046954</v>
+        <v>7046933</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2457,24 +2465,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2485,26 +2483,51 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131067766</v>
+        <v>131067459</v>
       </c>
       <c r="B17" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2512,42 +2535,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466011</v>
+        <v>466261</v>
       </c>
       <c r="R17" t="n">
-        <v>7046933</v>
+        <v>7046954</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2577,14 +2592,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2595,48 +2615,23 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131067459</v>
+        <v>131067456</v>
       </c>
       <c r="B18" t="n">
         <v>79249</v>
@@ -2674,7 +2669,7 @@
         <v>466261</v>
       </c>
       <c r="R18" t="n">
-        <v>7046954</v>
+        <v>7046745</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2706,7 +2701,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2716,7 +2711,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2743,10 +2738,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131067456</v>
+        <v>131067463</v>
       </c>
       <c r="B19" t="n">
-        <v>79249</v>
+        <v>80355</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2754,21 +2749,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2778,10 +2773,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466261</v>
+        <v>466198</v>
       </c>
       <c r="R19" t="n">
-        <v>7046745</v>
+        <v>7046954</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2813,7 +2808,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2823,7 +2818,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3178,45 +3178,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131067464</v>
+        <v>131067014</v>
       </c>
       <c r="B23" t="n">
-        <v>75227</v>
+        <v>79249</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466197</v>
+        <v>465848</v>
       </c>
       <c r="R23" t="n">
-        <v>7046956</v>
+        <v>7046818</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3246,24 +3249,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Död sälg</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3272,25 +3265,51 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131067014</v>
+        <v>131067467</v>
       </c>
       <c r="B24" t="n">
         <v>79249</v>
@@ -3319,19 +3338,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465848</v>
+        <v>465982</v>
       </c>
       <c r="R24" t="n">
-        <v>7046818</v>
+        <v>7046926</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3361,14 +3377,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På gran i granskog.</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3377,76 +3398,50 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131067467</v>
+        <v>131067464</v>
       </c>
       <c r="B25" t="n">
-        <v>79249</v>
+        <v>75227</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3456,10 +3451,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465982</v>
+        <v>466197</v>
       </c>
       <c r="R25" t="n">
-        <v>7046926</v>
+        <v>7046956</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3491,7 +3486,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3501,7 +3496,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Död sälg</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4688,10 +4688,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131067778</v>
+        <v>131067455</v>
       </c>
       <c r="B35" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4699,42 +4699,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466299</v>
+        <v>466247</v>
       </c>
       <c r="R35" t="n">
-        <v>7046954</v>
+        <v>7046669</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4764,14 +4756,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4782,43 +4779,23 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131067455</v>
+        <v>131067823</v>
       </c>
       <c r="B36" t="n">
         <v>79249</v>
@@ -4847,16 +4824,19 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466247</v>
+        <v>466269</v>
       </c>
       <c r="R36" t="n">
-        <v>7046669</v>
+        <v>7046701</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4886,46 +4866,42 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>10:26</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>10:26</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131067823</v>
+        <v>131067462</v>
       </c>
       <c r="B37" t="n">
         <v>79249</v>
@@ -4954,19 +4930,16 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466269</v>
+        <v>466212</v>
       </c>
       <c r="R37" t="n">
-        <v>7046701</v>
+        <v>7046990</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4996,45 +4969,49 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131067462</v>
+        <v>131067778</v>
       </c>
       <c r="B38" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5042,34 +5019,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466212</v>
+        <v>466299</v>
       </c>
       <c r="R38" t="n">
-        <v>7046990</v>
+        <v>7046954</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5099,19 +5084,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>11:39</t>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5122,16 +5102,36 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5653,7 +5653,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131067017</v>
+        <v>131067468</v>
       </c>
       <c r="B43" t="n">
         <v>79249</v>
@@ -5684,14 +5684,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466015</v>
+        <v>465833</v>
       </c>
       <c r="R43" t="n">
-        <v>7046893</v>
+        <v>7046793</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5721,14 +5721,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5743,22 +5748,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131067010</v>
+        <v>131067471</v>
       </c>
       <c r="B44" t="n">
-        <v>91837</v>
+        <v>79249</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5766,37 +5771,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>465776</v>
+        <v>465684</v>
       </c>
       <c r="R44" t="n">
-        <v>7046851</v>
+        <v>7046838</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5826,14 +5828,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5842,54 +5849,28 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131067809</v>
+        <v>131067017</v>
       </c>
       <c r="B45" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5897,42 +5878,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466011</v>
+        <v>466015</v>
       </c>
       <c r="R45" t="n">
-        <v>7046932</v>
+        <v>7046893</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5969,7 +5942,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5980,31 +5953,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6021,10 +5969,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131067468</v>
+        <v>131067010</v>
       </c>
       <c r="B46" t="n">
-        <v>79249</v>
+        <v>91837</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6032,34 +5980,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>465833</v>
+        <v>465776</v>
       </c>
       <c r="R46" t="n">
-        <v>7046793</v>
+        <v>7046851</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6089,19 +6040,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>14:48</t>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6110,28 +6056,54 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131067471</v>
+        <v>131067809</v>
       </c>
       <c r="B47" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6139,34 +6111,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>465684</v>
+        <v>466011</v>
       </c>
       <c r="R47" t="n">
-        <v>7046838</v>
+        <v>7046932</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6196,19 +6176,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>15:18</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6219,16 +6194,41 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -7611,10 +7611,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131067771</v>
+        <v>131067819</v>
       </c>
       <c r="B59" t="n">
-        <v>57887</v>
+        <v>91837</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7622,29 +7622,24 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7654,10 +7649,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>466198</v>
+        <v>466023</v>
       </c>
       <c r="R59" t="n">
-        <v>7046862</v>
+        <v>7046926</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7692,17 +7687,13 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7741,10 +7732,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131067819</v>
+        <v>131067016</v>
       </c>
       <c r="B60" t="n">
-        <v>91837</v>
+        <v>79249</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7752,37 +7743,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>466023</v>
+        <v>466002</v>
       </c>
       <c r="R60" t="n">
-        <v>7046926</v>
+        <v>7046855</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7817,35 +7805,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7862,10 +7834,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131067016</v>
+        <v>131067771</v>
       </c>
       <c r="B61" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7873,34 +7845,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>466002</v>
+        <v>466198</v>
       </c>
       <c r="R61" t="n">
-        <v>7046855</v>
+        <v>7046862</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7937,7 +7917,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7948,6 +7928,26 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -8853,10 +8853,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131067758</v>
+        <v>131067026</v>
       </c>
       <c r="B69" t="n">
-        <v>91817</v>
+        <v>79249</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8864,30 +8864,26 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8895,10 +8891,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>466220</v>
+        <v>466116</v>
       </c>
       <c r="R69" t="n">
-        <v>7046897</v>
+        <v>7046744</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8933,6 +8929,11 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På bark av tall i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8945,27 +8946,27 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8983,10 +8984,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131067026</v>
+        <v>131067758</v>
       </c>
       <c r="B70" t="n">
-        <v>79249</v>
+        <v>91817</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8994,26 +8995,30 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9021,10 +9026,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>466116</v>
+        <v>466220</v>
       </c>
       <c r="R70" t="n">
-        <v>7046744</v>
+        <v>7046897</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9059,11 +9064,6 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>På bark av tall i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -9076,27 +9076,27 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9483,10 +9483,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131067822</v>
+        <v>131067814</v>
       </c>
       <c r="B74" t="n">
-        <v>79249</v>
+        <v>91837</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9494,26 +9494,26 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9521,10 +9521,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>466268</v>
+        <v>465657</v>
       </c>
       <c r="R74" t="n">
-        <v>7046889</v>
+        <v>7046731</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9572,6 +9572,21 @@
       <c r="AH74" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9589,7 +9604,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131067018</v>
+        <v>131067822</v>
       </c>
       <c r="B75" t="n">
         <v>79249</v>
@@ -9627,10 +9642,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>466067</v>
+        <v>466268</v>
       </c>
       <c r="R75" t="n">
-        <v>7046910</v>
+        <v>7046889</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9665,11 +9680,6 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>På flera granar i granskog.</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -9683,26 +9693,6 @@
       <c r="AH75" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9720,10 +9710,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131067773</v>
+        <v>131067018</v>
       </c>
       <c r="B76" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9731,31 +9721,26 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9763,10 +9748,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>466253</v>
+        <v>466067</v>
       </c>
       <c r="R76" t="n">
-        <v>7046994</v>
+        <v>7046910</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9803,7 +9788,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På flera granar i granskog.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9812,6 +9797,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -9830,9 +9816,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9850,10 +9841,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131067814</v>
+        <v>131066994</v>
       </c>
       <c r="B77" t="n">
-        <v>91837</v>
+        <v>57887</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9861,24 +9852,29 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -9888,10 +9884,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>465657</v>
+        <v>466211</v>
       </c>
       <c r="R77" t="n">
-        <v>7046731</v>
+        <v>7046715</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9926,13 +9922,17 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på stambasen av en gran med spår av kådaflöde som står på sluttningen av en mindre kulle.</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9951,9 +9951,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9971,7 +9976,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131066994</v>
+        <v>131067773</v>
       </c>
       <c r="B78" t="n">
         <v>57887</v>
@@ -10004,7 +10009,7 @@
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -10014,10 +10019,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>466211</v>
+        <v>466253</v>
       </c>
       <c r="R78" t="n">
-        <v>7046715</v>
+        <v>7046994</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10054,7 +10059,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran med spår av kådaflöde som står på sluttningen av en mindre kulle.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10081,14 +10086,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>

--- a/artfynd/A 41290-2025 artfynd.xlsx
+++ b/artfynd/A 41290-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131067818</v>
+        <v>131067813</v>
       </c>
       <c r="B2" t="n">
-        <v>91837</v>
+        <v>57067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,50 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465908</v>
+        <v>465954</v>
       </c>
       <c r="R2" t="n">
-        <v>7046627</v>
+        <v>7046648</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,34 +764,23 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Synobservation av 1 födosökande järpe i en björk.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -796,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131067813</v>
+        <v>131067818</v>
       </c>
       <c r="B3" t="n">
-        <v>57067</v>
+        <v>91838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,50 +809,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465954</v>
+        <v>465908</v>
       </c>
       <c r="R3" t="n">
-        <v>7046648</v>
+        <v>7046627</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,23 +874,34 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Synobservation av 1 födosökande järpe i en björk.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -922,7 +922,7 @@
         <v>131067020</v>
       </c>
       <c r="B4" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>131067470</v>
       </c>
       <c r="B5" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>131067023</v>
       </c>
       <c r="B6" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>131066991</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>131067779</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1529,10 +1529,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131067028</v>
+        <v>131067812</v>
       </c>
       <c r="B9" t="n">
-        <v>79249</v>
+        <v>80356</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,34 +1540,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466204</v>
+        <v>466199</v>
       </c>
       <c r="R9" t="n">
-        <v>7046724</v>
+        <v>7046948</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1604,7 +1607,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Skrovellav på gran!</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,8 +1616,34 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1631,10 +1660,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131067027</v>
+        <v>131067028</v>
       </c>
       <c r="B10" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,10 +1695,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466140</v>
+        <v>466204</v>
       </c>
       <c r="R10" t="n">
-        <v>7046777</v>
+        <v>7046724</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1733,10 +1762,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131067812</v>
+        <v>131067027</v>
       </c>
       <c r="B11" t="n">
-        <v>80355</v>
+        <v>79250</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1744,37 +1773,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466199</v>
+        <v>466140</v>
       </c>
       <c r="R11" t="n">
-        <v>7046948</v>
+        <v>7046777</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1811,7 +1837,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Skrovellav på gran!</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,34 +1846,8 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1867,7 +1867,7 @@
         <v>131066988</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>131066992</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>131067808</v>
       </c>
       <c r="B14" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2389,10 +2389,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131067766</v>
+        <v>131067459</v>
       </c>
       <c r="B16" t="n">
-        <v>57887</v>
+        <v>79250</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2400,42 +2400,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466011</v>
+        <v>466261</v>
       </c>
       <c r="R16" t="n">
-        <v>7046933</v>
+        <v>7046954</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2465,14 +2457,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2483,51 +2480,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131067459</v>
+        <v>131067456</v>
       </c>
       <c r="B17" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2562,7 +2534,7 @@
         <v>466261</v>
       </c>
       <c r="R17" t="n">
-        <v>7046954</v>
+        <v>7046745</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2594,7 +2566,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2604,7 +2576,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2631,45 +2603,57 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131067456</v>
+        <v>131067003</v>
       </c>
       <c r="B18" t="n">
-        <v>79249</v>
+        <v>57076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466261</v>
+        <v>466180</v>
       </c>
       <c r="R18" t="n">
-        <v>7046745</v>
+        <v>7046822</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2699,19 +2683,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:34</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:34</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket under en tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2722,26 +2701,31 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131067463</v>
+        <v>131067766</v>
       </c>
       <c r="B19" t="n">
-        <v>80355</v>
+        <v>57888</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2749,34 +2733,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466198</v>
+        <v>466011</v>
       </c>
       <c r="R19" t="n">
-        <v>7046954</v>
+        <v>7046933</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2806,24 +2798,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2834,73 +2816,86 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131067003</v>
+        <v>131067463</v>
       </c>
       <c r="B20" t="n">
-        <v>57076</v>
+        <v>80356</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466180</v>
+        <v>466198</v>
       </c>
       <c r="R20" t="n">
-        <v>7046822</v>
+        <v>7046954</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2930,14 +2925,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket under en tall.</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2948,21 +2953,16 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2972,7 +2972,7 @@
         <v>131067025</v>
       </c>
       <c r="B21" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>131067457</v>
       </c>
       <c r="B22" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3178,48 +3178,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131067014</v>
+        <v>131067464</v>
       </c>
       <c r="B23" t="n">
-        <v>79249</v>
+        <v>75228</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465848</v>
+        <v>466197</v>
       </c>
       <c r="R23" t="n">
-        <v>7046818</v>
+        <v>7046956</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3249,14 +3246,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Död sälg</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3265,54 +3272,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131067467</v>
+        <v>131067014</v>
       </c>
       <c r="B24" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3338,16 +3319,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465982</v>
+        <v>465848</v>
       </c>
       <c r="R24" t="n">
-        <v>7046926</v>
+        <v>7046818</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3377,19 +3361,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:07</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3398,50 +3377,76 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131067464</v>
+        <v>131067467</v>
       </c>
       <c r="B25" t="n">
-        <v>75227</v>
+        <v>79250</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3451,10 +3456,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466197</v>
+        <v>465982</v>
       </c>
       <c r="R25" t="n">
-        <v>7046956</v>
+        <v>7046926</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3486,7 +3491,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3496,12 +3501,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Död sälg</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3531,7 +3531,7 @@
         <v>131067765</v>
       </c>
       <c r="B26" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>131067777</v>
       </c>
       <c r="B27" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>131067820</v>
       </c>
       <c r="B28" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>131067815</v>
       </c>
       <c r="B29" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>131067775</v>
       </c>
       <c r="B30" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>131066990</v>
       </c>
       <c r="B31" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>131067460</v>
       </c>
       <c r="B32" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>131067767</v>
       </c>
       <c r="B33" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>131067465</v>
       </c>
       <c r="B34" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>131067455</v>
       </c>
       <c r="B35" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>131067823</v>
       </c>
       <c r="B36" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>131067462</v>
       </c>
       <c r="B37" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         <v>131067778</v>
       </c>
       <c r="B38" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>131067769</v>
       </c>
       <c r="B39" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>131067466</v>
       </c>
       <c r="B40" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>131067776</v>
       </c>
       <c r="B41" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>131066993</v>
       </c>
       <c r="B42" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         <v>131067468</v>
       </c>
       <c r="B43" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>131067471</v>
       </c>
       <c r="B44" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>131067017</v>
       </c>
       <c r="B45" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>131067010</v>
       </c>
       <c r="B46" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>131067809</v>
       </c>
       <c r="B47" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>131067824</v>
       </c>
       <c r="B48" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>131067458</v>
       </c>
       <c r="B49" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>131067022</v>
       </c>
       <c r="B50" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>131067770</v>
       </c>
       <c r="B51" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>131066989</v>
       </c>
       <c r="B52" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>131067768</v>
       </c>
       <c r="B53" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6987,10 +6987,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131067821</v>
+        <v>131067004</v>
       </c>
       <c r="B54" t="n">
-        <v>79249</v>
+        <v>57885</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6998,26 +6998,31 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7025,10 +7030,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>466212</v>
+        <v>465997</v>
       </c>
       <c r="R54" t="n">
-        <v>7046860</v>
+        <v>7046830</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7063,19 +7068,43 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i en gran med sockel.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7093,10 +7122,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131067019</v>
+        <v>131067821</v>
       </c>
       <c r="B55" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7131,10 +7160,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>466214</v>
+        <v>466212</v>
       </c>
       <c r="R55" t="n">
-        <v>7046881</v>
+        <v>7046860</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7169,11 +7198,6 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -7187,26 +7211,6 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7224,10 +7228,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131067013</v>
+        <v>131067019</v>
       </c>
       <c r="B56" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7262,10 +7266,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>465836</v>
+        <v>466214</v>
       </c>
       <c r="R56" t="n">
-        <v>7046836</v>
+        <v>7046881</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7302,7 +7306,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i en lucka.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7355,10 +7359,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131067816</v>
+        <v>131067013</v>
       </c>
       <c r="B57" t="n">
-        <v>91837</v>
+        <v>79250</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7366,26 +7370,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7393,10 +7397,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>466283</v>
+        <v>465836</v>
       </c>
       <c r="R57" t="n">
-        <v>7046884</v>
+        <v>7046836</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7431,6 +7435,11 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran i en lucka.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7456,9 +7465,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7476,10 +7490,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131067004</v>
+        <v>131067816</v>
       </c>
       <c r="B58" t="n">
-        <v>57884</v>
+        <v>91838</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7487,29 +7501,24 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -7519,10 +7528,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>465997</v>
+        <v>466283</v>
       </c>
       <c r="R58" t="n">
-        <v>7046830</v>
+        <v>7046884</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7557,17 +7566,13 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i en gran med sockel.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7586,14 +7591,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7614,7 +7614,7 @@
         <v>131067819</v>
       </c>
       <c r="B59" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>131067016</v>
       </c>
       <c r="B60" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>131067771</v>
       </c>
       <c r="B61" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7964,10 +7964,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131067021</v>
+        <v>131067774</v>
       </c>
       <c r="B62" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7975,26 +7975,31 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8002,10 +8007,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>466160</v>
+        <v>466303</v>
       </c>
       <c r="R62" t="n">
-        <v>7046831</v>
+        <v>7047009</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8042,7 +8047,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8051,7 +8056,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -8072,12 +8076,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8095,10 +8099,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131067015</v>
+        <v>131067772</v>
       </c>
       <c r="B63" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8106,34 +8110,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>465958</v>
+        <v>466208</v>
       </c>
       <c r="R63" t="n">
-        <v>7046711</v>
+        <v>7046922</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8170,7 +8182,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8181,6 +8193,31 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -8197,10 +8234,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131067774</v>
+        <v>131067021</v>
       </c>
       <c r="B64" t="n">
-        <v>57887</v>
+        <v>79250</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8208,31 +8245,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8240,10 +8272,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>466303</v>
+        <v>466160</v>
       </c>
       <c r="R64" t="n">
-        <v>7047009</v>
+        <v>7046831</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8280,7 +8312,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8289,6 +8321,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -8309,12 +8342,12 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8332,10 +8365,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131067772</v>
+        <v>131067015</v>
       </c>
       <c r="B65" t="n">
-        <v>57887</v>
+        <v>79250</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8343,42 +8376,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>466208</v>
+        <v>465958</v>
       </c>
       <c r="R65" t="n">
-        <v>7046922</v>
+        <v>7046711</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8415,7 +8440,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8426,31 +8451,6 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8470,7 +8470,7 @@
         <v>131067817</v>
       </c>
       <c r="B66" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8588,10 +8588,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131067807</v>
+        <v>131067758</v>
       </c>
       <c r="B67" t="n">
-        <v>57887</v>
+        <v>91818</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8599,29 +8599,28 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -8631,10 +8630,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>465804</v>
+        <v>466220</v>
       </c>
       <c r="R67" t="n">
-        <v>7046812</v>
+        <v>7046897</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8669,17 +8668,13 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8700,12 +8695,12 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8723,10 +8718,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131067780</v>
+        <v>131067807</v>
       </c>
       <c r="B68" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8766,10 +8761,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>466268</v>
+        <v>465804</v>
       </c>
       <c r="R68" t="n">
-        <v>7046893</v>
+        <v>7046812</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8833,9 +8828,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8853,10 +8853,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131067026</v>
+        <v>131067780</v>
       </c>
       <c r="B69" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8864,26 +8864,31 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8891,10 +8896,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>466116</v>
+        <v>466268</v>
       </c>
       <c r="R69" t="n">
-        <v>7046744</v>
+        <v>7046893</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8931,7 +8936,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På bark av tall i barrblandskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8940,33 +8945,27 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8984,10 +8983,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131067758</v>
+        <v>131067026</v>
       </c>
       <c r="B70" t="n">
-        <v>91817</v>
+        <v>79250</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8995,30 +8994,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9026,10 +9021,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>466220</v>
+        <v>466116</v>
       </c>
       <c r="R70" t="n">
-        <v>7046897</v>
+        <v>7046744</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9064,6 +9059,11 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På bark av tall i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -9076,27 +9076,27 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9117,7 +9117,7 @@
         <v>131067472</v>
       </c>
       <c r="B71" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>131067024</v>
       </c>
       <c r="B72" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>131067029</v>
       </c>
       <c r="B73" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>131067814</v>
       </c>
       <c r="B74" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>131067822</v>
       </c>
       <c r="B75" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>131067018</v>
       </c>
       <c r="B76" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
         <v>131066994</v>
       </c>
       <c r="B77" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>131067773</v>
       </c>
       <c r="B78" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
         <v>131067011</v>
       </c>
       <c r="B79" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>131066995</v>
       </c>
       <c r="B80" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>131067811</v>
       </c>
       <c r="B81" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>131067764</v>
       </c>
       <c r="B82" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 41290-2025 artfynd.xlsx
+++ b/artfynd/A 41290-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131067813</v>
+        <v>131067818</v>
       </c>
       <c r="B2" t="n">
-        <v>57067</v>
+        <v>91838</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,50 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465954</v>
+        <v>465908</v>
       </c>
       <c r="R2" t="n">
-        <v>7046648</v>
+        <v>7046627</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,23 +751,34 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Synobservation av 1 födosökande järpe i en björk.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -798,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131067818</v>
+        <v>131067813</v>
       </c>
       <c r="B3" t="n">
-        <v>91838</v>
+        <v>57067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,37 +807,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465908</v>
+        <v>465954</v>
       </c>
       <c r="R3" t="n">
-        <v>7046627</v>
+        <v>7046648</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,34 +885,23 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Synobservation av 1 födosökande järpe i en björk.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131067020</v>
+        <v>131066991</v>
       </c>
       <c r="B4" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,34 +930,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466180</v>
+        <v>466192</v>
       </c>
       <c r="R4" t="n">
-        <v>7046800</v>
+        <v>7046678</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +1002,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Ringhack, äldre, enstaka på en gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,6 +1013,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1021,10 +1054,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131067470</v>
+        <v>131067779</v>
       </c>
       <c r="B5" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,34 +1065,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465713</v>
+        <v>466288</v>
       </c>
       <c r="R5" t="n">
-        <v>7046828</v>
+        <v>7046865</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,24 +1130,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Död gran</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,23 +1148,43 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131067023</v>
+        <v>131067020</v>
       </c>
       <c r="B6" t="n">
         <v>79250</v>
@@ -1162,19 +1213,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466072</v>
+        <v>466180</v>
       </c>
       <c r="R6" t="n">
-        <v>7046758</v>
+        <v>7046800</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,7 +1259,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,34 +1268,8 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1264,10 +1286,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131066991</v>
+        <v>131067470</v>
       </c>
       <c r="B7" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,42 +1297,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466192</v>
+        <v>465713</v>
       </c>
       <c r="R7" t="n">
-        <v>7046678</v>
+        <v>7046828</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,14 +1354,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på en gran.</t>
+          <t>Död gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,51 +1382,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131067779</v>
+        <v>131067023</v>
       </c>
       <c r="B8" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1410,31 +1409,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1442,10 +1436,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466288</v>
+        <v>466072</v>
       </c>
       <c r="R8" t="n">
-        <v>7046865</v>
+        <v>7046758</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1482,7 +1476,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,12 +1485,13 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1509,9 +1504,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1529,10 +1529,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131067812</v>
+        <v>131067028</v>
       </c>
       <c r="B9" t="n">
-        <v>80356</v>
+        <v>79250</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,37 +1540,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466199</v>
+        <v>466204</v>
       </c>
       <c r="R9" t="n">
-        <v>7046948</v>
+        <v>7046724</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1607,7 +1604,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Skrovellav på gran!</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1616,34 +1613,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1660,7 +1631,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131067028</v>
+        <v>131067027</v>
       </c>
       <c r="B10" t="n">
         <v>79250</v>
@@ -1695,10 +1666,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466204</v>
+        <v>466140</v>
       </c>
       <c r="R10" t="n">
-        <v>7046724</v>
+        <v>7046777</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1762,10 +1733,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131067027</v>
+        <v>131067812</v>
       </c>
       <c r="B11" t="n">
-        <v>79250</v>
+        <v>80356</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,34 +1744,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466140</v>
+        <v>466199</v>
       </c>
       <c r="R11" t="n">
-        <v>7046777</v>
+        <v>7046948</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1837,7 +1811,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Skrovellav på gran!</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1846,8 +1820,34 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1864,10 +1864,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131066988</v>
+        <v>131067469</v>
       </c>
       <c r="B12" t="n">
-        <v>57888</v>
+        <v>57067</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,16 +1875,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1892,25 +1892,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465681</v>
+        <v>465770</v>
       </c>
       <c r="R12" t="n">
-        <v>7046766</v>
+        <v>7046758</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,14 +1940,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka på stambasen av en gran i granskog.</t>
+          <t>Flög upp.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1958,41 +1968,16 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2134,7 +2119,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131067808</v>
+        <v>131066988</v>
       </c>
       <c r="B14" t="n">
         <v>57888</v>
@@ -2167,7 +2152,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2177,10 +2162,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465816</v>
+        <v>465681</v>
       </c>
       <c r="R14" t="n">
-        <v>7046818</v>
+        <v>7046766</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2217,7 +2202,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, enstaka på stambasen av en gran i granskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2269,10 +2254,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131067469</v>
+        <v>131067808</v>
       </c>
       <c r="B15" t="n">
-        <v>57067</v>
+        <v>57888</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2280,16 +2265,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2297,25 +2282,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465770</v>
+        <v>465816</v>
       </c>
       <c r="R15" t="n">
-        <v>7046758</v>
+        <v>7046818</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2345,24 +2330,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Flög upp.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2373,16 +2348,41 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2603,57 +2603,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131067003</v>
+        <v>131067463</v>
       </c>
       <c r="B18" t="n">
-        <v>57076</v>
+        <v>80356</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466180</v>
+        <v>466198</v>
       </c>
       <c r="R18" t="n">
-        <v>7046822</v>
+        <v>7046954</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2683,14 +2671,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket under en tall.</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2701,53 +2699,48 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131067766</v>
+        <v>131067003</v>
       </c>
       <c r="B19" t="n">
-        <v>57888</v>
+        <v>57076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2755,20 +2748,24 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466011</v>
+        <v>466180</v>
       </c>
       <c r="R19" t="n">
-        <v>7046933</v>
+        <v>7046822</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2805,7 +2802,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Färsk spillning ovanpå snötäcket under en tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2819,27 +2816,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2857,10 +2834,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131067463</v>
+        <v>131067766</v>
       </c>
       <c r="B20" t="n">
-        <v>80356</v>
+        <v>57888</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2868,34 +2845,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466198</v>
+        <v>466011</v>
       </c>
       <c r="R20" t="n">
-        <v>7046954</v>
+        <v>7046933</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2925,24 +2910,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2953,16 +2928,41 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131067820</v>
+        <v>131067775</v>
       </c>
       <c r="B28" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3804,34 +3804,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3839,10 +3836,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466201</v>
+        <v>466299</v>
       </c>
       <c r="R28" t="n">
-        <v>7046958</v>
+        <v>7047010</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3879,7 +3876,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav här!</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3888,7 +3885,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3907,14 +3903,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3932,10 +3923,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131067815</v>
+        <v>131066990</v>
       </c>
       <c r="B29" t="n">
-        <v>91838</v>
+        <v>57888</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3943,24 +3934,29 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3970,10 +3966,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466248</v>
+        <v>466169</v>
       </c>
       <c r="R29" t="n">
-        <v>7046866</v>
+        <v>7046684</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4008,13 +4004,17 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4033,9 +4033,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4053,7 +4058,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131067775</v>
+        <v>131067460</v>
       </c>
       <c r="B30" t="n">
         <v>57888</v>
@@ -4092,14 +4097,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466299</v>
+        <v>466264</v>
       </c>
       <c r="R30" t="n">
-        <v>7047010</v>
+        <v>7046965</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4129,14 +4134,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4147,43 +4162,23 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131066990</v>
+        <v>131067767</v>
       </c>
       <c r="B31" t="n">
         <v>57888</v>
@@ -4226,10 +4221,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466169</v>
+        <v>466140</v>
       </c>
       <c r="R31" t="n">
-        <v>7046684</v>
+        <v>7046909</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4266,7 +4261,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack, äldre, på tall.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4280,27 +4275,22 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4318,7 +4308,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131067460</v>
+        <v>131067465</v>
       </c>
       <c r="B32" t="n">
         <v>57888</v>
@@ -4351,7 +4341,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4361,10 +4351,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466264</v>
+        <v>466152</v>
       </c>
       <c r="R32" t="n">
-        <v>7046965</v>
+        <v>7046928</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4396,7 +4386,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4406,12 +4396,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4438,10 +4428,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131067767</v>
+        <v>131067820</v>
       </c>
       <c r="B33" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4449,31 +4439,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4481,10 +4474,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466140</v>
+        <v>466201</v>
       </c>
       <c r="R33" t="n">
-        <v>7046909</v>
+        <v>7046958</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4521,7 +4514,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på tall.</t>
+          <t>Rikligt med garnlav här!</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4530,27 +4523,33 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4568,10 +4567,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131067465</v>
+        <v>131067815</v>
       </c>
       <c r="B34" t="n">
-        <v>57888</v>
+        <v>91838</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4579,42 +4578,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466152</v>
+        <v>466248</v>
       </c>
       <c r="R34" t="n">
-        <v>7046928</v>
+        <v>7046866</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4644,44 +4638,50 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre och färska ringhack</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -5653,10 +5653,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131067468</v>
+        <v>131067809</v>
       </c>
       <c r="B43" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5664,34 +5664,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>465833</v>
+        <v>466011</v>
       </c>
       <c r="R43" t="n">
-        <v>7046793</v>
+        <v>7046932</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5721,19 +5729,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>14:48</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5744,23 +5747,48 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131067471</v>
+        <v>131067468</v>
       </c>
       <c r="B44" t="n">
         <v>79250</v>
@@ -5795,10 +5823,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>465684</v>
+        <v>465833</v>
       </c>
       <c r="R44" t="n">
-        <v>7046838</v>
+        <v>7046793</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5830,7 +5858,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5840,7 +5868,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5867,7 +5895,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131067017</v>
+        <v>131067471</v>
       </c>
       <c r="B45" t="n">
         <v>79250</v>
@@ -5898,14 +5926,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466015</v>
+        <v>465684</v>
       </c>
       <c r="R45" t="n">
-        <v>7046893</v>
+        <v>7046838</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5935,14 +5963,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5957,22 +5990,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131067010</v>
+        <v>131067017</v>
       </c>
       <c r="B46" t="n">
-        <v>91838</v>
+        <v>79250</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5980,37 +6013,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>465776</v>
+        <v>466015</v>
       </c>
       <c r="R46" t="n">
-        <v>7046851</v>
+        <v>7046893</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6047,7 +6077,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6056,34 +6086,8 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6100,10 +6104,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131067809</v>
+        <v>131067010</v>
       </c>
       <c r="B47" t="n">
-        <v>57888</v>
+        <v>91838</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6111,29 +6115,24 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -6143,10 +6142,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>466011</v>
+        <v>465776</v>
       </c>
       <c r="R47" t="n">
-        <v>7046932</v>
+        <v>7046851</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6183,7 +6182,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6192,6 +6191,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6461,10 +6461,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131067022</v>
+        <v>131067770</v>
       </c>
       <c r="B50" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6472,26 +6472,31 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6499,10 +6504,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>466123</v>
+        <v>466195</v>
       </c>
       <c r="R50" t="n">
-        <v>7046774</v>
+        <v>7046876</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6539,7 +6544,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i  barrblandskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6548,13 +6553,12 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -6567,14 +6571,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6592,10 +6591,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131067770</v>
+        <v>131067022</v>
       </c>
       <c r="B51" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6603,31 +6602,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6635,10 +6629,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>466195</v>
+        <v>466123</v>
       </c>
       <c r="R51" t="n">
-        <v>7046876</v>
+        <v>7046774</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6675,7 +6669,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Långväxta bålar på gran i  barrblandskog.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6684,12 +6678,13 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -6702,9 +6697,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7611,10 +7611,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131067819</v>
+        <v>131067016</v>
       </c>
       <c r="B59" t="n">
-        <v>91838</v>
+        <v>79250</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7622,37 +7622,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>466023</v>
+        <v>466002</v>
       </c>
       <c r="R59" t="n">
-        <v>7046926</v>
+        <v>7046855</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7687,35 +7684,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7732,10 +7713,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131067016</v>
+        <v>131067819</v>
       </c>
       <c r="B60" t="n">
-        <v>79250</v>
+        <v>91838</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7743,34 +7724,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>466002</v>
+        <v>466023</v>
       </c>
       <c r="R60" t="n">
-        <v>7046855</v>
+        <v>7046926</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7805,19 +7789,35 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -8588,10 +8588,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131067758</v>
+        <v>131067026</v>
       </c>
       <c r="B67" t="n">
-        <v>91818</v>
+        <v>79250</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8599,30 +8599,26 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8630,10 +8626,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>466220</v>
+        <v>466116</v>
       </c>
       <c r="R67" t="n">
-        <v>7046897</v>
+        <v>7046744</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8668,6 +8664,11 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På bark av tall i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8680,27 +8681,27 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8718,10 +8719,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131067807</v>
+        <v>131067758</v>
       </c>
       <c r="B68" t="n">
-        <v>57888</v>
+        <v>91818</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8729,29 +8730,28 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -8761,10 +8761,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>465804</v>
+        <v>466220</v>
       </c>
       <c r="R68" t="n">
-        <v>7046812</v>
+        <v>7046897</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8799,17 +8799,13 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8830,12 +8826,12 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8853,7 +8849,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131067780</v>
+        <v>131067807</v>
       </c>
       <c r="B69" t="n">
         <v>57888</v>
@@ -8896,10 +8892,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>466268</v>
+        <v>465804</v>
       </c>
       <c r="R69" t="n">
-        <v>7046893</v>
+        <v>7046812</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8963,9 +8959,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8983,10 +8984,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131067026</v>
+        <v>131067780</v>
       </c>
       <c r="B70" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8994,26 +8995,31 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9021,10 +9027,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>466116</v>
+        <v>466268</v>
       </c>
       <c r="R70" t="n">
-        <v>7046744</v>
+        <v>7046893</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9061,7 +9067,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På bark av tall i barrblandskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9070,33 +9076,27 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9114,10 +9114,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131067472</v>
+        <v>131067814</v>
       </c>
       <c r="B71" t="n">
-        <v>79250</v>
+        <v>91838</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9125,34 +9125,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>465661</v>
+        <v>465657</v>
       </c>
       <c r="R71" t="n">
-        <v>7046738</v>
+        <v>7046731</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9182,49 +9185,60 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131067024</v>
+        <v>131066994</v>
       </c>
       <c r="B72" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9232,26 +9246,31 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9259,10 +9278,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>466097</v>
+        <v>466211</v>
       </c>
       <c r="R72" t="n">
-        <v>7046728</v>
+        <v>7046715</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9299,7 +9318,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran med spår av kådaflöde som står på sluttningen av en mindre kulle.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9308,13 +9327,12 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
@@ -9329,12 +9347,12 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9352,7 +9370,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131067029</v>
+        <v>131067472</v>
       </c>
       <c r="B73" t="n">
         <v>79250</v>
@@ -9381,19 +9399,16 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>466255</v>
+        <v>465661</v>
       </c>
       <c r="R73" t="n">
-        <v>7046672</v>
+        <v>7046738</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9423,14 +9438,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9439,54 +9459,28 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131067814</v>
+        <v>131067024</v>
       </c>
       <c r="B74" t="n">
-        <v>91838</v>
+        <v>79250</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9494,26 +9488,26 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9521,10 +9515,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>465657</v>
+        <v>466097</v>
       </c>
       <c r="R74" t="n">
-        <v>7046731</v>
+        <v>7046728</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9559,6 +9553,11 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På gran i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -9571,7 +9570,7 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
@@ -9584,9 +9583,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9604,7 +9608,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131067822</v>
+        <v>131067029</v>
       </c>
       <c r="B75" t="n">
         <v>79250</v>
@@ -9642,10 +9646,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>466268</v>
+        <v>466255</v>
       </c>
       <c r="R75" t="n">
-        <v>7046889</v>
+        <v>7046672</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9680,6 +9684,11 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -9693,6 +9702,26 @@
       <c r="AH75" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9710,7 +9739,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131067018</v>
+        <v>131067822</v>
       </c>
       <c r="B76" t="n">
         <v>79250</v>
@@ -9748,10 +9777,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>466067</v>
+        <v>466268</v>
       </c>
       <c r="R76" t="n">
-        <v>7046910</v>
+        <v>7046889</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9786,11 +9815,6 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>På flera granar i granskog.</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -9804,26 +9828,6 @@
       <c r="AH76" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9841,10 +9845,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131066994</v>
+        <v>131067018</v>
       </c>
       <c r="B77" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9852,31 +9856,26 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9884,10 +9883,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>466211</v>
+        <v>466067</v>
       </c>
       <c r="R77" t="n">
-        <v>7046715</v>
+        <v>7046910</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9924,7 +9923,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran med spår av kådaflöde som står på sluttningen av en mindre kulle.</t>
+          <t>På flera granar i granskog.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9933,6 +9932,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9953,12 +9953,12 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10106,10 +10106,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131067011</v>
+        <v>131067811</v>
       </c>
       <c r="B79" t="n">
-        <v>79250</v>
+        <v>58047</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10117,37 +10117,50 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>465794</v>
+        <v>465799</v>
       </c>
       <c r="R79" t="n">
-        <v>7046853</v>
+        <v>7046814</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10184,7 +10197,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På flera granar i granskog.</t>
+          <t>Synobservation av 2 st födosökande talltitor i äldre granskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10193,33 +10206,12 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10237,10 +10229,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131066995</v>
+        <v>131067011</v>
       </c>
       <c r="B80" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10248,31 +10240,26 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -10280,10 +10267,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>466224</v>
+        <v>465794</v>
       </c>
       <c r="R80" t="n">
-        <v>7046722</v>
+        <v>7046853</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10320,7 +10307,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran i granskog.</t>
+          <t>På flera granar i granskog.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10329,6 +10316,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -10349,12 +10337,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10372,10 +10360,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131067811</v>
+        <v>131066995</v>
       </c>
       <c r="B81" t="n">
-        <v>58047</v>
+        <v>57888</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10383,50 +10371,42 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>465799</v>
+        <v>466224</v>
       </c>
       <c r="R81" t="n">
-        <v>7046814</v>
+        <v>7046722</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10463,7 +10443,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Synobservation av 2 st födosökande talltitor i äldre granskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran i granskog.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10478,6 +10458,26 @@
       <c r="AH81" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>

--- a/artfynd/A 41290-2025 artfynd.xlsx
+++ b/artfynd/A 41290-2025 artfynd.xlsx
@@ -10498,7 +10498,7 @@
         <v>131067764</v>
       </c>
       <c r="B82" t="n">
-        <v>57888</v>
+        <v>57896</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 41290-2025 artfynd.xlsx
+++ b/artfynd/A 41290-2025 artfynd.xlsx
@@ -10498,7 +10498,7 @@
         <v>131067764</v>
       </c>
       <c r="B82" t="n">
-        <v>57896</v>
+        <v>57898</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 41290-2025 artfynd.xlsx
+++ b/artfynd/A 41290-2025 artfynd.xlsx
@@ -10498,7 +10498,7 @@
         <v>131067764</v>
       </c>
       <c r="B82" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 41290-2025 artfynd.xlsx
+++ b/artfynd/A 41290-2025 artfynd.xlsx
@@ -10498,7 +10498,7 @@
         <v>131067764</v>
       </c>
       <c r="B82" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 41290-2025 artfynd.xlsx
+++ b/artfynd/A 41290-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY82"/>
+  <dimension ref="A1:AY75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131067818</v>
+        <v>131067758</v>
       </c>
       <c r="B2" t="n">
-        <v>91838</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
@@ -713,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465908</v>
+        <v>466220</v>
       </c>
       <c r="R2" t="n">
-        <v>7046627</v>
+        <v>7046897</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,9 +780,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -796,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131067813</v>
+        <v>131067463</v>
       </c>
       <c r="B3" t="n">
-        <v>57067</v>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,50 +816,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465954</v>
+        <v>466198</v>
       </c>
       <c r="R3" t="n">
-        <v>7046648</v>
+        <v>7046954</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,14 +873,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Synobservation av 1 födosökande järpe i en björk.</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,31 +901,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131066991</v>
+        <v>131067812</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,31 +928,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -962,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466192</v>
+        <v>466199</v>
       </c>
       <c r="R4" t="n">
-        <v>7046678</v>
+        <v>7046948</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,7 +995,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på en gran.</t>
+          <t>Skrovellav på gran!</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,6 +1004,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1031,12 +1025,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1054,42 +1048,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131067779</v>
+        <v>131067011</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1097,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466288</v>
+        <v>465794</v>
       </c>
       <c r="R5" t="n">
-        <v>7046865</v>
+        <v>7046853</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1137,7 +1126,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På flera granar i granskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,6 +1135,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1164,9 +1154,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1184,14 +1179,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131067020</v>
+        <v>131067013</v>
       </c>
       <c r="B6" t="n">
-        <v>79250</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1213,16 +1208,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466180</v>
+        <v>465836</v>
       </c>
       <c r="R6" t="n">
-        <v>7046800</v>
+        <v>7046836</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1259,7 +1257,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Långväxta bålar på gran i en lucka.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,8 +1266,34 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1286,14 +1310,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131067470</v>
+        <v>131067014</v>
       </c>
       <c r="B7" t="n">
-        <v>79250</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1315,16 +1339,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465713</v>
+        <v>465848</v>
       </c>
       <c r="R7" t="n">
-        <v>7046828</v>
+        <v>7046818</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,24 +1381,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Död gran</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,32 +1397,58 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131067023</v>
+        <v>131067015</v>
       </c>
       <c r="B8" t="n">
-        <v>79250</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1427,19 +1470,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466072</v>
+        <v>465958</v>
       </c>
       <c r="R8" t="n">
-        <v>7046758</v>
+        <v>7046711</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1516,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1485,34 +1525,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1529,14 +1543,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131067028</v>
+        <v>131067016</v>
       </c>
       <c r="B9" t="n">
-        <v>79250</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1564,10 +1578,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466204</v>
+        <v>466002</v>
       </c>
       <c r="R9" t="n">
-        <v>7046724</v>
+        <v>7046855</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1604,7 +1618,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1631,14 +1645,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131067027</v>
+        <v>131067017</v>
       </c>
       <c r="B10" t="n">
-        <v>79250</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1666,10 +1680,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466140</v>
+        <v>466015</v>
       </c>
       <c r="R10" t="n">
-        <v>7046777</v>
+        <v>7046893</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1733,32 +1747,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131067812</v>
+        <v>131067018</v>
       </c>
       <c r="B11" t="n">
-        <v>80356</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1771,10 +1785,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466199</v>
+        <v>466067</v>
       </c>
       <c r="R11" t="n">
-        <v>7046948</v>
+        <v>7046910</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1811,7 +1825,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Skrovellav på gran!</t>
+          <t>På flera granar i granskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1864,53 +1878,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131067469</v>
+        <v>131067019</v>
       </c>
       <c r="B12" t="n">
-        <v>57067</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465770</v>
+        <v>466214</v>
       </c>
       <c r="R12" t="n">
-        <v>7046758</v>
+        <v>7046881</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,24 +1949,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Flög upp.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1966,71 +1965,89 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131066992</v>
+        <v>131067020</v>
       </c>
       <c r="B13" t="n">
-        <v>57888</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466171</v>
+        <v>466180</v>
       </c>
       <c r="R13" t="n">
-        <v>7046705</v>
+        <v>7046800</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2067,7 +2084,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på ca 2 meters höjd på en tall.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2078,31 +2095,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2119,42 +2111,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131066988</v>
+        <v>131067021</v>
       </c>
       <c r="B14" t="n">
-        <v>57888</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2162,10 +2149,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465681</v>
+        <v>466160</v>
       </c>
       <c r="R14" t="n">
-        <v>7046766</v>
+        <v>7046831</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2202,7 +2189,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka på stambasen av en gran i granskog.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2211,6 +2198,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2231,12 +2219,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2254,42 +2242,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131067808</v>
+        <v>131067022</v>
       </c>
       <c r="B15" t="n">
-        <v>57888</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2297,10 +2280,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465816</v>
+        <v>466123</v>
       </c>
       <c r="R15" t="n">
-        <v>7046818</v>
+        <v>7046774</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2337,7 +2320,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Långväxta bålar på gran i  barrblandskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2346,12 +2329,13 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2366,12 +2350,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2389,14 +2373,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131067459</v>
+        <v>131067023</v>
       </c>
       <c r="B16" t="n">
-        <v>79250</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2418,16 +2402,19 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466261</v>
+        <v>466072</v>
       </c>
       <c r="R16" t="n">
-        <v>7046954</v>
+        <v>7046758</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2457,19 +2444,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:07</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2478,32 +2460,58 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131067456</v>
+        <v>131067024</v>
       </c>
       <c r="B17" t="n">
-        <v>79250</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2525,16 +2533,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466261</v>
+        <v>466097</v>
       </c>
       <c r="R17" t="n">
-        <v>7046745</v>
+        <v>7046728</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2564,19 +2575,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:34</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>10:34</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2585,63 +2591,89 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131067463</v>
+        <v>131067025</v>
       </c>
       <c r="B18" t="n">
-        <v>80356</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466198</v>
+        <v>466160</v>
       </c>
       <c r="R18" t="n">
-        <v>7046954</v>
+        <v>7046687</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2671,24 +2703,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2703,69 +2725,60 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131067003</v>
+        <v>131067026</v>
       </c>
       <c r="B19" t="n">
-        <v>57076</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466180</v>
+        <v>466116</v>
       </c>
       <c r="R19" t="n">
-        <v>7046822</v>
+        <v>7046744</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2802,7 +2815,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket under en tall.</t>
+          <t>På bark av tall i barrblandskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2811,12 +2824,33 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2834,53 +2868,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131067766</v>
+        <v>131067027</v>
       </c>
       <c r="B20" t="n">
-        <v>57888</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466011</v>
+        <v>466140</v>
       </c>
       <c r="R20" t="n">
-        <v>7046933</v>
+        <v>7046777</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2917,7 +2943,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2928,31 +2954,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2969,14 +2970,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131067025</v>
+        <v>131067028</v>
       </c>
       <c r="B21" t="n">
-        <v>79250</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -3004,10 +3005,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466160</v>
+        <v>466204</v>
       </c>
       <c r="R21" t="n">
-        <v>7046687</v>
+        <v>7046724</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3044,7 +3045,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3071,14 +3072,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131067457</v>
+        <v>131067029</v>
       </c>
       <c r="B22" t="n">
-        <v>79250</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -3100,16 +3101,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466188</v>
+        <v>466255</v>
       </c>
       <c r="R22" t="n">
-        <v>7046783</v>
+        <v>7046672</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3139,19 +3143,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>10:44</t>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3160,50 +3159,76 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131067464</v>
+        <v>131067455</v>
       </c>
       <c r="B23" t="n">
-        <v>75228</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3213,10 +3238,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466197</v>
+        <v>466247</v>
       </c>
       <c r="R23" t="n">
-        <v>7046956</v>
+        <v>7046669</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3248,7 +3273,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3258,12 +3283,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Död sälg</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3290,14 +3310,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131067014</v>
+        <v>131067456</v>
       </c>
       <c r="B24" t="n">
-        <v>79250</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3319,19 +3339,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465848</v>
+        <v>466261</v>
       </c>
       <c r="R24" t="n">
-        <v>7046818</v>
+        <v>7046745</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3361,14 +3378,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På gran i granskog.</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3377,58 +3399,32 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131067467</v>
+        <v>131067457</v>
       </c>
       <c r="B25" t="n">
-        <v>79250</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3456,10 +3452,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465982</v>
+        <v>466188</v>
       </c>
       <c r="R25" t="n">
-        <v>7046926</v>
+        <v>7046783</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3491,7 +3487,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3501,7 +3497,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3528,53 +3524,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131067765</v>
+        <v>131067459</v>
       </c>
       <c r="B26" t="n">
-        <v>57888</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466021</v>
+        <v>466261</v>
       </c>
       <c r="R26" t="n">
-        <v>7046920</v>
+        <v>7046954</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3604,14 +3592,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Gammalt bohål 40 - 45 mm i diameter. Uthackat i stående död grantickerötad gran på 1,8 meters höjd över marken. På/kring fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3622,94 +3615,61 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131067777</v>
+        <v>131067462</v>
       </c>
       <c r="B27" t="n">
-        <v>57888</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466291</v>
+        <v>466212</v>
       </c>
       <c r="R27" t="n">
-        <v>7046932</v>
+        <v>7046990</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3739,14 +3699,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3757,89 +3722,61 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131067775</v>
+        <v>131067467</v>
       </c>
       <c r="B28" t="n">
-        <v>57888</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466299</v>
+        <v>465982</v>
       </c>
       <c r="R28" t="n">
-        <v>7047010</v>
+        <v>7046926</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3869,14 +3806,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3887,89 +3829,61 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131066990</v>
+        <v>131067468</v>
       </c>
       <c r="B29" t="n">
-        <v>57888</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466169</v>
+        <v>465833</v>
       </c>
       <c r="R29" t="n">
-        <v>7046684</v>
+        <v>7046793</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3999,14 +3913,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4017,94 +3936,61 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131067460</v>
+        <v>131067470</v>
       </c>
       <c r="B30" t="n">
-        <v>57888</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466264</v>
+        <v>465713</v>
       </c>
       <c r="R30" t="n">
-        <v>7046965</v>
+        <v>7046828</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4136,7 +4022,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4146,12 +4032,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Död gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4178,53 +4064,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131067767</v>
+        <v>131067471</v>
       </c>
       <c r="B31" t="n">
-        <v>57888</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466140</v>
+        <v>465684</v>
       </c>
       <c r="R31" t="n">
-        <v>7046909</v>
+        <v>7046838</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4254,14 +4132,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på tall.</t>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4272,89 +4155,61 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131067465</v>
+        <v>131067472</v>
       </c>
       <c r="B32" t="n">
-        <v>57888</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466152</v>
+        <v>465661</v>
       </c>
       <c r="R32" t="n">
-        <v>7046928</v>
+        <v>7046738</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4386,7 +4241,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4396,12 +4251,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre och färska ringhack</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4431,11 +4281,11 @@
         <v>131067820</v>
       </c>
       <c r="B33" t="n">
-        <v>79250</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4567,37 +4417,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131067815</v>
+        <v>131067821</v>
       </c>
       <c r="B34" t="n">
-        <v>91838</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4605,10 +4455,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466248</v>
+        <v>466212</v>
       </c>
       <c r="R34" t="n">
-        <v>7046866</v>
+        <v>7046860</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4656,21 +4506,6 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4688,14 +4523,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131067455</v>
+        <v>131067822</v>
       </c>
       <c r="B35" t="n">
-        <v>79250</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4717,16 +4552,19 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466247</v>
+        <v>466268</v>
       </c>
       <c r="R35" t="n">
-        <v>7046669</v>
+        <v>7046889</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4756,39 +4594,35 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>10:26</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>10:26</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4798,11 +4632,11 @@
         <v>131067823</v>
       </c>
       <c r="B36" t="n">
-        <v>79250</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4901,14 +4735,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131067462</v>
+        <v>131067824</v>
       </c>
       <c r="B37" t="n">
-        <v>79250</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4930,16 +4764,19 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466212</v>
+        <v>466223</v>
       </c>
       <c r="R37" t="n">
-        <v>7046990</v>
+        <v>7046669</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4969,92 +4806,80 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131067778</v>
+        <v>131067464</v>
       </c>
       <c r="B38" t="n">
-        <v>57888</v>
+        <v>75300</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466299</v>
+        <v>466197</v>
       </c>
       <c r="R38" t="n">
-        <v>7046954</v>
+        <v>7046956</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5084,14 +4909,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Död sälg</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5102,63 +4937,43 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131067769</v>
+        <v>131067004</v>
       </c>
       <c r="B39" t="n">
-        <v>57888</v>
+        <v>57950</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5181,10 +4996,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466118</v>
+        <v>465997</v>
       </c>
       <c r="R39" t="n">
-        <v>7046899</v>
+        <v>7046830</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5221,7 +5036,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Rejäla hackspår i en gran med sockel.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5248,9 +5063,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5268,10 +5088,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131067466</v>
+        <v>131066988</v>
       </c>
       <c r="B40" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5301,20 +5121,20 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465976</v>
+        <v>465681</v>
       </c>
       <c r="R40" t="n">
-        <v>7046933</v>
+        <v>7046766</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5344,24 +5164,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack, färska, enstaka på stambasen av en gran i granskog.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5372,26 +5182,51 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131067776</v>
+        <v>131066989</v>
       </c>
       <c r="B41" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5431,10 +5266,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466296</v>
+        <v>465997</v>
       </c>
       <c r="R41" t="n">
-        <v>7046956</v>
+        <v>7046831</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5471,7 +5306,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, äldre, enstaka på en gammal gran med sockel och hackspår av spillkråka.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5498,9 +5333,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5518,10 +5358,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131066993</v>
+        <v>131066990</v>
       </c>
       <c r="B42" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5561,10 +5401,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466166</v>
+        <v>466169</v>
       </c>
       <c r="R42" t="n">
-        <v>7046714</v>
+        <v>7046684</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5653,10 +5493,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131067809</v>
+        <v>131066991</v>
       </c>
       <c r="B43" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5696,10 +5536,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466011</v>
+        <v>466192</v>
       </c>
       <c r="R43" t="n">
-        <v>7046932</v>
+        <v>7046678</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5736,7 +5576,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, äldre, enstaka på en gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5788,10 +5628,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131067468</v>
+        <v>131066992</v>
       </c>
       <c r="B44" t="n">
-        <v>79250</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5799,34 +5639,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>465833</v>
+        <v>466171</v>
       </c>
       <c r="R44" t="n">
-        <v>7046793</v>
+        <v>7046705</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5856,19 +5704,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:48</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på ca 2 meters höjd på en tall.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5879,26 +5722,51 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131067471</v>
+        <v>131066993</v>
       </c>
       <c r="B45" t="n">
-        <v>79250</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5906,34 +5774,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>465684</v>
+        <v>466166</v>
       </c>
       <c r="R45" t="n">
-        <v>7046838</v>
+        <v>7046714</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5963,19 +5839,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>15:18</t>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5986,26 +5857,51 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131067017</v>
+        <v>131066994</v>
       </c>
       <c r="B46" t="n">
-        <v>79250</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6013,34 +5909,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466015</v>
+        <v>466211</v>
       </c>
       <c r="R46" t="n">
-        <v>7046893</v>
+        <v>7046715</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6077,7 +5981,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran med spår av kådaflöde som står på sluttningen av en mindre kulle.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6088,6 +5992,31 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6104,10 +6033,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131067010</v>
+        <v>131066995</v>
       </c>
       <c r="B47" t="n">
-        <v>91838</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6115,24 +6044,29 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -6142,10 +6076,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>465776</v>
+        <v>466224</v>
       </c>
       <c r="R47" t="n">
-        <v>7046851</v>
+        <v>7046722</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6182,7 +6116,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran i granskog.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6191,7 +6125,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6235,10 +6168,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131067824</v>
+        <v>131067458</v>
       </c>
       <c r="B48" t="n">
-        <v>79250</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6246,37 +6179,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>466223</v>
+        <v>466199</v>
       </c>
       <c r="R48" t="n">
-        <v>7046669</v>
+        <v>7046831</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6306,45 +6244,54 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack, färska</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131067458</v>
+        <v>131067460</v>
       </c>
       <c r="B49" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6374,7 +6321,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6384,10 +6331,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>466199</v>
+        <v>466264</v>
       </c>
       <c r="R49" t="n">
-        <v>7046831</v>
+        <v>7046965</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6419,7 +6366,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6429,12 +6376,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack, färska</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6461,10 +6408,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131067770</v>
+        <v>131067465</v>
       </c>
       <c r="B50" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6494,20 +6441,20 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>466195</v>
+        <v>466152</v>
       </c>
       <c r="R50" t="n">
-        <v>7046876</v>
+        <v>7046928</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6537,14 +6484,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6555,46 +6512,26 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131067022</v>
+        <v>131067466</v>
       </c>
       <c r="B51" t="n">
-        <v>79250</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6602,37 +6539,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>466123</v>
+        <v>465976</v>
       </c>
       <c r="R51" t="n">
-        <v>7046774</v>
+        <v>7046933</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6662,14 +6604,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i  barrblandskog.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6678,54 +6630,28 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131066989</v>
+        <v>131067764</v>
       </c>
       <c r="B52" t="n">
-        <v>57888</v>
+        <v>57975</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6750,25 +6676,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>465997</v>
+        <v>465732</v>
       </c>
       <c r="R52" t="n">
-        <v>7046831</v>
+        <v>7046817</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6805,7 +6743,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på en gammal gran med sockel och hackspår av spillkråka.</t>
+          <t>Synobservation av 2 st individer, en hona och en hane, som födosökte i samma döda gran. Hanen födösökte även i en björkhögstubbe. Fyndplatsen finns i äldre granskog med stående död ved i en volym som indikerar mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6822,24 +6760,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad granskog med inslag av bl.a. björk.</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6857,10 +6780,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131067768</v>
+        <v>131067765</v>
       </c>
       <c r="B53" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6890,7 +6813,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -6900,10 +6823,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>466112</v>
+        <v>466021</v>
       </c>
       <c r="R53" t="n">
-        <v>7046911</v>
+        <v>7046920</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6940,7 +6863,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Gammalt bohål 40 - 45 mm i diameter. Uthackat i stående död grantickerötad gran på 1,8 meters höjd över marken. På/kring fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6967,9 +6890,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6987,10 +6915,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131067004</v>
+        <v>131067766</v>
       </c>
       <c r="B54" t="n">
-        <v>57885</v>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6998,16 +6926,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -7020,7 +6948,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -7030,10 +6958,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>465997</v>
+        <v>466011</v>
       </c>
       <c r="R54" t="n">
-        <v>7046830</v>
+        <v>7046933</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7070,7 +6998,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i en gran med sockel.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7122,10 +7050,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131067821</v>
+        <v>131067767</v>
       </c>
       <c r="B55" t="n">
-        <v>79250</v>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7133,26 +7061,31 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7160,10 +7093,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>466212</v>
+        <v>466140</v>
       </c>
       <c r="R55" t="n">
-        <v>7046860</v>
+        <v>7046909</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7198,19 +7131,38 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på tall.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7228,10 +7180,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131067019</v>
+        <v>131067768</v>
       </c>
       <c r="B56" t="n">
-        <v>79250</v>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7239,26 +7191,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7266,10 +7223,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>466214</v>
+        <v>466112</v>
       </c>
       <c r="R56" t="n">
-        <v>7046881</v>
+        <v>7046911</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7306,7 +7263,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7315,7 +7272,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7334,14 +7290,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7359,10 +7310,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131067013</v>
+        <v>131067769</v>
       </c>
       <c r="B57" t="n">
-        <v>79250</v>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7370,26 +7321,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7397,10 +7353,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>465836</v>
+        <v>466118</v>
       </c>
       <c r="R57" t="n">
-        <v>7046836</v>
+        <v>7046899</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7437,7 +7393,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i en lucka.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7446,7 +7402,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7465,14 +7420,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7490,10 +7440,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131067816</v>
+        <v>131067770</v>
       </c>
       <c r="B58" t="n">
-        <v>91838</v>
+        <v>57953</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7501,24 +7451,29 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -7528,10 +7483,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>466283</v>
+        <v>466195</v>
       </c>
       <c r="R58" t="n">
-        <v>7046884</v>
+        <v>7046876</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7566,13 +7521,17 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7611,10 +7570,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131067016</v>
+        <v>131067771</v>
       </c>
       <c r="B59" t="n">
-        <v>79250</v>
+        <v>57953</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7622,34 +7581,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>466002</v>
+        <v>466198</v>
       </c>
       <c r="R59" t="n">
-        <v>7046855</v>
+        <v>7046862</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7686,7 +7653,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7697,6 +7664,26 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7713,10 +7700,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131067819</v>
+        <v>131067772</v>
       </c>
       <c r="B60" t="n">
-        <v>91838</v>
+        <v>57953</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7724,24 +7711,29 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -7751,10 +7743,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>466023</v>
+        <v>466208</v>
       </c>
       <c r="R60" t="n">
-        <v>7046926</v>
+        <v>7046922</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7789,13 +7781,17 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7814,9 +7810,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7834,10 +7835,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131067771</v>
+        <v>131067773</v>
       </c>
       <c r="B61" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7877,10 +7878,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>466198</v>
+        <v>466253</v>
       </c>
       <c r="R61" t="n">
-        <v>7046862</v>
+        <v>7046994</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7964,10 +7965,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131067774</v>
+        <v>131067777</v>
       </c>
       <c r="B62" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7997,7 +7998,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -8007,10 +8008,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>466303</v>
+        <v>466291</v>
       </c>
       <c r="R62" t="n">
-        <v>7047009</v>
+        <v>7046932</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8047,7 +8048,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8074,14 +8075,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8099,10 +8095,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131067772</v>
+        <v>131067779</v>
       </c>
       <c r="B63" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8132,7 +8128,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -8142,10 +8138,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>466208</v>
+        <v>466288</v>
       </c>
       <c r="R63" t="n">
-        <v>7046922</v>
+        <v>7046865</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8182,7 +8178,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8209,14 +8205,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8234,10 +8225,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131067021</v>
+        <v>131067780</v>
       </c>
       <c r="B64" t="n">
-        <v>79250</v>
+        <v>57953</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8245,26 +8236,31 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8272,10 +8268,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>466160</v>
+        <v>466268</v>
       </c>
       <c r="R64" t="n">
-        <v>7046831</v>
+        <v>7046893</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8312,7 +8308,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8321,7 +8317,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -8340,14 +8335,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8365,10 +8355,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131067015</v>
+        <v>131067807</v>
       </c>
       <c r="B65" t="n">
-        <v>79250</v>
+        <v>57953</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8376,34 +8366,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>465958</v>
+        <v>465804</v>
       </c>
       <c r="R65" t="n">
-        <v>7046711</v>
+        <v>7046812</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8440,7 +8438,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8451,6 +8449,31 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8467,10 +8490,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131067817</v>
+        <v>131067808</v>
       </c>
       <c r="B66" t="n">
-        <v>91838</v>
+        <v>57953</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8478,24 +8501,29 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -8505,10 +8533,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>465737</v>
+        <v>465816</v>
       </c>
       <c r="R66" t="n">
-        <v>7046798</v>
+        <v>7046818</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8543,13 +8571,17 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -8568,9 +8600,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8588,10 +8625,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131067026</v>
+        <v>131067809</v>
       </c>
       <c r="B67" t="n">
-        <v>79250</v>
+        <v>57953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8599,26 +8636,31 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8626,10 +8668,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>466116</v>
+        <v>466011</v>
       </c>
       <c r="R67" t="n">
-        <v>7046744</v>
+        <v>7046932</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8666,7 +8708,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På bark av tall i barrblandskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8675,33 +8717,32 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8719,52 +8760,57 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131067758</v>
+        <v>131067003</v>
       </c>
       <c r="B68" t="n">
-        <v>91818</v>
+        <v>57141</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>466220</v>
+        <v>466180</v>
       </c>
       <c r="R68" t="n">
-        <v>7046897</v>
+        <v>7046822</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8799,39 +8845,23 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket under en tall.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8849,27 +8879,27 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131067807</v>
+        <v>131067469</v>
       </c>
       <c r="B69" t="n">
-        <v>57888</v>
+        <v>57132</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -8877,25 +8907,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>465804</v>
+        <v>465770</v>
       </c>
       <c r="R69" t="n">
-        <v>7046812</v>
+        <v>7046758</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8925,14 +8955,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Flög upp.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8943,68 +8983,43 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131067780</v>
+        <v>131067813</v>
       </c>
       <c r="B70" t="n">
-        <v>57888</v>
+        <v>57132</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -9012,25 +9027,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>466268</v>
+        <v>465954</v>
       </c>
       <c r="R70" t="n">
-        <v>7046893</v>
+        <v>7046648</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9067,7 +9090,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Synobservation av 1 födosökande järpe i en björk.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9082,21 +9105,6 @@
       <c r="AH70" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9114,10 +9122,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131067814</v>
+        <v>131067811</v>
       </c>
       <c r="B71" t="n">
-        <v>91838</v>
+        <v>58114</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9125,37 +9133,50 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>465657</v>
+        <v>465799</v>
       </c>
       <c r="R71" t="n">
-        <v>7046731</v>
+        <v>7046814</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9190,34 +9211,23 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Synobservation av 2 st födosökande talltitor i äldre granskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9235,10 +9245,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131066994</v>
+        <v>131067774</v>
       </c>
       <c r="B72" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9278,10 +9288,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>466211</v>
+        <v>466303</v>
       </c>
       <c r="R72" t="n">
-        <v>7046715</v>
+        <v>7047009</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9318,7 +9328,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran med spår av kådaflöde som står på sluttningen av en mindre kulle.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9370,10 +9380,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131067472</v>
+        <v>131067775</v>
       </c>
       <c r="B73" t="n">
-        <v>79250</v>
+        <v>57953</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9381,34 +9391,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>465661</v>
+        <v>466299</v>
       </c>
       <c r="R73" t="n">
-        <v>7046738</v>
+        <v>7047010</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9438,19 +9456,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>15:28</t>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9461,26 +9474,46 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131067024</v>
+        <v>131067776</v>
       </c>
       <c r="B74" t="n">
-        <v>79250</v>
+        <v>57953</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9488,26 +9521,31 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9515,10 +9553,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>466097</v>
+        <v>466296</v>
       </c>
       <c r="R74" t="n">
-        <v>7046728</v>
+        <v>7046956</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9555,7 +9593,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9564,13 +9602,12 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
@@ -9583,14 +9620,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9608,10 +9640,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131067029</v>
+        <v>131067778</v>
       </c>
       <c r="B75" t="n">
-        <v>79250</v>
+        <v>57953</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9619,26 +9651,31 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9646,10 +9683,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>466255</v>
+        <v>466299</v>
       </c>
       <c r="R75" t="n">
-        <v>7046672</v>
+        <v>7046954</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9686,7 +9723,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9695,7 +9732,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -9714,14 +9750,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9736,894 +9767,6 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>131067822</v>
-      </c>
-      <c r="B76" t="n">
-        <v>79250</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Långan Öst, Jmt</t>
-        </is>
-      </c>
-      <c r="Q76" t="n">
-        <v>466268</v>
-      </c>
-      <c r="R76" t="n">
-        <v>7046889</v>
-      </c>
-      <c r="S76" t="n">
-        <v>10</v>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AD76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF76" t="inlineStr"/>
-      <c r="AG76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT76" t="inlineStr"/>
-      <c r="AW76" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>131067018</v>
-      </c>
-      <c r="B77" t="n">
-        <v>79250</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>Långan Öst, Jmt</t>
-        </is>
-      </c>
-      <c r="Q77" t="n">
-        <v>466067</v>
-      </c>
-      <c r="R77" t="n">
-        <v>7046910</v>
-      </c>
-      <c r="S77" t="n">
-        <v>10</v>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På flera granar i granskog.</t>
-        </is>
-      </c>
-      <c r="AD77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF77" t="inlineStr"/>
-      <c r="AG77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT77" t="inlineStr"/>
-      <c r="AW77" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>131067773</v>
-      </c>
-      <c r="B78" t="n">
-        <v>57888</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Långan Öst, Jmt</t>
-        </is>
-      </c>
-      <c r="Q78" t="n">
-        <v>466253</v>
-      </c>
-      <c r="R78" t="n">
-        <v>7046994</v>
-      </c>
-      <c r="S78" t="n">
-        <v>10</v>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
-      <c r="AD78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AT78" t="inlineStr"/>
-      <c r="AW78" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>131067811</v>
-      </c>
-      <c r="B79" t="n">
-        <v>58047</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>Långan Öst, Jmt</t>
-        </is>
-      </c>
-      <c r="Q79" t="n">
-        <v>465799</v>
-      </c>
-      <c r="R79" t="n">
-        <v>7046814</v>
-      </c>
-      <c r="S79" t="n">
-        <v>10</v>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Synobservation av 2 st födosökande talltitor i äldre granskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
-        </is>
-      </c>
-      <c r="AD79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT79" t="inlineStr"/>
-      <c r="AW79" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>131067011</v>
-      </c>
-      <c r="B80" t="n">
-        <v>79250</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Långan Öst, Jmt</t>
-        </is>
-      </c>
-      <c r="Q80" t="n">
-        <v>465794</v>
-      </c>
-      <c r="R80" t="n">
-        <v>7046853</v>
-      </c>
-      <c r="S80" t="n">
-        <v>10</v>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>På flera granar i granskog.</t>
-        </is>
-      </c>
-      <c r="AD80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF80" t="inlineStr"/>
-      <c r="AG80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT80" t="inlineStr"/>
-      <c r="AW80" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>131066995</v>
-      </c>
-      <c r="B81" t="n">
-        <v>57888</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>Långan Öst, Jmt</t>
-        </is>
-      </c>
-      <c r="Q81" t="n">
-        <v>466224</v>
-      </c>
-      <c r="R81" t="n">
-        <v>7046722</v>
-      </c>
-      <c r="S81" t="n">
-        <v>10</v>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran i granskog.</t>
-        </is>
-      </c>
-      <c r="AD81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT81" t="inlineStr"/>
-      <c r="AW81" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>131067764</v>
-      </c>
-      <c r="B82" t="n">
-        <v>57948</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Långan Öst, Jmt</t>
-        </is>
-      </c>
-      <c r="Q82" t="n">
-        <v>465732</v>
-      </c>
-      <c r="R82" t="n">
-        <v>7046817</v>
-      </c>
-      <c r="S82" t="n">
-        <v>10</v>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Synobservation av 2 st individer, en hona och en hane, som födosökte i samma döda gran. Hanen födösökte även i en björkhögstubbe. Fyndplatsen finns i äldre granskog med stående död ved i en volym som indikerar mycket högt livsmiljövärde för tretåig hackspett.</t>
-        </is>
-      </c>
-      <c r="AD82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad granskog med inslag av bl.a. björk.</t>
-        </is>
-      </c>
-      <c r="AT82" t="inlineStr"/>
-      <c r="AW82" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41290-2025 artfynd.xlsx
+++ b/artfynd/A 41290-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY75"/>
+  <dimension ref="A1:AZ75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067758</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067463</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1045,6 +1060,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067812</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1176,6 +1196,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067011</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1307,6 +1332,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067013</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1438,6 +1468,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067014</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1540,6 +1575,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067015</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1642,6 +1682,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067016</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1744,6 +1789,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067017</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1875,6 +1925,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067018</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2006,6 +2061,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067019</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2108,6 +2168,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067020</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2239,6 +2304,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067021</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2370,6 +2440,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067022</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2501,6 +2576,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067023</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2632,6 +2712,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067024</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2734,6 +2819,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067025</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2865,6 +2955,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067026</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2967,6 +3062,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067027</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3069,6 +3169,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067028</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3200,6 +3305,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067029</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3307,6 +3417,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067455</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3414,6 +3529,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067456</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3521,6 +3641,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067457</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3628,6 +3753,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067459</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3735,6 +3865,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067462</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3842,6 +3977,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067467</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3949,6 +4089,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067468</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4061,6 +4206,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067470</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4168,6 +4318,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067471</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4275,6 +4430,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067472</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4414,6 +4574,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067820</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4520,6 +4685,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067821</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4626,6 +4796,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067822</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4732,6 +4907,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067823</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4838,6 +5018,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067824</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4950,6 +5135,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067464</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5085,6 +5275,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067004</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5220,6 +5415,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066988</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5355,6 +5555,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066989</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5490,6 +5695,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066990</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5625,6 +5835,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066991</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5760,6 +5975,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066992</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5895,6 +6115,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066993</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6030,6 +6255,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066994</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6165,6 +6395,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066995</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6285,6 +6520,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067458</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6405,6 +6645,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067460</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6525,6 +6770,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067465</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6645,6 +6895,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067466</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6777,6 +7032,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067764</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6912,6 +7172,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067765</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7047,6 +7312,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067766</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7177,6 +7447,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067767</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7307,6 +7582,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067768</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7437,6 +7717,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067769</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7567,6 +7852,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067770</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7697,6 +7987,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067771</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7832,6 +8127,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067772</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7962,6 +8262,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067773</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8097,6 +8402,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067774</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8227,6 +8537,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067775</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8357,6 +8672,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067776</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8487,6 +8807,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067777</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8617,6 +8942,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067778</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8747,6 +9077,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067779</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8877,6 +9212,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067780</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -9012,6 +9352,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067807</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -9147,6 +9492,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067808</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9282,6 +9632,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067809</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9401,6 +9756,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067003</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9521,6 +9881,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067469</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9644,6 +10009,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067813</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9767,8 +10137,89 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067811</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>